--- a/research/traditional_assets/database/data/jordan/jordan_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_restaurant_dining.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ase_jnth" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.147</v>
+        <v>0.0144</v>
       </c>
       <c r="G2">
-        <v>0.0630272952853598</v>
+        <v>0.05400943396226415</v>
       </c>
       <c r="H2">
-        <v>0.0630272952853598</v>
+        <v>0.05400943396226415</v>
       </c>
       <c r="I2">
-        <v>-0.006947890818858561</v>
+        <v>0.02995283018867925</v>
       </c>
       <c r="J2">
-        <v>-0.006947890818858561</v>
+        <v>0.02995283018867925</v>
       </c>
       <c r="K2">
-        <v>-0.412</v>
+        <v>-2.53</v>
       </c>
       <c r="L2">
-        <v>-0.1022332506203474</v>
+        <v>-0.5966981132075471</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.035</v>
+        <v>0.031</v>
       </c>
       <c r="V2">
-        <v>0.00671785028790787</v>
+        <v>0.004889589905362776</v>
       </c>
       <c r="W2">
-        <v>-0.03349593495934959</v>
+        <v>-0.2162393162393162</v>
       </c>
       <c r="X2">
-        <v>0.1623483380693494</v>
+        <v>0.1391218114106326</v>
       </c>
       <c r="Y2">
-        <v>-0.195844273028699</v>
+        <v>-0.3553611276499489</v>
       </c>
       <c r="Z2">
-        <v>0.3869419107057129</v>
+        <v>0.4324324324324326</v>
       </c>
       <c r="AA2">
-        <v>-0.002688430148823812</v>
+        <v>0.01295257521672616</v>
       </c>
       <c r="AB2">
-        <v>0.1552084497676226</v>
+        <v>0.1348501844064836</v>
       </c>
       <c r="AC2">
-        <v>-0.1578968799164464</v>
+        <v>-0.1218976091897574</v>
       </c>
       <c r="AD2">
-        <v>0.554</v>
+        <v>0.493</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.554</v>
+        <v>0.493</v>
       </c>
       <c r="AG2">
-        <v>0.519</v>
+        <v>0.462</v>
       </c>
       <c r="AH2">
-        <v>0.09611380985426787</v>
+        <v>0.07214986096882775</v>
       </c>
       <c r="AI2">
-        <v>0.0444837000160591</v>
+        <v>0.05070451506736603</v>
       </c>
       <c r="AJ2">
-        <v>0.09059172630476522</v>
+        <v>0.0679211996471626</v>
       </c>
       <c r="AK2">
-        <v>0.04179080441259361</v>
+        <v>0.04766817994222038</v>
       </c>
       <c r="AL2">
-        <v>0.092</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AM2">
-        <v>0.092</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AN2">
-        <v>4.043795620437956</v>
+        <v>1.290575916230366</v>
       </c>
       <c r="AO2">
-        <v>-0.3043478260869565</v>
+        <v>1.494117647058824</v>
       </c>
       <c r="AP2">
-        <v>3.788321167883212</v>
+        <v>1.209424083769634</v>
       </c>
       <c r="AQ2">
-        <v>-0.3043478260869565</v>
+        <v>1.494117647058824</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.147</v>
+        <v>0.0144</v>
       </c>
       <c r="G3">
-        <v>0.0630272952853598</v>
+        <v>0.05400943396226415</v>
       </c>
       <c r="H3">
-        <v>0.0630272952853598</v>
+        <v>0.05400943396226415</v>
       </c>
       <c r="I3">
-        <v>-0.006947890818858561</v>
+        <v>0.02995283018867925</v>
       </c>
       <c r="J3">
-        <v>-0.006947890818858561</v>
+        <v>0.02995283018867925</v>
       </c>
       <c r="K3">
-        <v>-0.412</v>
+        <v>-2.53</v>
       </c>
       <c r="L3">
-        <v>-0.1022332506203474</v>
+        <v>-0.5966981132075471</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.035</v>
+        <v>0.031</v>
       </c>
       <c r="V3">
-        <v>0.00671785028790787</v>
+        <v>0.004889589905362776</v>
       </c>
       <c r="W3">
-        <v>-0.03349593495934959</v>
+        <v>-0.2162393162393162</v>
       </c>
       <c r="X3">
-        <v>0.1623483380693494</v>
+        <v>0.1391218114106326</v>
       </c>
       <c r="Y3">
-        <v>-0.195844273028699</v>
+        <v>-0.3553611276499489</v>
       </c>
       <c r="Z3">
-        <v>0.3869419107057129</v>
+        <v>0.4324324324324326</v>
       </c>
       <c r="AA3">
-        <v>-0.002688430148823812</v>
+        <v>0.01295257521672616</v>
       </c>
       <c r="AB3">
-        <v>0.1552084497676226</v>
+        <v>0.1348501844064836</v>
       </c>
       <c r="AC3">
-        <v>-0.1578968799164464</v>
+        <v>-0.1218976091897574</v>
       </c>
       <c r="AD3">
-        <v>0.554</v>
+        <v>0.493</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.554</v>
+        <v>0.493</v>
       </c>
       <c r="AG3">
-        <v>0.519</v>
+        <v>0.462</v>
       </c>
       <c r="AH3">
-        <v>0.09611380985426787</v>
+        <v>0.07214986096882775</v>
       </c>
       <c r="AI3">
-        <v>0.0444837000160591</v>
+        <v>0.05070451506736603</v>
       </c>
       <c r="AJ3">
-        <v>0.09059172630476522</v>
+        <v>0.0679211996471626</v>
       </c>
       <c r="AK3">
-        <v>0.04179080441259361</v>
+        <v>0.04766817994222038</v>
       </c>
       <c r="AL3">
-        <v>0.092</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AM3">
-        <v>0.092</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AN3">
-        <v>4.043795620437956</v>
+        <v>1.290575916230366</v>
       </c>
       <c r="AO3">
-        <v>-0.3043478260869565</v>
+        <v>1.494117647058824</v>
       </c>
       <c r="AP3">
-        <v>3.788321167883212</v>
+        <v>1.209424083769634</v>
       </c>
       <c r="AQ3">
-        <v>-0.3043478260869565</v>
+        <v>1.494117647058824</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Al-Tajamouat For Catering And Housing Co Plc (ASE:JNTH)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ASE:JNTH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restaurant/Dining</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.49411764705882</v>
+      </c>
+      <c r="F2">
+        <v>4.57239548446355</v>
+      </c>
+      <c r="G2">
+        <v>1.29057591623037</v>
+      </c>
+      <c r="H2">
+        <v>4.29298429319372</v>
+      </c>
+      <c r="I2">
+        <v>0.07214986096882781</v>
+      </c>
+      <c r="J2">
+        <v>0.24</v>
+      </c>
+      <c r="K2">
+        <v>6.34</v>
+      </c>
+      <c r="L2">
+        <v>5.62031118145325</v>
+      </c>
+      <c r="M2">
+        <v>6.802</v>
+      </c>
+      <c r="N2">
+        <v>7.22923118145325</v>
+      </c>
+      <c r="O2">
+        <v>0.493</v>
+      </c>
+      <c r="P2">
+        <v>1.63992</v>
+      </c>
+      <c r="Q2">
+        <v>0.134850184406484</v>
+      </c>
+      <c r="R2">
+        <v>0.129173836156885</v>
+      </c>
+      <c r="S2">
+        <v>0.0799168878419704</v>
+      </c>
+      <c r="T2">
+        <v>0.04072</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.139121811410633</v>
+      </c>
+      <c r="X2">
+        <v>0.157106626522217</v>
+      </c>
+      <c r="Y2">
+        <v>0.897054197174286</v>
+      </c>
+      <c r="Z2">
+        <v>1.05787021170192</v>
+      </c>
+      <c r="AA2">
+        <v>0.493</v>
+      </c>
+      <c r="AB2">
+        <v>0.09989610980246301</v>
+      </c>
+      <c r="AC2">
+        <v>1.494117647058824</v>
+      </c>
+      <c r="AD2">
+        <v>0.493</v>
+      </c>
+      <c r="AE2">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AF2">
+        <v>0.255</v>
+      </c>
+      <c r="AG2">
+        <v>0.382</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>6.34</v>
+      </c>
+      <c r="AK2">
+        <v>0.1118347271844283</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.827</v>
+      </c>
+      <c r="AR2">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AS2">
+        <v>0.493</v>
+      </c>
+      <c r="AT2">
+        <v>0.031</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1332464665513499</v>
+      </c>
+      <c r="C2">
+        <v>6.94849917375351</v>
+      </c>
+      <c r="D2">
+        <v>6.917499173753511</v>
+      </c>
+      <c r="E2">
+        <v>-0.493</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.031</v>
+      </c>
+      <c r="H2">
+        <v>6.34</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K2">
+        <v>0.255</v>
+      </c>
+      <c r="L2">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="O2">
+        <v>0.07633333333333335</v>
+      </c>
+      <c r="P2">
+        <v>0.3053333333333333</v>
+      </c>
+      <c r="Q2">
+        <v>0.5603333333333333</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1332464665513499</v>
+      </c>
+      <c r="T2">
+        <v>0.8445182362326223</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1330271736182472</v>
+      </c>
+      <c r="C3">
+        <v>6.896268125099471</v>
+      </c>
+      <c r="D3">
+        <v>6.933598125099471</v>
+      </c>
+      <c r="E3">
+        <v>-0.42467</v>
+      </c>
+      <c r="F3">
+        <v>0.06833</v>
+      </c>
+      <c r="G3">
+        <v>0.031</v>
+      </c>
+      <c r="H3">
+        <v>6.34</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K3">
+        <v>0.255</v>
+      </c>
+      <c r="L3">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M3">
+        <v>0.003054351</v>
+      </c>
+      <c r="N3">
+        <v>0.3786123156666667</v>
+      </c>
+      <c r="O3">
+        <v>0.07572246313333335</v>
+      </c>
+      <c r="P3">
+        <v>0.3028898525333333</v>
+      </c>
+      <c r="Q3">
+        <v>0.5578898525333333</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1340096703214618</v>
+      </c>
+      <c r="T3">
+        <v>0.8513426260203607</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>124.958351763326</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1328078806851445</v>
+      </c>
+      <c r="C4">
+        <v>6.844112184749866</v>
+      </c>
+      <c r="D4">
+        <v>6.949772184749866</v>
+      </c>
+      <c r="E4">
+        <v>-0.35634</v>
+      </c>
+      <c r="F4">
+        <v>0.13666</v>
+      </c>
+      <c r="G4">
+        <v>0.031</v>
+      </c>
+      <c r="H4">
+        <v>6.34</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K4">
+        <v>0.255</v>
+      </c>
+      <c r="L4">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M4">
+        <v>0.006108702000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.3755579646666667</v>
+      </c>
+      <c r="O4">
+        <v>0.07511159293333335</v>
+      </c>
+      <c r="P4">
+        <v>0.3004463717333333</v>
+      </c>
+      <c r="Q4">
+        <v>0.5554463717333333</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1347884496787188</v>
+      </c>
+      <c r="T4">
+        <v>0.8583062890690732</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>62.47917588166302</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1325885877520418</v>
+      </c>
+      <c r="C5">
+        <v>6.792031879550885</v>
+      </c>
+      <c r="D5">
+        <v>6.966021879550885</v>
+      </c>
+      <c r="E5">
+        <v>-0.28801</v>
+      </c>
+      <c r="F5">
+        <v>0.20499</v>
+      </c>
+      <c r="G5">
+        <v>0.031</v>
+      </c>
+      <c r="H5">
+        <v>6.34</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K5">
+        <v>0.255</v>
+      </c>
+      <c r="L5">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M5">
+        <v>0.009163053000000001</v>
+      </c>
+      <c r="N5">
+        <v>0.3725036136666667</v>
+      </c>
+      <c r="O5">
+        <v>0.07450072273333334</v>
+      </c>
+      <c r="P5">
+        <v>0.2980028909333334</v>
+      </c>
+      <c r="Q5">
+        <v>0.5530028909333333</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1355832863423111</v>
+      </c>
+      <c r="T5">
+        <v>0.8654135327992026</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>41.65278392110869</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1323692948189391</v>
+      </c>
+      <c r="C6">
+        <v>6.740027741287689</v>
+      </c>
+      <c r="D6">
+        <v>6.982347741287689</v>
+      </c>
+      <c r="E6">
+        <v>-0.21968</v>
+      </c>
+      <c r="F6">
+        <v>0.27332</v>
+      </c>
+      <c r="G6">
+        <v>0.031</v>
+      </c>
+      <c r="H6">
+        <v>6.34</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K6">
+        <v>0.255</v>
+      </c>
+      <c r="L6">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M6">
+        <v>0.012217404</v>
+      </c>
+      <c r="N6">
+        <v>0.3694492626666667</v>
+      </c>
+      <c r="O6">
+        <v>0.07388985253333334</v>
+      </c>
+      <c r="P6">
+        <v>0.2955594101333334</v>
+      </c>
+      <c r="Q6">
+        <v>0.5505594101333333</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1363946821030615</v>
+      </c>
+      <c r="T6">
+        <v>0.8726688441070432</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>31.23958794083151</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1321500018858364</v>
+      </c>
+      <c r="C7">
+        <v>6.688100306742403</v>
+      </c>
+      <c r="D7">
+        <v>6.998750306742403</v>
+      </c>
+      <c r="E7">
+        <v>-0.15135</v>
+      </c>
+      <c r="F7">
+        <v>0.34165</v>
+      </c>
+      <c r="G7">
+        <v>0.031</v>
+      </c>
+      <c r="H7">
+        <v>6.34</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K7">
+        <v>0.255</v>
+      </c>
+      <c r="L7">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M7">
+        <v>0.015271755</v>
+      </c>
+      <c r="N7">
+        <v>0.3663949116666667</v>
+      </c>
+      <c r="O7">
+        <v>0.07327898233333334</v>
+      </c>
+      <c r="P7">
+        <v>0.2931159293333334</v>
+      </c>
+      <c r="Q7">
+        <v>0.5481159293333333</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1372231598798277</v>
+      </c>
+      <c r="T7">
+        <v>0.8800768988108379</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>24.99167035266521</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1319307089527337</v>
+      </c>
+      <c r="C8">
+        <v>6.636250117752945</v>
+      </c>
+      <c r="D8">
+        <v>7.015230117752945</v>
+      </c>
+      <c r="E8">
+        <v>-0.08302000000000004</v>
+      </c>
+      <c r="F8">
+        <v>0.40998</v>
+      </c>
+      <c r="G8">
+        <v>0.031</v>
+      </c>
+      <c r="H8">
+        <v>6.34</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K8">
+        <v>0.255</v>
+      </c>
+      <c r="L8">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M8">
+        <v>0.018326106</v>
+      </c>
+      <c r="N8">
+        <v>0.3633405606666667</v>
+      </c>
+      <c r="O8">
+        <v>0.07266811213333334</v>
+      </c>
+      <c r="P8">
+        <v>0.2906724485333333</v>
+      </c>
+      <c r="Q8">
+        <v>0.5456724485333333</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1380692648433337</v>
+      </c>
+      <c r="T8">
+        <v>0.8876425716998202</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>20.82639196055434</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.131711416019631</v>
+      </c>
+      <c r="C9">
+        <v>6.584477721272703</v>
+      </c>
+      <c r="D9">
+        <v>7.031787721272704</v>
+      </c>
+      <c r="E9">
+        <v>-0.01468999999999998</v>
+      </c>
+      <c r="F9">
+        <v>0.4783100000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.031</v>
+      </c>
+      <c r="H9">
+        <v>6.34</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K9">
+        <v>0.255</v>
+      </c>
+      <c r="L9">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M9">
+        <v>0.02138045700000001</v>
+      </c>
+      <c r="N9">
+        <v>0.3602862096666667</v>
+      </c>
+      <c r="O9">
+        <v>0.07205724193333334</v>
+      </c>
+      <c r="P9">
+        <v>0.2882289677333333</v>
+      </c>
+      <c r="Q9">
+        <v>0.5432289677333333</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1389335656125064</v>
+      </c>
+      <c r="T9">
+        <v>0.8953709472315761</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>17.85119310904657</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1314921230865283</v>
+      </c>
+      <c r="C10">
+        <v>6.532783669431037</v>
+      </c>
+      <c r="D10">
+        <v>7.048423669431037</v>
+      </c>
+      <c r="E10">
+        <v>0.05363999999999997</v>
+      </c>
+      <c r="F10">
+        <v>0.54664</v>
+      </c>
+      <c r="G10">
+        <v>0.031</v>
+      </c>
+      <c r="H10">
+        <v>6.34</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K10">
+        <v>0.255</v>
+      </c>
+      <c r="L10">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M10">
+        <v>0.024434808</v>
+      </c>
+      <c r="N10">
+        <v>0.3572318586666667</v>
+      </c>
+      <c r="O10">
+        <v>0.07144637173333335</v>
+      </c>
+      <c r="P10">
+        <v>0.2857854869333334</v>
+      </c>
+      <c r="Q10">
+        <v>0.5407854869333334</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1398166555288351</v>
+      </c>
+      <c r="T10">
+        <v>0.9032673309270657</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>15.61979397041576</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1312728301534256</v>
+      </c>
+      <c r="C11">
+        <v>6.481168519594654</v>
+      </c>
+      <c r="D11">
+        <v>7.065138519594655</v>
+      </c>
+      <c r="E11">
+        <v>0.12197</v>
+      </c>
+      <c r="F11">
+        <v>0.61497</v>
+      </c>
+      <c r="G11">
+        <v>0.031</v>
+      </c>
+      <c r="H11">
+        <v>6.34</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K11">
+        <v>0.255</v>
+      </c>
+      <c r="L11">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M11">
+        <v>0.027489159</v>
+      </c>
+      <c r="N11">
+        <v>0.3541775076666667</v>
+      </c>
+      <c r="O11">
+        <v>0.07083550153333334</v>
+      </c>
+      <c r="P11">
+        <v>0.2833420061333334</v>
+      </c>
+      <c r="Q11">
+        <v>0.5383420061333334</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1407191540147534</v>
+      </c>
+      <c r="T11">
+        <v>0.9113372615169616</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>13.88426130703623</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1311415372203229</v>
+      </c>
+      <c r="C12">
+        <v>6.42288386632525</v>
+      </c>
+      <c r="D12">
+        <v>7.075183866325251</v>
+      </c>
+      <c r="E12">
+        <v>0.1903</v>
+      </c>
+      <c r="F12">
+        <v>0.6833</v>
+      </c>
+      <c r="G12">
+        <v>0.031</v>
+      </c>
+      <c r="H12">
+        <v>6.34</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K12">
+        <v>0.255</v>
+      </c>
+      <c r="L12">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M12">
+        <v>0.03129514</v>
+      </c>
+      <c r="N12">
+        <v>0.3503715266666667</v>
+      </c>
+      <c r="O12">
+        <v>0.07007430533333335</v>
+      </c>
+      <c r="P12">
+        <v>0.2802972213333333</v>
+      </c>
+      <c r="Q12">
+        <v>0.5352972213333334</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.141641708022581</v>
+      </c>
+      <c r="T12">
+        <v>0.9195865238977444</v>
+      </c>
+      <c r="U12">
+        <v>0.0458</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03664</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>12.19571686423728</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1309310442872202</v>
+      </c>
+      <c r="C13">
+        <v>6.370718626160393</v>
+      </c>
+      <c r="D13">
+        <v>7.091348626160393</v>
+      </c>
+      <c r="E13">
+        <v>0.25863</v>
+      </c>
+      <c r="F13">
+        <v>0.75163</v>
+      </c>
+      <c r="G13">
+        <v>0.031</v>
+      </c>
+      <c r="H13">
+        <v>6.34</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K13">
+        <v>0.255</v>
+      </c>
+      <c r="L13">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M13">
+        <v>0.034424654</v>
+      </c>
+      <c r="N13">
+        <v>0.3472420126666667</v>
+      </c>
+      <c r="O13">
+        <v>0.06944840253333334</v>
+      </c>
+      <c r="P13">
+        <v>0.2777936101333334</v>
+      </c>
+      <c r="Q13">
+        <v>0.5327936101333334</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1425849935811463</v>
+      </c>
+      <c r="T13">
+        <v>0.9280211629612412</v>
+      </c>
+      <c r="U13">
+        <v>0.0458</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03664</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>11.0870153311248</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1307205513541175</v>
+      </c>
+      <c r="C14">
+        <v>6.318627418791476</v>
+      </c>
+      <c r="D14">
+        <v>7.107587418791477</v>
+      </c>
+      <c r="E14">
+        <v>0.32696</v>
+      </c>
+      <c r="F14">
+        <v>0.81996</v>
+      </c>
+      <c r="G14">
+        <v>0.031</v>
+      </c>
+      <c r="H14">
+        <v>6.34</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K14">
+        <v>0.255</v>
+      </c>
+      <c r="L14">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M14">
+        <v>0.037554168</v>
+      </c>
+      <c r="N14">
+        <v>0.3441124986666667</v>
+      </c>
+      <c r="O14">
+        <v>0.06882249973333335</v>
+      </c>
+      <c r="P14">
+        <v>0.2752899989333334</v>
+      </c>
+      <c r="Q14">
+        <v>0.5302899989333334</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1435497174478608</v>
+      </c>
+      <c r="T14">
+        <v>0.9366474983670903</v>
+      </c>
+      <c r="U14">
+        <v>0.0458</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03664</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>10.1630973868644</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1307388584210148</v>
+      </c>
+      <c r="C15">
+        <v>6.248882140414207</v>
+      </c>
+      <c r="D15">
+        <v>7.106172140414206</v>
+      </c>
+      <c r="E15">
+        <v>0.39529</v>
+      </c>
+      <c r="F15">
+        <v>0.88829</v>
+      </c>
+      <c r="G15">
+        <v>0.031</v>
+      </c>
+      <c r="H15">
+        <v>6.34</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K15">
+        <v>0.255</v>
+      </c>
+      <c r="L15">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M15">
+        <v>0.04263792</v>
+      </c>
+      <c r="N15">
+        <v>0.3390287466666667</v>
+      </c>
+      <c r="O15">
+        <v>0.06780574933333335</v>
+      </c>
+      <c r="P15">
+        <v>0.2712229973333334</v>
+      </c>
+      <c r="Q15">
+        <v>0.5262229973333334</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1445366188747296</v>
+      </c>
+      <c r="T15">
+        <v>0.9454721403339933</v>
+      </c>
+      <c r="U15">
+        <v>0.048</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.0384</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>8.951343467661339</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1305459654879121</v>
+      </c>
+      <c r="C16">
+        <v>6.195492638124458</v>
+      </c>
+      <c r="D16">
+        <v>7.121112638124458</v>
+      </c>
+      <c r="E16">
+        <v>0.4636200000000001</v>
+      </c>
+      <c r="F16">
+        <v>0.9566200000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.031</v>
+      </c>
+      <c r="H16">
+        <v>6.34</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K16">
+        <v>0.255</v>
+      </c>
+      <c r="L16">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M16">
+        <v>0.04591776000000001</v>
+      </c>
+      <c r="N16">
+        <v>0.3357489066666667</v>
+      </c>
+      <c r="O16">
+        <v>0.06714978133333334</v>
+      </c>
+      <c r="P16">
+        <v>0.2685991253333334</v>
+      </c>
+      <c r="Q16">
+        <v>0.5235991253333334</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1455464714975722</v>
+      </c>
+      <c r="T16">
+        <v>0.9545020065326848</v>
+      </c>
+      <c r="U16">
+        <v>0.048</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.0384</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.311961791399812</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1303530725548094</v>
+      </c>
+      <c r="C17">
+        <v>6.142166092027114</v>
+      </c>
+      <c r="D17">
+        <v>7.136116092027114</v>
+      </c>
+      <c r="E17">
+        <v>0.5319499999999999</v>
+      </c>
+      <c r="F17">
+        <v>1.02495</v>
+      </c>
+      <c r="G17">
+        <v>0.031</v>
+      </c>
+      <c r="H17">
+        <v>6.34</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K17">
+        <v>0.255</v>
+      </c>
+      <c r="L17">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M17">
+        <v>0.0491976</v>
+      </c>
+      <c r="N17">
+        <v>0.3324690666666667</v>
+      </c>
+      <c r="O17">
+        <v>0.06649381333333335</v>
+      </c>
+      <c r="P17">
+        <v>0.2659752533333334</v>
+      </c>
+      <c r="Q17">
+        <v>0.5209752533333334</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1465800853585993</v>
+      </c>
+      <c r="T17">
+        <v>0.9637443401713455</v>
+      </c>
+      <c r="U17">
+        <v>0.048</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.0384</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>7.757831005306493</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1303521796217067</v>
+      </c>
+      <c r="C18">
+        <v>6.073905692492222</v>
+      </c>
+      <c r="D18">
+        <v>7.136185692492222</v>
+      </c>
+      <c r="E18">
+        <v>0.6002799999999999</v>
+      </c>
+      <c r="F18">
+        <v>1.09328</v>
+      </c>
+      <c r="G18">
+        <v>0.031</v>
+      </c>
+      <c r="H18">
+        <v>6.34</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K18">
+        <v>0.255</v>
+      </c>
+      <c r="L18">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M18">
+        <v>0.05411736</v>
+      </c>
+      <c r="N18">
+        <v>0.3275493066666667</v>
+      </c>
+      <c r="O18">
+        <v>0.06550986133333335</v>
+      </c>
+      <c r="P18">
+        <v>0.2620394453333333</v>
+      </c>
+      <c r="Q18">
+        <v>0.5170394453333333</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1476383090734603</v>
+      </c>
+      <c r="T18">
+        <v>0.9732067293728314</v>
+      </c>
+      <c r="U18">
+        <v>0.0495</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.0396</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.05257364118772</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.130171286688604</v>
+      </c>
+      <c r="C19">
+        <v>6.019703605186281</v>
+      </c>
+      <c r="D19">
+        <v>7.150313605186281</v>
+      </c>
+      <c r="E19">
+        <v>0.6686099999999999</v>
+      </c>
+      <c r="F19">
+        <v>1.16161</v>
+      </c>
+      <c r="G19">
+        <v>0.031</v>
+      </c>
+      <c r="H19">
+        <v>6.34</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K19">
+        <v>0.255</v>
+      </c>
+      <c r="L19">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M19">
+        <v>0.057499695</v>
+      </c>
+      <c r="N19">
+        <v>0.3241669716666667</v>
+      </c>
+      <c r="O19">
+        <v>0.06483339433333334</v>
+      </c>
+      <c r="P19">
+        <v>0.2593335773333333</v>
+      </c>
+      <c r="Q19">
+        <v>0.5143335773333333</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1487220321549446</v>
+      </c>
+      <c r="T19">
+        <v>0.9828971279526665</v>
+      </c>
+      <c r="U19">
+        <v>0.0495</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.0396</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>6.637716368176678</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1299903937555013</v>
+      </c>
+      <c r="C20">
+        <v>5.965557568511565</v>
+      </c>
+      <c r="D20">
+        <v>7.164497568511566</v>
+      </c>
+      <c r="E20">
+        <v>0.7369399999999999</v>
+      </c>
+      <c r="F20">
+        <v>1.22994</v>
+      </c>
+      <c r="G20">
+        <v>0.031</v>
+      </c>
+      <c r="H20">
+        <v>6.34</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K20">
+        <v>0.255</v>
+      </c>
+      <c r="L20">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M20">
+        <v>0.06088203</v>
+      </c>
+      <c r="N20">
+        <v>0.3207846366666667</v>
+      </c>
+      <c r="O20">
+        <v>0.06415692733333334</v>
+      </c>
+      <c r="P20">
+        <v>0.2566277093333333</v>
+      </c>
+      <c r="Q20">
+        <v>0.5116277093333333</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1498321875067089</v>
+      </c>
+      <c r="T20">
+        <v>0.9928238777173755</v>
+      </c>
+      <c r="U20">
+        <v>0.0495</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.0396</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.268954347722418</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1300223008223986</v>
+      </c>
+      <c r="C21">
+        <v>5.894721623132602</v>
+      </c>
+      <c r="D21">
+        <v>7.161991623132603</v>
+      </c>
+      <c r="E21">
+        <v>0.8052699999999999</v>
+      </c>
+      <c r="F21">
+        <v>1.29827</v>
+      </c>
+      <c r="G21">
+        <v>0.031</v>
+      </c>
+      <c r="H21">
+        <v>6.34</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K21">
+        <v>0.255</v>
+      </c>
+      <c r="L21">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M21">
+        <v>0.066081943</v>
+      </c>
+      <c r="N21">
+        <v>0.3155847236666667</v>
+      </c>
+      <c r="O21">
+        <v>0.06311694473333333</v>
+      </c>
+      <c r="P21">
+        <v>0.2524677789333333</v>
+      </c>
+      <c r="Q21">
+        <v>0.5074677789333333</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1509697541017267</v>
+      </c>
+      <c r="T21">
+        <v>1.002995732414547</v>
+      </c>
+      <c r="U21">
+        <v>0.0509</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.775657454059222</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1298526078892959</v>
+      </c>
+      <c r="C22">
+        <v>5.839739284375475</v>
+      </c>
+      <c r="D22">
+        <v>7.175339284375475</v>
+      </c>
+      <c r="E22">
+        <v>0.8735999999999999</v>
+      </c>
+      <c r="F22">
+        <v>1.3666</v>
+      </c>
+      <c r="G22">
+        <v>0.031</v>
+      </c>
+      <c r="H22">
+        <v>6.34</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K22">
+        <v>0.255</v>
+      </c>
+      <c r="L22">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M22">
+        <v>0.06955994</v>
+      </c>
+      <c r="N22">
+        <v>0.3121067266666667</v>
+      </c>
+      <c r="O22">
+        <v>0.06242134533333335</v>
+      </c>
+      <c r="P22">
+        <v>0.2496853813333334</v>
+      </c>
+      <c r="Q22">
+        <v>0.5046853813333334</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1521357598616199</v>
+      </c>
+      <c r="T22">
+        <v>1.013421883479147</v>
+      </c>
+      <c r="U22">
+        <v>0.0509</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.486874581356262</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1296829149561932</v>
+      </c>
+      <c r="C23">
+        <v>5.784806790053626</v>
+      </c>
+      <c r="D23">
+        <v>7.188736790053627</v>
+      </c>
+      <c r="E23">
+        <v>0.9419299999999999</v>
+      </c>
+      <c r="F23">
+        <v>1.43493</v>
+      </c>
+      <c r="G23">
+        <v>0.031</v>
+      </c>
+      <c r="H23">
+        <v>6.34</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K23">
+        <v>0.255</v>
+      </c>
+      <c r="L23">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M23">
+        <v>0.073037937</v>
+      </c>
+      <c r="N23">
+        <v>0.3086287296666667</v>
+      </c>
+      <c r="O23">
+        <v>0.06172574593333335</v>
+      </c>
+      <c r="P23">
+        <v>0.2469029837333334</v>
+      </c>
+      <c r="Q23">
+        <v>0.5019029837333333</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1533312847546749</v>
+      </c>
+      <c r="T23">
+        <v>1.024111987735256</v>
+      </c>
+      <c r="U23">
+        <v>0.0509</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.225594839386916</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1295132220230905</v>
+      </c>
+      <c r="C24">
+        <v>5.729924419891942</v>
+      </c>
+      <c r="D24">
+        <v>7.202184419891942</v>
+      </c>
+      <c r="E24">
+        <v>1.01026</v>
+      </c>
+      <c r="F24">
+        <v>1.50326</v>
+      </c>
+      <c r="G24">
+        <v>0.031</v>
+      </c>
+      <c r="H24">
+        <v>6.34</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K24">
+        <v>0.255</v>
+      </c>
+      <c r="L24">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M24">
+        <v>0.07651593400000001</v>
+      </c>
+      <c r="N24">
+        <v>0.3051507326666667</v>
+      </c>
+      <c r="O24">
+        <v>0.06103014653333334</v>
+      </c>
+      <c r="P24">
+        <v>0.2441205861333334</v>
+      </c>
+      <c r="Q24">
+        <v>0.4991205861333334</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1545574641321673</v>
+      </c>
+      <c r="T24">
+        <v>1.035076197228701</v>
+      </c>
+      <c r="U24">
+        <v>0.0509</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>4.988067801232965</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1293435290899878</v>
+      </c>
+      <c r="C25">
+        <v>5.675092455712299</v>
+      </c>
+      <c r="D25">
+        <v>7.215682455712299</v>
+      </c>
+      <c r="E25">
+        <v>1.07859</v>
+      </c>
+      <c r="F25">
+        <v>1.57159</v>
+      </c>
+      <c r="G25">
+        <v>0.031</v>
+      </c>
+      <c r="H25">
+        <v>6.34</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K25">
+        <v>0.255</v>
+      </c>
+      <c r="L25">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M25">
+        <v>0.079993931</v>
+      </c>
+      <c r="N25">
+        <v>0.3016727356666667</v>
+      </c>
+      <c r="O25">
+        <v>0.06033454713333334</v>
+      </c>
+      <c r="P25">
+        <v>0.2413381885333334</v>
+      </c>
+      <c r="Q25">
+        <v>0.4963381885333333</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1558154923246595</v>
+      </c>
+      <c r="T25">
+        <v>1.046325191384314</v>
+      </c>
+      <c r="U25">
+        <v>0.0509</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>4.77119528813588</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1291738361568851</v>
+      </c>
+      <c r="C26">
+        <v>5.620311181453252</v>
+      </c>
+      <c r="D26">
+        <v>7.229231181453252</v>
+      </c>
+      <c r="E26">
+        <v>1.14692</v>
+      </c>
+      <c r="F26">
+        <v>1.63992</v>
+      </c>
+      <c r="G26">
+        <v>0.031</v>
+      </c>
+      <c r="H26">
+        <v>6.34</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K26">
+        <v>0.255</v>
+      </c>
+      <c r="L26">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M26">
+        <v>0.083471928</v>
+      </c>
+      <c r="N26">
+        <v>0.2981947386666667</v>
+      </c>
+      <c r="O26">
+        <v>0.05963894773333334</v>
+      </c>
+      <c r="P26">
+        <v>0.2385557909333333</v>
+      </c>
+      <c r="Q26">
+        <v>0.4935557909333333</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1571066265222172</v>
+      </c>
+      <c r="T26">
+        <v>1.057870211701916</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.572395484463551</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1295241432237824</v>
+      </c>
+      <c r="C27">
+        <v>5.524067434559543</v>
+      </c>
+      <c r="D27">
+        <v>7.201317434559543</v>
+      </c>
+      <c r="E27">
+        <v>1.21525</v>
+      </c>
+      <c r="F27">
+        <v>1.70825</v>
+      </c>
+      <c r="G27">
+        <v>0.031</v>
+      </c>
+      <c r="H27">
+        <v>6.34</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K27">
+        <v>0.255</v>
+      </c>
+      <c r="L27">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M27">
+        <v>0.091391375</v>
+      </c>
+      <c r="N27">
+        <v>0.2902752916666667</v>
+      </c>
+      <c r="O27">
+        <v>0.05805505833333335</v>
+      </c>
+      <c r="P27">
+        <v>0.2322202333333334</v>
+      </c>
+      <c r="Q27">
+        <v>0.4872202333333334</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1584321909650432</v>
+      </c>
+      <c r="T27">
+        <v>1.069723099227988</v>
+      </c>
+      <c r="U27">
+        <v>0.0535</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.0428</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.17617818603415</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1293752502906797</v>
+      </c>
+      <c r="C28">
+        <v>5.467575384458594</v>
+      </c>
+      <c r="D28">
+        <v>7.213155384458594</v>
+      </c>
+      <c r="E28">
+        <v>1.28358</v>
+      </c>
+      <c r="F28">
+        <v>1.77658</v>
+      </c>
+      <c r="G28">
+        <v>0.031</v>
+      </c>
+      <c r="H28">
+        <v>6.34</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K28">
+        <v>0.255</v>
+      </c>
+      <c r="L28">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M28">
+        <v>0.09504703</v>
+      </c>
+      <c r="N28">
+        <v>0.2866196366666667</v>
+      </c>
+      <c r="O28">
+        <v>0.05732392733333334</v>
+      </c>
+      <c r="P28">
+        <v>0.2292957093333333</v>
+      </c>
+      <c r="Q28">
+        <v>0.4842957093333333</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1597935814738915</v>
+      </c>
+      <c r="T28">
+        <v>1.081896335065576</v>
+      </c>
+      <c r="U28">
+        <v>0.0535</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.0428</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.015555948109759</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.129809557357577</v>
+      </c>
+      <c r="C29">
+        <v>5.364823457256046</v>
+      </c>
+      <c r="D29">
+        <v>7.178733457256047</v>
+      </c>
+      <c r="E29">
+        <v>1.35191</v>
+      </c>
+      <c r="F29">
+        <v>1.84491</v>
+      </c>
+      <c r="G29">
+        <v>0.031</v>
+      </c>
+      <c r="H29">
+        <v>6.34</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K29">
+        <v>0.255</v>
+      </c>
+      <c r="L29">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M29">
+        <v>0.103683942</v>
+      </c>
+      <c r="N29">
+        <v>0.2779827246666667</v>
+      </c>
+      <c r="O29">
+        <v>0.05559654493333334</v>
+      </c>
+      <c r="P29">
+        <v>0.2223861797333334</v>
+      </c>
+      <c r="Q29">
+        <v>0.4773861797333334</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1611922703528452</v>
+      </c>
+      <c r="T29">
+        <v>1.094403084213782</v>
+      </c>
+      <c r="U29">
+        <v>0.0562</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.04496</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>3.681058602755156</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1296822644244743</v>
+      </c>
+      <c r="C30">
+        <v>5.306548246752363</v>
+      </c>
+      <c r="D30">
+        <v>7.188788246752363</v>
+      </c>
+      <c r="E30">
+        <v>1.42024</v>
+      </c>
+      <c r="F30">
+        <v>1.91324</v>
+      </c>
+      <c r="G30">
+        <v>0.031</v>
+      </c>
+      <c r="H30">
+        <v>6.34</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K30">
+        <v>0.255</v>
+      </c>
+      <c r="L30">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M30">
+        <v>0.107524088</v>
+      </c>
+      <c r="N30">
+        <v>0.2741425786666667</v>
+      </c>
+      <c r="O30">
+        <v>0.05482851573333334</v>
+      </c>
+      <c r="P30">
+        <v>0.2193140629333334</v>
+      </c>
+      <c r="Q30">
+        <v>0.4743140629333333</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1626298117006587</v>
+      </c>
+      <c r="T30">
+        <v>1.107257243060549</v>
+      </c>
+      <c r="U30">
+        <v>0.0562</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.04496</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.549592224085329</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1306453714913716</v>
+      </c>
+      <c r="C31">
+        <v>5.162835321620138</v>
+      </c>
+      <c r="D31">
+        <v>7.113405321620138</v>
+      </c>
+      <c r="E31">
+        <v>1.48857</v>
+      </c>
+      <c r="F31">
+        <v>1.98157</v>
+      </c>
+      <c r="G31">
+        <v>0.031</v>
+      </c>
+      <c r="H31">
+        <v>6.34</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K31">
+        <v>0.255</v>
+      </c>
+      <c r="L31">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M31">
+        <v>0.120677613</v>
+      </c>
+      <c r="N31">
+        <v>0.2609890536666667</v>
+      </c>
+      <c r="O31">
+        <v>0.05219781073333334</v>
+      </c>
+      <c r="P31">
+        <v>0.2087912429333333</v>
+      </c>
+      <c r="Q31">
+        <v>0.4637912429333333</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1641078471709459</v>
+      </c>
+      <c r="T31">
+        <v>1.120473490888916</v>
+      </c>
+      <c r="U31">
+        <v>0.0609</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.162696519914317</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1305556785582689</v>
+      </c>
+      <c r="C32">
+        <v>5.101458811558522</v>
+      </c>
+      <c r="D32">
+        <v>7.120358811558522</v>
+      </c>
+      <c r="E32">
+        <v>1.5569</v>
+      </c>
+      <c r="F32">
+        <v>2.0499</v>
+      </c>
+      <c r="G32">
+        <v>0.031</v>
+      </c>
+      <c r="H32">
+        <v>6.34</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K32">
+        <v>0.255</v>
+      </c>
+      <c r="L32">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M32">
+        <v>0.12483891</v>
+      </c>
+      <c r="N32">
+        <v>0.2568277566666667</v>
+      </c>
+      <c r="O32">
+        <v>0.05136555133333334</v>
+      </c>
+      <c r="P32">
+        <v>0.2054622053333333</v>
+      </c>
+      <c r="Q32">
+        <v>0.4604622053333334</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1656281122260984</v>
+      </c>
+      <c r="T32">
+        <v>1.134067345798093</v>
+      </c>
+      <c r="U32">
+        <v>0.0609</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.057273302583839</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1327723856251662</v>
+      </c>
+      <c r="C33">
+        <v>4.865167238683444</v>
+      </c>
+      <c r="D33">
+        <v>6.952397238683444</v>
+      </c>
+      <c r="E33">
+        <v>1.62523</v>
+      </c>
+      <c r="F33">
+        <v>2.11823</v>
+      </c>
+      <c r="G33">
+        <v>0.031</v>
+      </c>
+      <c r="H33">
+        <v>6.34</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K33">
+        <v>0.255</v>
+      </c>
+      <c r="L33">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M33">
+        <v>0.148699746</v>
+      </c>
+      <c r="N33">
+        <v>0.2329669206666667</v>
+      </c>
+      <c r="O33">
+        <v>0.04659338413333335</v>
+      </c>
+      <c r="P33">
+        <v>0.1863735365333334</v>
+      </c>
+      <c r="Q33">
+        <v>0.4413735365333334</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1671924429350235</v>
+      </c>
+      <c r="T33">
+        <v>1.148055225487246</v>
+      </c>
+      <c r="U33">
+        <v>0.0702</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.05616</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.566693467429774</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1339602926920635</v>
+      </c>
+      <c r="C34">
+        <v>4.710048919962794</v>
+      </c>
+      <c r="D34">
+        <v>6.865608919962794</v>
+      </c>
+      <c r="E34">
+        <v>1.69356</v>
+      </c>
+      <c r="F34">
+        <v>2.18656</v>
+      </c>
+      <c r="G34">
+        <v>0.031</v>
+      </c>
+      <c r="H34">
+        <v>6.34</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K34">
+        <v>0.255</v>
+      </c>
+      <c r="L34">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M34">
+        <v>0.163773344</v>
+      </c>
+      <c r="N34">
+        <v>0.2178933226666667</v>
+      </c>
+      <c r="O34">
+        <v>0.04357866453333335</v>
+      </c>
+      <c r="P34">
+        <v>0.1743146581333334</v>
+      </c>
+      <c r="Q34">
+        <v>0.4293146581333334</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1688027833706816</v>
+      </c>
+      <c r="T34">
+        <v>1.162454513402551</v>
+      </c>
+      <c r="U34">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.05992</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.330456577027985</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1339825997589608</v>
+      </c>
+      <c r="C35">
+        <v>4.640109890603895</v>
+      </c>
+      <c r="D35">
+        <v>6.863999890603895</v>
+      </c>
+      <c r="E35">
+        <v>1.76189</v>
+      </c>
+      <c r="F35">
+        <v>2.25489</v>
+      </c>
+      <c r="G35">
+        <v>0.031</v>
+      </c>
+      <c r="H35">
+        <v>6.34</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K35">
+        <v>0.255</v>
+      </c>
+      <c r="L35">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M35">
+        <v>0.168891261</v>
+      </c>
+      <c r="N35">
+        <v>0.2127754056666667</v>
+      </c>
+      <c r="O35">
+        <v>0.04255508113333335</v>
+      </c>
+      <c r="P35">
+        <v>0.1702203245333334</v>
+      </c>
+      <c r="Q35">
+        <v>0.4252203245333334</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1704611936700907</v>
+      </c>
+      <c r="T35">
+        <v>1.177283630807865</v>
+      </c>
+      <c r="U35">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.05992</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.25983668075441</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1340049068258581</v>
+      </c>
+      <c r="C36">
+        <v>4.57017161525499</v>
+      </c>
+      <c r="D36">
+        <v>6.862391615254991</v>
+      </c>
+      <c r="E36">
+        <v>1.83022</v>
+      </c>
+      <c r="F36">
+        <v>2.32322</v>
+      </c>
+      <c r="G36">
+        <v>0.031</v>
+      </c>
+      <c r="H36">
+        <v>6.34</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K36">
+        <v>0.255</v>
+      </c>
+      <c r="L36">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M36">
+        <v>0.174009178</v>
+      </c>
+      <c r="N36">
+        <v>0.2076574886666667</v>
+      </c>
+      <c r="O36">
+        <v>0.04153149773333335</v>
+      </c>
+      <c r="P36">
+        <v>0.1661259909333334</v>
+      </c>
+      <c r="Q36">
+        <v>0.4211259909333334</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1721698588270577</v>
+      </c>
+      <c r="T36">
+        <v>1.192562115407279</v>
+      </c>
+      <c r="U36">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.05992</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.193370896026339</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1340272138927554</v>
+      </c>
+      <c r="C37">
+        <v>4.500234093386197</v>
+      </c>
+      <c r="D37">
+        <v>6.860784093386198</v>
+      </c>
+      <c r="E37">
+        <v>1.89855</v>
+      </c>
+      <c r="F37">
+        <v>2.391550000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.031</v>
+      </c>
+      <c r="H37">
+        <v>6.34</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K37">
+        <v>0.255</v>
+      </c>
+      <c r="L37">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M37">
+        <v>0.179127095</v>
+      </c>
+      <c r="N37">
+        <v>0.2025395716666667</v>
+      </c>
+      <c r="O37">
+        <v>0.04050791433333334</v>
+      </c>
+      <c r="P37">
+        <v>0.1620316573333334</v>
+      </c>
+      <c r="Q37">
+        <v>0.4170316573333334</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1739310982965468</v>
+      </c>
+      <c r="T37">
+        <v>1.208310707225137</v>
+      </c>
+      <c r="U37">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.05992</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.130703156139872</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1340495209596527</v>
+      </c>
+      <c r="C38">
+        <v>4.430297324468127</v>
+      </c>
+      <c r="D38">
+        <v>6.859177324468127</v>
+      </c>
+      <c r="E38">
+        <v>1.96688</v>
+      </c>
+      <c r="F38">
+        <v>2.45988</v>
+      </c>
+      <c r="G38">
+        <v>0.031</v>
+      </c>
+      <c r="H38">
+        <v>6.34</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K38">
+        <v>0.255</v>
+      </c>
+      <c r="L38">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M38">
+        <v>0.184245012</v>
+      </c>
+      <c r="N38">
+        <v>0.1974216546666667</v>
+      </c>
+      <c r="O38">
+        <v>0.03948433093333335</v>
+      </c>
+      <c r="P38">
+        <v>0.1579373237333334</v>
+      </c>
+      <c r="Q38">
+        <v>0.4129373237333334</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1757473764994573</v>
+      </c>
+      <c r="T38">
+        <v>1.224551442537302</v>
+      </c>
+      <c r="U38">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.05992</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.07151695735821</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.13407182802655</v>
+      </c>
+      <c r="C39">
+        <v>4.360361307971885</v>
+      </c>
+      <c r="D39">
+        <v>6.857571307971885</v>
+      </c>
+      <c r="E39">
+        <v>2.03521</v>
+      </c>
+      <c r="F39">
+        <v>2.52821</v>
+      </c>
+      <c r="G39">
+        <v>0.031</v>
+      </c>
+      <c r="H39">
+        <v>6.34</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K39">
+        <v>0.255</v>
+      </c>
+      <c r="L39">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M39">
+        <v>0.189362929</v>
+      </c>
+      <c r="N39">
+        <v>0.1923037376666667</v>
+      </c>
+      <c r="O39">
+        <v>0.03846074753333335</v>
+      </c>
+      <c r="P39">
+        <v>0.1538429901333334</v>
+      </c>
+      <c r="Q39">
+        <v>0.4088429901333334</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1776213143278572</v>
+      </c>
+      <c r="T39">
+        <v>1.241307756748267</v>
+      </c>
+      <c r="U39">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.05992</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.015530012564744</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1390493350934473</v>
+      </c>
+      <c r="C40">
+        <v>3.951544165435086</v>
+      </c>
+      <c r="D40">
+        <v>6.517084165435087</v>
+      </c>
+      <c r="E40">
+        <v>2.10354</v>
+      </c>
+      <c r="F40">
+        <v>2.59654</v>
+      </c>
+      <c r="G40">
+        <v>0.031</v>
+      </c>
+      <c r="H40">
+        <v>6.34</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K40">
+        <v>0.255</v>
+      </c>
+      <c r="L40">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M40">
+        <v>0.236804448</v>
+      </c>
+      <c r="N40">
+        <v>0.1448622186666667</v>
+      </c>
+      <c r="O40">
+        <v>0.02897244373333334</v>
+      </c>
+      <c r="P40">
+        <v>0.1158897749333333</v>
+      </c>
+      <c r="Q40">
+        <v>0.3708897749333334</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1795557017636246</v>
+      </c>
+      <c r="T40">
+        <v>1.258604597224102</v>
+      </c>
+      <c r="U40">
+        <v>0.0912</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>1.611737743484728</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1392020421603446</v>
+      </c>
+      <c r="C41">
+        <v>3.873301968569238</v>
+      </c>
+      <c r="D41">
+        <v>6.507171968569239</v>
+      </c>
+      <c r="E41">
+        <v>2.17187</v>
+      </c>
+      <c r="F41">
+        <v>2.66487</v>
+      </c>
+      <c r="G41">
+        <v>0.031</v>
+      </c>
+      <c r="H41">
+        <v>6.34</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K41">
+        <v>0.255</v>
+      </c>
+      <c r="L41">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M41">
+        <v>0.243036144</v>
+      </c>
+      <c r="N41">
+        <v>0.1386305226666667</v>
+      </c>
+      <c r="O41">
+        <v>0.02772610453333334</v>
+      </c>
+      <c r="P41">
+        <v>0.1109044181333334</v>
+      </c>
+      <c r="Q41">
+        <v>0.3659044181333334</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1815535117382698</v>
+      </c>
+      <c r="T41">
+        <v>1.276468547223734</v>
+      </c>
+      <c r="U41">
+        <v>0.0912</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>1.570411134677428</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1393547492272419</v>
+      </c>
+      <c r="C42">
+        <v>3.795089877939477</v>
+      </c>
+      <c r="D42">
+        <v>6.497289877939477</v>
+      </c>
+      <c r="E42">
+        <v>2.2402</v>
+      </c>
+      <c r="F42">
+        <v>2.7332</v>
+      </c>
+      <c r="G42">
+        <v>0.031</v>
+      </c>
+      <c r="H42">
+        <v>6.34</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K42">
+        <v>0.255</v>
+      </c>
+      <c r="L42">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M42">
+        <v>0.24926784</v>
+      </c>
+      <c r="N42">
+        <v>0.1323988266666667</v>
+      </c>
+      <c r="O42">
+        <v>0.02647976533333334</v>
+      </c>
+      <c r="P42">
+        <v>0.1059190613333334</v>
+      </c>
+      <c r="Q42">
+        <v>0.3609190613333333</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1836179153787365</v>
+      </c>
+      <c r="T42">
+        <v>1.294927962223354</v>
+      </c>
+      <c r="U42">
+        <v>0.0912</v>
+      </c>
+      <c r="V42">
+        <v>0.2</v>
+      </c>
+      <c r="W42">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>1.531150856310492</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1636357211537894</v>
+      </c>
+      <c r="C43">
+        <v>2.463014920432169</v>
+      </c>
+      <c r="D43">
+        <v>5.233544920432169</v>
+      </c>
+      <c r="E43">
+        <v>2.30853</v>
+      </c>
+      <c r="F43">
+        <v>2.80153</v>
+      </c>
+      <c r="G43">
+        <v>0.031</v>
+      </c>
+      <c r="H43">
+        <v>6.34</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K43">
+        <v>0.255</v>
+      </c>
+      <c r="L43">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M43">
+        <v>0.438719598</v>
+      </c>
+      <c r="N43">
+        <v>-0.05705293133333333</v>
+      </c>
+      <c r="O43">
+        <v>-0.01141058626666667</v>
+      </c>
+      <c r="P43">
+        <v>-0.04564234506666667</v>
+      </c>
+      <c r="Q43">
+        <v>0.2093576549333333</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1874593183075098</v>
+      </c>
+      <c r="T43">
+        <v>1.329276889658375</v>
+      </c>
+      <c r="U43">
+        <v>0.1566</v>
+      </c>
+      <c r="V43">
+        <v>0.1739911635616819</v>
+      </c>
+      <c r="W43">
+        <v>0.1293529837862406</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.8699558178084095</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1648137211537894</v>
+      </c>
+      <c r="C44">
+        <v>2.345760756779028</v>
+      </c>
+      <c r="D44">
+        <v>5.184620756779029</v>
+      </c>
+      <c r="E44">
+        <v>2.37686</v>
+      </c>
+      <c r="F44">
+        <v>2.86986</v>
+      </c>
+      <c r="G44">
+        <v>0.031</v>
+      </c>
+      <c r="H44">
+        <v>6.34</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K44">
+        <v>0.255</v>
+      </c>
+      <c r="L44">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M44">
+        <v>0.4494200760000001</v>
+      </c>
+      <c r="N44">
+        <v>-0.06775340933333335</v>
+      </c>
+      <c r="O44">
+        <v>-0.01355068186666667</v>
+      </c>
+      <c r="P44">
+        <v>-0.05420272746666668</v>
+      </c>
+      <c r="Q44">
+        <v>0.2007972725333333</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1900224100024668</v>
+      </c>
+      <c r="T44">
+        <v>1.35219545672145</v>
+      </c>
+      <c r="U44">
+        <v>0.1566</v>
+      </c>
+      <c r="V44">
+        <v>0.1698485168102133</v>
+      </c>
+      <c r="W44">
+        <v>0.1300017222675206</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.8492425840510665</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1659917211537894</v>
+      </c>
+      <c r="C45">
+        <v>2.229412826082887</v>
+      </c>
+      <c r="D45">
+        <v>5.136602826082887</v>
+      </c>
+      <c r="E45">
+        <v>2.44519</v>
+      </c>
+      <c r="F45">
+        <v>2.93819</v>
+      </c>
+      <c r="G45">
+        <v>0.031</v>
+      </c>
+      <c r="H45">
+        <v>6.34</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K45">
+        <v>0.255</v>
+      </c>
+      <c r="L45">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M45">
+        <v>0.4601205540000001</v>
+      </c>
+      <c r="N45">
+        <v>-0.07845388733333336</v>
+      </c>
+      <c r="O45">
+        <v>-0.01569077746666667</v>
+      </c>
+      <c r="P45">
+        <v>-0.06276310986666669</v>
+      </c>
+      <c r="Q45">
+        <v>0.1922368901333333</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1926754347393522</v>
+      </c>
+      <c r="T45">
+        <v>1.375918184032353</v>
+      </c>
+      <c r="U45">
+        <v>0.1566</v>
+      </c>
+      <c r="V45">
+        <v>0.165898551302999</v>
+      </c>
+      <c r="W45">
+        <v>0.1306202868659504</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.8294927565149951</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1671697211537894</v>
+      </c>
+      <c r="C46">
+        <v>2.113946179880496</v>
+      </c>
+      <c r="D46">
+        <v>5.089466179880496</v>
+      </c>
+      <c r="E46">
+        <v>2.51352</v>
+      </c>
+      <c r="F46">
+        <v>3.00652</v>
+      </c>
+      <c r="G46">
+        <v>0.031</v>
+      </c>
+      <c r="H46">
+        <v>6.34</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K46">
+        <v>0.255</v>
+      </c>
+      <c r="L46">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M46">
+        <v>0.4708210320000001</v>
+      </c>
+      <c r="N46">
+        <v>-0.08915436533333337</v>
+      </c>
+      <c r="O46">
+        <v>-0.01783087306666668</v>
+      </c>
+      <c r="P46">
+        <v>-0.0713234922666667</v>
+      </c>
+      <c r="Q46">
+        <v>0.1836765077333333</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1954232103596978</v>
+      </c>
+      <c r="T46">
+        <v>1.400488151604359</v>
+      </c>
+      <c r="U46">
+        <v>0.1566</v>
+      </c>
+      <c r="V46">
+        <v>0.1621281296824763</v>
+      </c>
+      <c r="W46">
+        <v>0.1312107348917242</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.8106406484123816</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1935220883412692</v>
+      </c>
+      <c r="C47">
+        <v>1.178774974475843</v>
+      </c>
+      <c r="D47">
+        <v>4.222624974475844</v>
+      </c>
+      <c r="E47">
+        <v>2.58185</v>
+      </c>
+      <c r="F47">
+        <v>3.07485</v>
+      </c>
+      <c r="G47">
+        <v>0.031</v>
+      </c>
+      <c r="H47">
+        <v>6.34</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K47">
+        <v>0.255</v>
+      </c>
+      <c r="L47">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M47">
+        <v>0.64202868</v>
+      </c>
+      <c r="N47">
+        <v>-0.2603620133333333</v>
+      </c>
+      <c r="O47">
+        <v>-0.05207240266666666</v>
+      </c>
+      <c r="P47">
+        <v>-0.2082896106666667</v>
+      </c>
+      <c r="Q47">
+        <v>0.04671038933333335</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2013333908889283</v>
+      </c>
+      <c r="T47">
+        <v>1.453335604967248</v>
+      </c>
+      <c r="U47">
+        <v>0.2088</v>
+      </c>
+      <c r="V47">
+        <v>0.1188939617671493</v>
+      </c>
+      <c r="W47">
+        <v>0.1839749407830192</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5944698088357465</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1952220883412692</v>
+      </c>
+      <c r="C48">
+        <v>1.064553358191144</v>
+      </c>
+      <c r="D48">
+        <v>4.176733358191145</v>
+      </c>
+      <c r="E48">
+        <v>2.65018</v>
+      </c>
+      <c r="F48">
+        <v>3.14318</v>
+      </c>
+      <c r="G48">
+        <v>0.031</v>
+      </c>
+      <c r="H48">
+        <v>6.34</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K48">
+        <v>0.255</v>
+      </c>
+      <c r="L48">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M48">
+        <v>0.6562959840000001</v>
+      </c>
+      <c r="N48">
+        <v>-0.2746293173333334</v>
+      </c>
+      <c r="O48">
+        <v>-0.05492586346666668</v>
+      </c>
+      <c r="P48">
+        <v>-0.2197034538666667</v>
+      </c>
+      <c r="Q48">
+        <v>0.03529654613333327</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2043432684979825</v>
+      </c>
+      <c r="T48">
+        <v>1.480249227281456</v>
+      </c>
+      <c r="U48">
+        <v>0.2088</v>
+      </c>
+      <c r="V48">
+        <v>0.1163093104243852</v>
+      </c>
+      <c r="W48">
+        <v>0.1845146159833884</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5815465521219259</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1969220883412692</v>
+      </c>
+      <c r="C49">
+        <v>0.9513185205216579</v>
+      </c>
+      <c r="D49">
+        <v>4.131828520521658</v>
+      </c>
+      <c r="E49">
+        <v>2.71851</v>
+      </c>
+      <c r="F49">
+        <v>3.21151</v>
+      </c>
+      <c r="G49">
+        <v>0.031</v>
+      </c>
+      <c r="H49">
+        <v>6.34</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K49">
+        <v>0.255</v>
+      </c>
+      <c r="L49">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M49">
+        <v>0.6705632880000001</v>
+      </c>
+      <c r="N49">
+        <v>-0.2888966213333334</v>
+      </c>
+      <c r="O49">
+        <v>-0.05777932426666668</v>
+      </c>
+      <c r="P49">
+        <v>-0.2311172970666667</v>
+      </c>
+      <c r="Q49">
+        <v>0.02388270293333331</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2074667263941708</v>
+      </c>
+      <c r="T49">
+        <v>1.50817845798488</v>
+      </c>
+      <c r="U49">
+        <v>0.2088</v>
+      </c>
+      <c r="V49">
+        <v>0.1138346442451429</v>
+      </c>
+      <c r="W49">
+        <v>0.1850313262816141</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5691732212257148</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1986220883412692</v>
+      </c>
+      <c r="C50">
+        <v>0.839038972885362</v>
+      </c>
+      <c r="D50">
+        <v>4.087878972885362</v>
+      </c>
+      <c r="E50">
+        <v>2.78684</v>
+      </c>
+      <c r="F50">
+        <v>3.27984</v>
+      </c>
+      <c r="G50">
+        <v>0.031</v>
+      </c>
+      <c r="H50">
+        <v>6.34</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K50">
+        <v>0.255</v>
+      </c>
+      <c r="L50">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M50">
+        <v>0.6848305920000001</v>
+      </c>
+      <c r="N50">
+        <v>-0.3031639253333334</v>
+      </c>
+      <c r="O50">
+        <v>-0.06063278506666667</v>
+      </c>
+      <c r="P50">
+        <v>-0.2425311402666667</v>
+      </c>
+      <c r="Q50">
+        <v>0.01246885973333331</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2107103172863664</v>
+      </c>
+      <c r="T50">
+        <v>1.537181889869205</v>
+      </c>
+      <c r="U50">
+        <v>0.2088</v>
+      </c>
+      <c r="V50">
+        <v>0.1114630891567025</v>
+      </c>
+      <c r="W50">
+        <v>0.1855265069840805</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5573154457835123</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2003220883412692</v>
+      </c>
+      <c r="C51">
+        <v>0.7276845523539595</v>
+      </c>
+      <c r="D51">
+        <v>4.04485455235396</v>
+      </c>
+      <c r="E51">
+        <v>2.85517</v>
+      </c>
+      <c r="F51">
+        <v>3.34817</v>
+      </c>
+      <c r="G51">
+        <v>0.031</v>
+      </c>
+      <c r="H51">
+        <v>6.34</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K51">
+        <v>0.255</v>
+      </c>
+      <c r="L51">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M51">
+        <v>0.6990978960000001</v>
+      </c>
+      <c r="N51">
+        <v>-0.3174312293333333</v>
+      </c>
+      <c r="O51">
+        <v>-0.06348624586666667</v>
+      </c>
+      <c r="P51">
+        <v>-0.2539449834666667</v>
+      </c>
+      <c r="Q51">
+        <v>0.001055016533333342</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2140811078213932</v>
+      </c>
+      <c r="T51">
+        <v>1.567322711239189</v>
+      </c>
+      <c r="U51">
+        <v>0.2088</v>
+      </c>
+      <c r="V51">
+        <v>0.1091883322351371</v>
+      </c>
+      <c r="W51">
+        <v>0.1860014762293034</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5459416611756855</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2020220883412692</v>
+      </c>
+      <c r="C52">
+        <v>0.6172263526177524</v>
+      </c>
+      <c r="D52">
+        <v>4.002726352617753</v>
+      </c>
+      <c r="E52">
+        <v>2.9235</v>
+      </c>
+      <c r="F52">
+        <v>3.4165</v>
+      </c>
+      <c r="G52">
+        <v>0.031</v>
+      </c>
+      <c r="H52">
+        <v>6.34</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K52">
+        <v>0.255</v>
+      </c>
+      <c r="L52">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M52">
+        <v>0.7133652</v>
+      </c>
+      <c r="N52">
+        <v>-0.3316985333333333</v>
+      </c>
+      <c r="O52">
+        <v>-0.06633970666666666</v>
+      </c>
+      <c r="P52">
+        <v>-0.2653588266666667</v>
+      </c>
+      <c r="Q52">
+        <v>-0.01035882666666665</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2175867299778211</v>
+      </c>
+      <c r="T52">
+        <v>1.598669165463973</v>
+      </c>
+      <c r="U52">
+        <v>0.2088</v>
+      </c>
+      <c r="V52">
+        <v>0.1070045655904344</v>
+      </c>
+      <c r="W52">
+        <v>0.1864574467047173</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5350228279521718</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2037220883412692</v>
+      </c>
+      <c r="C53">
+        <v>0.5076366592201693</v>
+      </c>
+      <c r="D53">
+        <v>3.961466659220169</v>
+      </c>
+      <c r="E53">
+        <v>2.99183</v>
+      </c>
+      <c r="F53">
+        <v>3.48483</v>
+      </c>
+      <c r="G53">
+        <v>0.031</v>
+      </c>
+      <c r="H53">
+        <v>6.34</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K53">
+        <v>0.255</v>
+      </c>
+      <c r="L53">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M53">
+        <v>0.727632504</v>
+      </c>
+      <c r="N53">
+        <v>-0.3459658373333333</v>
+      </c>
+      <c r="O53">
+        <v>-0.06919316746666666</v>
+      </c>
+      <c r="P53">
+        <v>-0.2767726698666667</v>
+      </c>
+      <c r="Q53">
+        <v>-0.02177266986666665</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2212354387528786</v>
+      </c>
+      <c r="T53">
+        <v>1.631295066799972</v>
+      </c>
+      <c r="U53">
+        <v>0.2088</v>
+      </c>
+      <c r="V53">
+        <v>0.104906436853367</v>
+      </c>
+      <c r="W53">
+        <v>0.186895535985017</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5245321842668351</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2054220883412692</v>
+      </c>
+      <c r="C54">
+        <v>0.3988888887569817</v>
+      </c>
+      <c r="D54">
+        <v>3.921048888756982</v>
+      </c>
+      <c r="E54">
+        <v>3.06016</v>
+      </c>
+      <c r="F54">
+        <v>3.55316</v>
+      </c>
+      <c r="G54">
+        <v>0.031</v>
+      </c>
+      <c r="H54">
+        <v>6.34</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K54">
+        <v>0.255</v>
+      </c>
+      <c r="L54">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M54">
+        <v>0.7418998080000001</v>
+      </c>
+      <c r="N54">
+        <v>-0.3602331413333334</v>
+      </c>
+      <c r="O54">
+        <v>-0.07204662826666668</v>
+      </c>
+      <c r="P54">
+        <v>-0.2881865130666667</v>
+      </c>
+      <c r="Q54">
+        <v>-0.0331865130666667</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2250361770602303</v>
+      </c>
+      <c r="T54">
+        <v>1.665280380691639</v>
+      </c>
+      <c r="U54">
+        <v>0.2088</v>
+      </c>
+      <c r="V54">
+        <v>0.1028890053754177</v>
+      </c>
+      <c r="W54">
+        <v>0.1873167756776128</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5144450268770884</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2071220883412692</v>
+      </c>
+      <c r="C55">
+        <v>0.2909575317599598</v>
+      </c>
+      <c r="D55">
+        <v>3.88144753175996</v>
+      </c>
+      <c r="E55">
+        <v>3.12849</v>
+      </c>
+      <c r="F55">
+        <v>3.62149</v>
+      </c>
+      <c r="G55">
+        <v>0.031</v>
+      </c>
+      <c r="H55">
+        <v>6.34</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K55">
+        <v>0.255</v>
+      </c>
+      <c r="L55">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M55">
+        <v>0.7561671120000001</v>
+      </c>
+      <c r="N55">
+        <v>-0.3745004453333334</v>
+      </c>
+      <c r="O55">
+        <v>-0.07490008906666668</v>
+      </c>
+      <c r="P55">
+        <v>-0.2996003562666667</v>
+      </c>
+      <c r="Q55">
+        <v>-0.0446003562666667</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2289986489125756</v>
+      </c>
+      <c r="T55">
+        <v>1.700711878153163</v>
+      </c>
+      <c r="U55">
+        <v>0.2088</v>
+      </c>
+      <c r="V55">
+        <v>0.1009477033872023</v>
+      </c>
+      <c r="W55">
+        <v>0.1877221195327522</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5047385169360112</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2256569000953445</v>
+      </c>
+      <c r="C56">
+        <v>-0.1623831330738388</v>
+      </c>
+      <c r="D56">
+        <v>3.496436866926162</v>
+      </c>
+      <c r="E56">
+        <v>3.196820000000001</v>
+      </c>
+      <c r="F56">
+        <v>3.689820000000001</v>
+      </c>
+      <c r="G56">
+        <v>0.031</v>
+      </c>
+      <c r="H56">
+        <v>6.34</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K56">
+        <v>0.255</v>
+      </c>
+      <c r="L56">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M56">
+        <v>0.8811290160000002</v>
+      </c>
+      <c r="N56">
+        <v>-0.4994623493333334</v>
+      </c>
+      <c r="O56">
+        <v>-0.09989246986666669</v>
+      </c>
+      <c r="P56">
+        <v>-0.3995698794666668</v>
+      </c>
+      <c r="Q56">
+        <v>-0.1445698794666668</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2345134277021431</v>
+      </c>
+      <c r="T56">
+        <v>1.75002374154666</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.08663127867455603</v>
+      </c>
+      <c r="W56">
+        <v>0.218112450652516</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.4331563933727801</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2276569000953445</v>
+      </c>
+      <c r="C57">
+        <v>-0.2677404999866808</v>
+      </c>
+      <c r="D57">
+        <v>3.45940950001332</v>
+      </c>
+      <c r="E57">
+        <v>3.265150000000001</v>
+      </c>
+      <c r="F57">
+        <v>3.758150000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.031</v>
+      </c>
+      <c r="H57">
+        <v>6.34</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K57">
+        <v>0.255</v>
+      </c>
+      <c r="L57">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M57">
+        <v>0.8974462200000002</v>
+      </c>
+      <c r="N57">
+        <v>-0.5157795533333335</v>
+      </c>
+      <c r="O57">
+        <v>-0.1031559106666667</v>
+      </c>
+      <c r="P57">
+        <v>-0.4126236426666668</v>
+      </c>
+      <c r="Q57">
+        <v>-0.1576236426666668</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.238862614984413</v>
+      </c>
+      <c r="T57">
+        <v>1.788913158025474</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.08505616451683683</v>
+      </c>
+      <c r="W57">
+        <v>0.2184885879133794</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.4252808225841841</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2296569000953445</v>
+      </c>
+      <c r="C58">
+        <v>-0.3723218432526054</v>
+      </c>
+      <c r="D58">
+        <v>3.423158156747395</v>
+      </c>
+      <c r="E58">
+        <v>3.333480000000001</v>
+      </c>
+      <c r="F58">
+        <v>3.826480000000001</v>
+      </c>
+      <c r="G58">
+        <v>0.031</v>
+      </c>
+      <c r="H58">
+        <v>6.34</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K58">
+        <v>0.255</v>
+      </c>
+      <c r="L58">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M58">
+        <v>0.9137634240000002</v>
+      </c>
+      <c r="N58">
+        <v>-0.5320967573333335</v>
+      </c>
+      <c r="O58">
+        <v>-0.1064193514666667</v>
+      </c>
+      <c r="P58">
+        <v>-0.4256774058666668</v>
+      </c>
+      <c r="Q58">
+        <v>-0.1706774058666668</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2434094925976951</v>
+      </c>
+      <c r="T58">
+        <v>1.829570275253326</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.08353730443617902</v>
+      </c>
+      <c r="W58">
+        <v>0.2188512917006405</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.4176865221808951</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2316569000953445</v>
+      </c>
+      <c r="C59">
+        <v>-0.4761513058599074</v>
+      </c>
+      <c r="D59">
+        <v>3.387658694140093</v>
+      </c>
+      <c r="E59">
+        <v>3.401810000000001</v>
+      </c>
+      <c r="F59">
+        <v>3.894810000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.031</v>
+      </c>
+      <c r="H59">
+        <v>6.34</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K59">
+        <v>0.255</v>
+      </c>
+      <c r="L59">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M59">
+        <v>0.9300806280000001</v>
+      </c>
+      <c r="N59">
+        <v>-0.5484139613333334</v>
+      </c>
+      <c r="O59">
+        <v>-0.1096827922666667</v>
+      </c>
+      <c r="P59">
+        <v>-0.4387311690666668</v>
+      </c>
+      <c r="Q59">
+        <v>-0.1837311690666668</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2481678528906647</v>
+      </c>
+      <c r="T59">
+        <v>1.87211842118945</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.08207173769168466</v>
+      </c>
+      <c r="W59">
+        <v>0.2192012690392257</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.4103586884584233</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2336569000953445</v>
+      </c>
+      <c r="C60">
+        <v>-0.5792520395879128</v>
+      </c>
+      <c r="D60">
+        <v>3.352887960412087</v>
+      </c>
+      <c r="E60">
+        <v>3.47014</v>
+      </c>
+      <c r="F60">
+        <v>3.96314</v>
+      </c>
+      <c r="G60">
+        <v>0.031</v>
+      </c>
+      <c r="H60">
+        <v>6.34</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K60">
+        <v>0.255</v>
+      </c>
+      <c r="L60">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M60">
+        <v>0.9463978319999999</v>
+      </c>
+      <c r="N60">
+        <v>-0.5647311653333332</v>
+      </c>
+      <c r="O60">
+        <v>-0.1129462330666667</v>
+      </c>
+      <c r="P60">
+        <v>-0.4517849322666666</v>
+      </c>
+      <c r="Q60">
+        <v>-0.1967849322666666</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2531528017690138</v>
+      </c>
+      <c r="T60">
+        <v>1.916692669313008</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.08065670773148322</v>
+      </c>
+      <c r="W60">
+        <v>0.2195391781937218</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.4032835386574161</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2356569000953445</v>
+      </c>
+      <c r="C61">
+        <v>-0.6816462553587419</v>
+      </c>
+      <c r="D61">
+        <v>3.318823744641258</v>
+      </c>
+      <c r="E61">
+        <v>3.53847</v>
+      </c>
+      <c r="F61">
+        <v>4.03147</v>
+      </c>
+      <c r="G61">
+        <v>0.031</v>
+      </c>
+      <c r="H61">
+        <v>6.34</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K61">
+        <v>0.255</v>
+      </c>
+      <c r="L61">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M61">
+        <v>0.962715036</v>
+      </c>
+      <c r="N61">
+        <v>-0.5810483693333333</v>
+      </c>
+      <c r="O61">
+        <v>-0.1162096738666667</v>
+      </c>
+      <c r="P61">
+        <v>-0.4648386954666666</v>
+      </c>
+      <c r="Q61">
+        <v>-0.2098386954666666</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2583809188853313</v>
+      </c>
+      <c r="T61">
+        <v>1.963441271003569</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.07928964488857672</v>
+      </c>
+      <c r="W61">
+        <v>0.2198656328006079</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3964482244428835</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2376569000953445</v>
+      </c>
+      <c r="C62">
+        <v>-0.7833552705505711</v>
+      </c>
+      <c r="D62">
+        <v>3.285444729449429</v>
+      </c>
+      <c r="E62">
+        <v>3.6068</v>
+      </c>
+      <c r="F62">
+        <v>4.0998</v>
+      </c>
+      <c r="G62">
+        <v>0.031</v>
+      </c>
+      <c r="H62">
+        <v>6.34</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K62">
+        <v>0.255</v>
+      </c>
+      <c r="L62">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M62">
+        <v>0.9790322400000001</v>
+      </c>
+      <c r="N62">
+        <v>-0.5973655733333334</v>
+      </c>
+      <c r="O62">
+        <v>-0.1194731146666667</v>
+      </c>
+      <c r="P62">
+        <v>-0.4778924586666667</v>
+      </c>
+      <c r="Q62">
+        <v>-0.2228924586666667</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2638704418574646</v>
+      </c>
+      <c r="T62">
+        <v>2.012527302778659</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.07796815080710043</v>
+      </c>
+      <c r="W62">
+        <v>0.2201812055872644</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3898407540355021</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2396569000953445</v>
+      </c>
+      <c r="C63">
+        <v>-0.8843995534842404</v>
+      </c>
+      <c r="D63">
+        <v>3.252730446515759</v>
+      </c>
+      <c r="E63">
+        <v>3.67513</v>
+      </c>
+      <c r="F63">
+        <v>4.16813</v>
+      </c>
+      <c r="G63">
+        <v>0.031</v>
+      </c>
+      <c r="H63">
+        <v>6.34</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K63">
+        <v>0.255</v>
+      </c>
+      <c r="L63">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M63">
+        <v>0.9953494439999999</v>
+      </c>
+      <c r="N63">
+        <v>-0.6136827773333332</v>
+      </c>
+      <c r="O63">
+        <v>-0.1227365554666666</v>
+      </c>
+      <c r="P63">
+        <v>-0.4909462218666666</v>
+      </c>
+      <c r="Q63">
+        <v>-0.2359462218666666</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2696414788281688</v>
+      </c>
+      <c r="T63">
+        <v>2.06413056695247</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.07668998440042667</v>
+      </c>
+      <c r="W63">
+        <v>0.2204864317251781</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3834499220021333</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2416569000953445</v>
+      </c>
+      <c r="C64">
+        <v>-0.9847987652782386</v>
+      </c>
+      <c r="D64">
+        <v>3.220661234721761</v>
+      </c>
+      <c r="E64">
+        <v>3.74346</v>
+      </c>
+      <c r="F64">
+        <v>4.23646</v>
+      </c>
+      <c r="G64">
+        <v>0.031</v>
+      </c>
+      <c r="H64">
+        <v>6.34</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K64">
+        <v>0.255</v>
+      </c>
+      <c r="L64">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M64">
+        <v>1.011666648</v>
+      </c>
+      <c r="N64">
+        <v>-0.6299999813333333</v>
+      </c>
+      <c r="O64">
+        <v>-0.1259999962666667</v>
+      </c>
+      <c r="P64">
+        <v>-0.5039999850666667</v>
+      </c>
+      <c r="Q64">
+        <v>-0.2489999850666667</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2757162545868048</v>
+      </c>
+      <c r="T64">
+        <v>2.118449792398588</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.0754530491681617</v>
+      </c>
+      <c r="W64">
+        <v>0.220781811858643</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3772652458408086</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2436569000953445</v>
+      </c>
+      <c r="C65">
+        <v>-1.084571799251933</v>
+      </c>
+      <c r="D65">
+        <v>3.189218200748067</v>
+      </c>
+      <c r="E65">
+        <v>3.811790000000001</v>
+      </c>
+      <c r="F65">
+        <v>4.304790000000001</v>
+      </c>
+      <c r="G65">
+        <v>0.031</v>
+      </c>
+      <c r="H65">
+        <v>6.34</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K65">
+        <v>0.255</v>
+      </c>
+      <c r="L65">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M65">
+        <v>1.027983852</v>
+      </c>
+      <c r="N65">
+        <v>-0.6463171853333335</v>
+      </c>
+      <c r="O65">
+        <v>-0.1292634370666667</v>
+      </c>
+      <c r="P65">
+        <v>-0.5170537482666668</v>
+      </c>
+      <c r="Q65">
+        <v>-0.2620537482666668</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2821193966026644</v>
+      </c>
+      <c r="T65">
+        <v>2.175705192193144</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.07425538172104802</v>
+      </c>
+      <c r="W65">
+        <v>0.2210678148450137</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3712769086052401</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2456569000953445</v>
+      </c>
+      <c r="C66">
+        <v>-1.183736818042971</v>
+      </c>
+      <c r="D66">
+        <v>3.158383181957029</v>
+      </c>
+      <c r="E66">
+        <v>3.88012</v>
+      </c>
+      <c r="F66">
+        <v>4.37312</v>
+      </c>
+      <c r="G66">
+        <v>0.031</v>
+      </c>
+      <c r="H66">
+        <v>6.34</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K66">
+        <v>0.255</v>
+      </c>
+      <c r="L66">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M66">
+        <v>1.044301056</v>
+      </c>
+      <c r="N66">
+        <v>-0.6626343893333334</v>
+      </c>
+      <c r="O66">
+        <v>-0.1325268778666667</v>
+      </c>
+      <c r="P66">
+        <v>-0.5301075114666667</v>
+      </c>
+      <c r="Q66">
+        <v>-0.2751075114666667</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2888782687305162</v>
+      </c>
+      <c r="T66">
+        <v>2.236141447531843</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.07309514138165665</v>
+      </c>
+      <c r="W66">
+        <v>0.2213448802380604</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3654757069082832</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2476569000953445</v>
+      </c>
+      <c r="C67">
+        <v>-1.282311288592092</v>
+      </c>
+      <c r="D67">
+        <v>3.128138711407909</v>
+      </c>
+      <c r="E67">
+        <v>3.948450000000001</v>
+      </c>
+      <c r="F67">
+        <v>4.441450000000001</v>
+      </c>
+      <c r="G67">
+        <v>0.031</v>
+      </c>
+      <c r="H67">
+        <v>6.34</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K67">
+        <v>0.255</v>
+      </c>
+      <c r="L67">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M67">
+        <v>1.06061826</v>
+      </c>
+      <c r="N67">
+        <v>-0.6789515933333335</v>
+      </c>
+      <c r="O67">
+        <v>-0.1357903186666667</v>
+      </c>
+      <c r="P67">
+        <v>-0.5431612746666669</v>
+      </c>
+      <c r="Q67">
+        <v>-0.2881612746666669</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2960233621228167</v>
+      </c>
+      <c r="T67">
+        <v>2.30003120317561</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.07197060074501577</v>
+      </c>
+      <c r="W67">
+        <v>0.2216134205420902</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3598530037250788</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2496569000953445</v>
+      </c>
+      <c r="C68">
+        <v>-1.380312015136904</v>
+      </c>
+      <c r="D68">
+        <v>3.098467984863096</v>
+      </c>
+      <c r="E68">
+        <v>4.01678</v>
+      </c>
+      <c r="F68">
+        <v>4.50978</v>
+      </c>
+      <c r="G68">
+        <v>0.031</v>
+      </c>
+      <c r="H68">
+        <v>6.34</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K68">
+        <v>0.255</v>
+      </c>
+      <c r="L68">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M68">
+        <v>1.076935464</v>
+      </c>
+      <c r="N68">
+        <v>-0.6952687973333335</v>
+      </c>
+      <c r="O68">
+        <v>-0.1390537594666667</v>
+      </c>
+      <c r="P68">
+        <v>-0.5562150378666668</v>
+      </c>
+      <c r="Q68">
+        <v>-0.3012150378666668</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.303588755126429</v>
+      </c>
+      <c r="T68">
+        <v>2.367679179739599</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.07088013709736402</v>
+      </c>
+      <c r="W68">
+        <v>0.2218738232611495</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3544006854868201</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2516569000953445</v>
+      </c>
+      <c r="C69">
+        <v>-1.47775517034564</v>
+      </c>
+      <c r="D69">
+        <v>3.06935482965436</v>
+      </c>
+      <c r="E69">
+        <v>4.08511</v>
+      </c>
+      <c r="F69">
+        <v>4.578110000000001</v>
+      </c>
+      <c r="G69">
+        <v>0.031</v>
+      </c>
+      <c r="H69">
+        <v>6.34</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K69">
+        <v>0.255</v>
+      </c>
+      <c r="L69">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M69">
+        <v>1.093252668</v>
+      </c>
+      <c r="N69">
+        <v>-0.7115860013333334</v>
+      </c>
+      <c r="O69">
+        <v>-0.1423172002666667</v>
+      </c>
+      <c r="P69">
+        <v>-0.5692688010666667</v>
+      </c>
+      <c r="Q69">
+        <v>-0.3142688010666667</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3116126567969268</v>
+      </c>
+      <c r="T69">
+        <v>2.439427033671101</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06982222460337352</v>
+      </c>
+      <c r="W69">
+        <v>0.2221264527647144</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3491111230168675</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2536569000953445</v>
+      </c>
+      <c r="C70">
+        <v>-1.574656324712033</v>
+      </c>
+      <c r="D70">
+        <v>3.040783675287967</v>
+      </c>
+      <c r="E70">
+        <v>4.15344</v>
+      </c>
+      <c r="F70">
+        <v>4.64644</v>
+      </c>
+      <c r="G70">
+        <v>0.031</v>
+      </c>
+      <c r="H70">
+        <v>6.34</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K70">
+        <v>0.255</v>
+      </c>
+      <c r="L70">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M70">
+        <v>1.109569872</v>
+      </c>
+      <c r="N70">
+        <v>-0.7279032053333333</v>
+      </c>
+      <c r="O70">
+        <v>-0.1455806410666667</v>
+      </c>
+      <c r="P70">
+        <v>-0.5823225642666666</v>
+      </c>
+      <c r="Q70">
+        <v>-0.3273225642666666</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3201380523218307</v>
+      </c>
+      <c r="T70">
+        <v>2.515659128473323</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06879542718273567</v>
+      </c>
+      <c r="W70">
+        <v>0.2223716519887627</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3439771359136784</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2556569000953445</v>
+      </c>
+      <c r="C71">
+        <v>-1.671030474323607</v>
+      </c>
+      <c r="D71">
+        <v>3.012739525676394</v>
+      </c>
+      <c r="E71">
+        <v>4.22177</v>
+      </c>
+      <c r="F71">
+        <v>4.714770000000001</v>
+      </c>
+      <c r="G71">
+        <v>0.031</v>
+      </c>
+      <c r="H71">
+        <v>6.34</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K71">
+        <v>0.255</v>
+      </c>
+      <c r="L71">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M71">
+        <v>1.125887076</v>
+      </c>
+      <c r="N71">
+        <v>-0.7442204093333334</v>
+      </c>
+      <c r="O71">
+        <v>-0.1488440818666667</v>
+      </c>
+      <c r="P71">
+        <v>-0.5953763274666668</v>
+      </c>
+      <c r="Q71">
+        <v>-0.3403763274666668</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3292134733644705</v>
+      </c>
+      <c r="T71">
+        <v>2.596809422940205</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06779839200617428</v>
+      </c>
+      <c r="W71">
+        <v>0.2226097439889256</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3389919600308714</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2576569000953445</v>
+      </c>
+      <c r="C72">
+        <v>-1.766892067107422</v>
+      </c>
+      <c r="D72">
+        <v>2.985207932892579</v>
+      </c>
+      <c r="E72">
+        <v>4.290100000000001</v>
+      </c>
+      <c r="F72">
+        <v>4.783100000000001</v>
+      </c>
+      <c r="G72">
+        <v>0.031</v>
+      </c>
+      <c r="H72">
+        <v>6.34</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K72">
+        <v>0.255</v>
+      </c>
+      <c r="L72">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M72">
+        <v>1.14220428</v>
+      </c>
+      <c r="N72">
+        <v>-0.7605376133333336</v>
+      </c>
+      <c r="O72">
+        <v>-0.1521075226666667</v>
+      </c>
+      <c r="P72">
+        <v>-0.6084300906666669</v>
+      </c>
+      <c r="Q72">
+        <v>-0.3534300906666669</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3388939224766195</v>
+      </c>
+      <c r="T72">
+        <v>2.683369737038212</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.06682984354894321</v>
+      </c>
+      <c r="W72">
+        <v>0.2228410333605124</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3341492177447161</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2596569000953445</v>
+      </c>
+      <c r="C73">
+        <v>-1.862255027649779</v>
+      </c>
+      <c r="D73">
+        <v>2.95817497235022</v>
+      </c>
+      <c r="E73">
+        <v>4.358429999999999</v>
+      </c>
+      <c r="F73">
+        <v>4.85143</v>
+      </c>
+      <c r="G73">
+        <v>0.031</v>
+      </c>
+      <c r="H73">
+        <v>6.34</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K73">
+        <v>0.255</v>
+      </c>
+      <c r="L73">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M73">
+        <v>1.158521484</v>
+      </c>
+      <c r="N73">
+        <v>-0.7768548173333333</v>
+      </c>
+      <c r="O73">
+        <v>-0.1553709634666667</v>
+      </c>
+      <c r="P73">
+        <v>-0.6214838538666666</v>
+      </c>
+      <c r="Q73">
+        <v>-0.3664838538666666</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3492419887689167</v>
+      </c>
+      <c r="T73">
+        <v>2.775899727970563</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06588857814684544</v>
+      </c>
+      <c r="W73">
+        <v>0.2230658075385333</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3294428907342272</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2616569000953445</v>
+      </c>
+      <c r="C74">
+        <v>-1.9571327806795</v>
+      </c>
+      <c r="D74">
+        <v>2.9316272193205</v>
+      </c>
+      <c r="E74">
+        <v>4.42676</v>
+      </c>
+      <c r="F74">
+        <v>4.91976</v>
+      </c>
+      <c r="G74">
+        <v>0.031</v>
+      </c>
+      <c r="H74">
+        <v>6.34</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K74">
+        <v>0.255</v>
+      </c>
+      <c r="L74">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M74">
+        <v>1.174838688</v>
+      </c>
+      <c r="N74">
+        <v>-0.7931720213333334</v>
+      </c>
+      <c r="O74">
+        <v>-0.1586344042666667</v>
+      </c>
+      <c r="P74">
+        <v>-0.6345376170666668</v>
+      </c>
+      <c r="Q74">
+        <v>-0.3795376170666668</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3603292026535208</v>
+      </c>
+      <c r="T74">
+        <v>2.875039003969512</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06497345900591703</v>
+      </c>
+      <c r="W74">
+        <v>0.223284337989387</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3248672950295851</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2636569000953445</v>
+      </c>
+      <c r="C75">
+        <v>-2.051538273297937</v>
+      </c>
+      <c r="D75">
+        <v>2.905551726702062</v>
+      </c>
+      <c r="E75">
+        <v>4.495089999999999</v>
+      </c>
+      <c r="F75">
+        <v>4.98809</v>
+      </c>
+      <c r="G75">
+        <v>0.031</v>
+      </c>
+      <c r="H75">
+        <v>6.34</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K75">
+        <v>0.255</v>
+      </c>
+      <c r="L75">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M75">
+        <v>1.191155892</v>
+      </c>
+      <c r="N75">
+        <v>-0.8094892253333333</v>
+      </c>
+      <c r="O75">
+        <v>-0.1618978450666667</v>
+      </c>
+      <c r="P75">
+        <v>-0.6475913802666666</v>
+      </c>
+      <c r="Q75">
+        <v>-0.3925913802666666</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3722376916406882</v>
+      </c>
+      <c r="T75">
+        <v>2.981521930042457</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06408341162227432</v>
+      </c>
+      <c r="W75">
+        <v>0.2234968813046009</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3204170581113717</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2656569000953445</v>
+      </c>
+      <c r="C76">
+        <v>-2.145483996033115</v>
+      </c>
+      <c r="D76">
+        <v>2.879936003966885</v>
+      </c>
+      <c r="E76">
+        <v>4.56342</v>
+      </c>
+      <c r="F76">
+        <v>5.05642</v>
+      </c>
+      <c r="G76">
+        <v>0.031</v>
+      </c>
+      <c r="H76">
+        <v>6.34</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K76">
+        <v>0.255</v>
+      </c>
+      <c r="L76">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M76">
+        <v>1.207473096</v>
+      </c>
+      <c r="N76">
+        <v>-0.8258064293333335</v>
+      </c>
+      <c r="O76">
+        <v>-0.1651612858666667</v>
+      </c>
+      <c r="P76">
+        <v>-0.6606451434666668</v>
+      </c>
+      <c r="Q76">
+        <v>-0.4056451434666668</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3850622182422532</v>
+      </c>
+      <c r="T76">
+        <v>3.096195850428705</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06321741957332466</v>
+      </c>
+      <c r="W76">
+        <v>0.2237036802058901</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3160870978666234</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2676569000953445</v>
+      </c>
+      <c r="C77">
+        <v>-2.238982002789889</v>
+      </c>
+      <c r="D77">
+        <v>2.854767997210112</v>
+      </c>
+      <c r="E77">
+        <v>4.63175</v>
+      </c>
+      <c r="F77">
+        <v>5.124750000000001</v>
+      </c>
+      <c r="G77">
+        <v>0.031</v>
+      </c>
+      <c r="H77">
+        <v>6.34</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K77">
+        <v>0.255</v>
+      </c>
+      <c r="L77">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M77">
+        <v>1.2237903</v>
+      </c>
+      <c r="N77">
+        <v>-0.8421236333333334</v>
+      </c>
+      <c r="O77">
+        <v>-0.1684247266666667</v>
+      </c>
+      <c r="P77">
+        <v>-0.6736989066666668</v>
+      </c>
+      <c r="Q77">
+        <v>-0.4186989066666668</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3989127069719434</v>
+      </c>
+      <c r="T77">
+        <v>3.220043684445854</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06237452064568035</v>
+      </c>
+      <c r="W77">
+        <v>0.2239049644698115</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3118726032284017</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2696569000953445</v>
+      </c>
+      <c r="C78">
+        <v>-2.3320439297631</v>
+      </c>
+      <c r="D78">
+        <v>2.8300360702369</v>
+      </c>
+      <c r="E78">
+        <v>4.70008</v>
+      </c>
+      <c r="F78">
+        <v>5.19308</v>
+      </c>
+      <c r="G78">
+        <v>0.031</v>
+      </c>
+      <c r="H78">
+        <v>6.34</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K78">
+        <v>0.255</v>
+      </c>
+      <c r="L78">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M78">
+        <v>1.240107504</v>
+      </c>
+      <c r="N78">
+        <v>-0.8584408373333333</v>
+      </c>
+      <c r="O78">
+        <v>-0.1716881674666667</v>
+      </c>
+      <c r="P78">
+        <v>-0.6867526698666666</v>
+      </c>
+      <c r="Q78">
+        <v>-0.4317526698666666</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4139174030957743</v>
+      </c>
+      <c r="T78">
+        <v>3.354212171297764</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.0615538032687635</v>
+      </c>
+      <c r="W78">
+        <v>0.2241009517794193</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3077690163438175</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2716569000953445</v>
+      </c>
+      <c r="C79">
+        <v>-2.424681013376068</v>
+      </c>
+      <c r="D79">
+        <v>2.805728986623933</v>
+      </c>
+      <c r="E79">
+        <v>4.76841</v>
+      </c>
+      <c r="F79">
+        <v>5.261410000000001</v>
+      </c>
+      <c r="G79">
+        <v>0.031</v>
+      </c>
+      <c r="H79">
+        <v>6.34</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K79">
+        <v>0.255</v>
+      </c>
+      <c r="L79">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M79">
+        <v>1.256424708</v>
+      </c>
+      <c r="N79">
+        <v>-0.8747580413333335</v>
+      </c>
+      <c r="O79">
+        <v>-0.1749516082666667</v>
+      </c>
+      <c r="P79">
+        <v>-0.6998064330666668</v>
+      </c>
+      <c r="Q79">
+        <v>-0.4448064330666668</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4302268554042862</v>
+      </c>
+      <c r="T79">
+        <v>3.500047483093319</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06075440322631202</v>
+      </c>
+      <c r="W79">
+        <v>0.2242918485095567</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3037720161315601</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2736569000953445</v>
+      </c>
+      <c r="C80">
+        <v>-2.516904107302496</v>
+      </c>
+      <c r="D80">
+        <v>2.781835892697504</v>
+      </c>
+      <c r="E80">
+        <v>4.83674</v>
+      </c>
+      <c r="F80">
+        <v>5.32974</v>
+      </c>
+      <c r="G80">
+        <v>0.031</v>
+      </c>
+      <c r="H80">
+        <v>6.34</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K80">
+        <v>0.255</v>
+      </c>
+      <c r="L80">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M80">
+        <v>1.272741912</v>
+      </c>
+      <c r="N80">
+        <v>-0.8910752453333334</v>
+      </c>
+      <c r="O80">
+        <v>-0.1782150490666667</v>
+      </c>
+      <c r="P80">
+        <v>-0.7128601962666667</v>
+      </c>
+      <c r="Q80">
+        <v>-0.4578601962666667</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4480189851953902</v>
+      </c>
+      <c r="T80">
+        <v>3.659140550506653</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05997550062084648</v>
+      </c>
+      <c r="W80">
+        <v>0.2244778504517419</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2998775031042324</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2756569000953445</v>
+      </c>
+      <c r="C81">
+        <v>-2.608723698626015</v>
+      </c>
+      <c r="D81">
+        <v>2.758346301373986</v>
+      </c>
+      <c r="E81">
+        <v>4.90507</v>
+      </c>
+      <c r="F81">
+        <v>5.398070000000001</v>
+      </c>
+      <c r="G81">
+        <v>0.031</v>
+      </c>
+      <c r="H81">
+        <v>6.34</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K81">
+        <v>0.255</v>
+      </c>
+      <c r="L81">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M81">
+        <v>1.289059116</v>
+      </c>
+      <c r="N81">
+        <v>-0.9073924493333335</v>
+      </c>
+      <c r="O81">
+        <v>-0.1814784898666667</v>
+      </c>
+      <c r="P81">
+        <v>-0.7259139594666668</v>
+      </c>
+      <c r="Q81">
+        <v>-0.4709139594666668</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4675056035380279</v>
+      </c>
+      <c r="T81">
+        <v>3.833385338626017</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05921631706868387</v>
+      </c>
+      <c r="W81">
+        <v>0.2246591434839983</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2960815853434193</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2776569000953445</v>
+      </c>
+      <c r="C82">
+        <v>-2.700149923187858</v>
+      </c>
+      <c r="D82">
+        <v>2.735250076812142</v>
+      </c>
+      <c r="E82">
+        <v>4.9734</v>
+      </c>
+      <c r="F82">
+        <v>5.4664</v>
+      </c>
+      <c r="G82">
+        <v>0.031</v>
+      </c>
+      <c r="H82">
+        <v>6.34</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K82">
+        <v>0.255</v>
+      </c>
+      <c r="L82">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M82">
+        <v>1.30537632</v>
+      </c>
+      <c r="N82">
+        <v>-0.9237096533333334</v>
+      </c>
+      <c r="O82">
+        <v>-0.1847419306666667</v>
+      </c>
+      <c r="P82">
+        <v>-0.7389677226666668</v>
+      </c>
+      <c r="Q82">
+        <v>-0.4839677226666668</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4889408837149293</v>
+      </c>
+      <c r="T82">
+        <v>4.025054605557318</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05847611310532531</v>
+      </c>
+      <c r="W82">
+        <v>0.2248359041904483</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2923805655266266</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2796569000953445</v>
+      </c>
+      <c r="C83">
+        <v>-2.791192580169904</v>
+      </c>
+      <c r="D83">
+        <v>2.712537419830097</v>
+      </c>
+      <c r="E83">
+        <v>5.04173</v>
+      </c>
+      <c r="F83">
+        <v>5.534730000000001</v>
+      </c>
+      <c r="G83">
+        <v>0.031</v>
+      </c>
+      <c r="H83">
+        <v>6.34</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K83">
+        <v>0.255</v>
+      </c>
+      <c r="L83">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M83">
+        <v>1.321693524</v>
+      </c>
+      <c r="N83">
+        <v>-0.9400268573333336</v>
+      </c>
+      <c r="O83">
+        <v>-0.1880053714666667</v>
+      </c>
+      <c r="P83">
+        <v>-0.7520214858666668</v>
+      </c>
+      <c r="Q83">
+        <v>-0.4970214858666668</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5126325091736098</v>
+      </c>
+      <c r="T83">
+        <v>4.236899584797177</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05775418578303735</v>
+      </c>
+      <c r="W83">
+        <v>0.2250083004350107</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2887709289151867</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2816569000953445</v>
+      </c>
+      <c r="C84">
+        <v>-2.881861145957123</v>
+      </c>
+      <c r="D84">
+        <v>2.690198854042877</v>
+      </c>
+      <c r="E84">
+        <v>5.11006</v>
+      </c>
+      <c r="F84">
+        <v>5.60306</v>
+      </c>
+      <c r="G84">
+        <v>0.031</v>
+      </c>
+      <c r="H84">
+        <v>6.34</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K84">
+        <v>0.255</v>
+      </c>
+      <c r="L84">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M84">
+        <v>1.338010728</v>
+      </c>
+      <c r="N84">
+        <v>-0.9563440613333335</v>
+      </c>
+      <c r="O84">
+        <v>-0.1912688122666667</v>
+      </c>
+      <c r="P84">
+        <v>-0.7650752490666668</v>
+      </c>
+      <c r="Q84">
+        <v>-0.5100752490666668</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5389565374610326</v>
+      </c>
+      <c r="T84">
+        <v>4.472282895063687</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05704986644421983</v>
+      </c>
+      <c r="W84">
+        <v>0.2251764918931203</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2852493322210991</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2836569000953445</v>
+      </c>
+      <c r="C85">
+        <v>-2.972164787320674</v>
+      </c>
+      <c r="D85">
+        <v>2.668225212679326</v>
+      </c>
+      <c r="E85">
+        <v>5.17839</v>
+      </c>
+      <c r="F85">
+        <v>5.671390000000001</v>
+      </c>
+      <c r="G85">
+        <v>0.031</v>
+      </c>
+      <c r="H85">
+        <v>6.34</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K85">
+        <v>0.255</v>
+      </c>
+      <c r="L85">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M85">
+        <v>1.354327932</v>
+      </c>
+      <c r="N85">
+        <v>-0.9726612653333334</v>
+      </c>
+      <c r="O85">
+        <v>-0.1945322530666667</v>
+      </c>
+      <c r="P85">
+        <v>-0.7781290122666668</v>
+      </c>
+      <c r="Q85">
+        <v>-0.5231290122666667</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5683775102528581</v>
+      </c>
+      <c r="T85">
+        <v>4.735358359479198</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05636251865573525</v>
+      </c>
+      <c r="W85">
+        <v>0.2253406305450104</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2818125932786762</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2856569000953445</v>
+      </c>
+      <c r="C86">
+        <v>-3.062112373960129</v>
+      </c>
+      <c r="D86">
+        <v>2.646607626039871</v>
+      </c>
+      <c r="E86">
+        <v>5.24672</v>
+      </c>
+      <c r="F86">
+        <v>5.73972</v>
+      </c>
+      <c r="G86">
+        <v>0.031</v>
+      </c>
+      <c r="H86">
+        <v>6.34</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K86">
+        <v>0.255</v>
+      </c>
+      <c r="L86">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M86">
+        <v>1.370645136</v>
+      </c>
+      <c r="N86">
+        <v>-0.9889784693333333</v>
+      </c>
+      <c r="O86">
+        <v>-0.1977956938666667</v>
+      </c>
+      <c r="P86">
+        <v>-0.7911827754666667</v>
+      </c>
+      <c r="Q86">
+        <v>-0.5361827754666667</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6014761046436614</v>
+      </c>
+      <c r="T86">
+        <v>5.031318256946645</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05569153629078602</v>
+      </c>
+      <c r="W86">
+        <v>0.2255008611337603</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2784576814539301</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2876569000953445</v>
+      </c>
+      <c r="C87">
+        <v>-3.151712490440933</v>
+      </c>
+      <c r="D87">
+        <v>2.625337509559067</v>
+      </c>
+      <c r="E87">
+        <v>5.315049999999999</v>
+      </c>
+      <c r="F87">
+        <v>5.80805</v>
+      </c>
+      <c r="G87">
+        <v>0.031</v>
+      </c>
+      <c r="H87">
+        <v>6.34</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K87">
+        <v>0.255</v>
+      </c>
+      <c r="L87">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M87">
+        <v>1.38696234</v>
+      </c>
+      <c r="N87">
+        <v>-1.005295673333333</v>
+      </c>
+      <c r="O87">
+        <v>-0.2010591346666667</v>
+      </c>
+      <c r="P87">
+        <v>-0.8042365386666667</v>
+      </c>
+      <c r="Q87">
+        <v>-0.5492365386666667</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6389878449532389</v>
+      </c>
+      <c r="T87">
+        <v>5.366739474076422</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05503634174618854</v>
+      </c>
+      <c r="W87">
+        <v>0.2256573215910102</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2751817087309426</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2896569000953445</v>
+      </c>
+      <c r="C88">
+        <v>-3.240973447560799</v>
+      </c>
+      <c r="D88">
+        <v>2.604406552439201</v>
+      </c>
+      <c r="E88">
+        <v>5.38338</v>
+      </c>
+      <c r="F88">
+        <v>5.87638</v>
+      </c>
+      <c r="G88">
+        <v>0.031</v>
+      </c>
+      <c r="H88">
+        <v>6.34</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K88">
+        <v>0.255</v>
+      </c>
+      <c r="L88">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M88">
+        <v>1.403279544</v>
+      </c>
+      <c r="N88">
+        <v>-1.021612877333333</v>
+      </c>
+      <c r="O88">
+        <v>-0.2043225754666667</v>
+      </c>
+      <c r="P88">
+        <v>-0.8172903018666666</v>
+      </c>
+      <c r="Q88">
+        <v>-0.5622903018666666</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6818584053070416</v>
+      </c>
+      <c r="T88">
+        <v>5.750078007939024</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05439638428402355</v>
+      </c>
+      <c r="W88">
+        <v>0.2258101434329752</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2719819214201178</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2916569000953445</v>
+      </c>
+      <c r="C89">
+        <v>-3.329903293176696</v>
+      </c>
+      <c r="D89">
+        <v>2.583806706823304</v>
+      </c>
+      <c r="E89">
+        <v>5.451709999999999</v>
+      </c>
+      <c r="F89">
+        <v>5.94471</v>
+      </c>
+      <c r="G89">
+        <v>0.031</v>
+      </c>
+      <c r="H89">
+        <v>6.34</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K89">
+        <v>0.255</v>
+      </c>
+      <c r="L89">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M89">
+        <v>1.419596748</v>
+      </c>
+      <c r="N89">
+        <v>-1.037930081333333</v>
+      </c>
+      <c r="O89">
+        <v>-0.2075860162666666</v>
+      </c>
+      <c r="P89">
+        <v>-0.8303440650666666</v>
+      </c>
+      <c r="Q89">
+        <v>-0.5753440650666666</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7313244364845064</v>
+      </c>
+      <c r="T89">
+        <v>6.19239170085741</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05377113848765547</v>
+      </c>
+      <c r="W89">
+        <v>0.2259594521291479</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2688556924382774</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2936569000953445</v>
+      </c>
+      <c r="C90">
+        <v>-3.41850982252204</v>
+      </c>
+      <c r="D90">
+        <v>2.56353017747796</v>
+      </c>
+      <c r="E90">
+        <v>5.52004</v>
+      </c>
+      <c r="F90">
+        <v>6.01304</v>
+      </c>
+      <c r="G90">
+        <v>0.031</v>
+      </c>
+      <c r="H90">
+        <v>6.34</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K90">
+        <v>0.255</v>
+      </c>
+      <c r="L90">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M90">
+        <v>1.435913952</v>
+      </c>
+      <c r="N90">
+        <v>-1.054247285333334</v>
+      </c>
+      <c r="O90">
+        <v>-0.2108494570666667</v>
+      </c>
+      <c r="P90">
+        <v>-0.8433978282666669</v>
+      </c>
+      <c r="Q90">
+        <v>-0.5883978282666669</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7890348061915486</v>
+      </c>
+      <c r="T90">
+        <v>6.708424342595529</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05316010282302302</v>
+      </c>
+      <c r="W90">
+        <v>0.2261053674458621</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.265800514115115</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2956569000953445</v>
+      </c>
+      <c r="C91">
+        <v>-3.50680058804188</v>
+      </c>
+      <c r="D91">
+        <v>2.543569411958121</v>
+      </c>
+      <c r="E91">
+        <v>5.58837</v>
+      </c>
+      <c r="F91">
+        <v>6.081370000000001</v>
+      </c>
+      <c r="G91">
+        <v>0.031</v>
+      </c>
+      <c r="H91">
+        <v>6.34</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K91">
+        <v>0.255</v>
+      </c>
+      <c r="L91">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M91">
+        <v>1.452231156</v>
+      </c>
+      <c r="N91">
+        <v>-1.070564489333333</v>
+      </c>
+      <c r="O91">
+        <v>-0.2141128978666667</v>
+      </c>
+      <c r="P91">
+        <v>-0.8564515914666668</v>
+      </c>
+      <c r="Q91">
+        <v>-0.6014515914666668</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8572379703907804</v>
+      </c>
+      <c r="T91">
+        <v>7.318281101013304</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05256279829692163</v>
+      </c>
+      <c r="W91">
+        <v>0.2262480037666951</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2628139914846083</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2976569000953445</v>
+      </c>
+      <c r="C92">
+        <v>-3.594782908772146</v>
+      </c>
+      <c r="D92">
+        <v>2.523917091227854</v>
+      </c>
+      <c r="E92">
+        <v>5.6567</v>
+      </c>
+      <c r="F92">
+        <v>6.1497</v>
+      </c>
+      <c r="G92">
+        <v>0.031</v>
+      </c>
+      <c r="H92">
+        <v>6.34</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K92">
+        <v>0.255</v>
+      </c>
+      <c r="L92">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M92">
+        <v>1.46854836</v>
+      </c>
+      <c r="N92">
+        <v>-1.086881693333333</v>
+      </c>
+      <c r="O92">
+        <v>-0.2173763386666667</v>
+      </c>
+      <c r="P92">
+        <v>-0.8695053546666667</v>
+      </c>
+      <c r="Q92">
+        <v>-0.6145053546666667</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9390817674298586</v>
+      </c>
+      <c r="T92">
+        <v>8.050109211114636</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05197876720473361</v>
+      </c>
+      <c r="W92">
+        <v>0.2263874703915096</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2598938360236681</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2996569000953445</v>
+      </c>
+      <c r="C93">
+        <v>-3.68246387928744</v>
+      </c>
+      <c r="D93">
+        <v>2.504566120712561</v>
+      </c>
+      <c r="E93">
+        <v>5.72503</v>
+      </c>
+      <c r="F93">
+        <v>6.218030000000001</v>
+      </c>
+      <c r="G93">
+        <v>0.031</v>
+      </c>
+      <c r="H93">
+        <v>6.34</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K93">
+        <v>0.255</v>
+      </c>
+      <c r="L93">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M93">
+        <v>1.484865564</v>
+      </c>
+      <c r="N93">
+        <v>-1.103198897333333</v>
+      </c>
+      <c r="O93">
+        <v>-0.2206397794666667</v>
+      </c>
+      <c r="P93">
+        <v>-0.8825591178666666</v>
+      </c>
+      <c r="Q93">
+        <v>-0.6275591178666666</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.039113074922065</v>
+      </c>
+      <c r="T93">
+        <v>8.944565790127374</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05140757196072555</v>
+      </c>
+      <c r="W93">
+        <v>0.2265238718157788</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2570378598036278</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3016569000953445</v>
+      </c>
+      <c r="C94">
+        <v>-3.769850378240322</v>
+      </c>
+      <c r="D94">
+        <v>2.485509621759678</v>
+      </c>
+      <c r="E94">
+        <v>5.79336</v>
+      </c>
+      <c r="F94">
+        <v>6.28636</v>
+      </c>
+      <c r="G94">
+        <v>0.031</v>
+      </c>
+      <c r="H94">
+        <v>6.34</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K94">
+        <v>0.255</v>
+      </c>
+      <c r="L94">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M94">
+        <v>1.501182768</v>
+      </c>
+      <c r="N94">
+        <v>-1.119516101333333</v>
+      </c>
+      <c r="O94">
+        <v>-0.2239032202666666</v>
+      </c>
+      <c r="P94">
+        <v>-0.8956128810666666</v>
+      </c>
+      <c r="Q94">
+        <v>-0.6406128810666666</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.164152209287323</v>
+      </c>
+      <c r="T94">
+        <v>10.0626365138933</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05084879400463072</v>
+      </c>
+      <c r="W94">
+        <v>0.2266573079916942</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2542439700231537</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3036569000953445</v>
+      </c>
+      <c r="C95">
+        <v>-3.856949076513729</v>
+      </c>
+      <c r="D95">
+        <v>2.466740923486271</v>
+      </c>
+      <c r="E95">
+        <v>5.86169</v>
+      </c>
+      <c r="F95">
+        <v>6.354690000000001</v>
+      </c>
+      <c r="G95">
+        <v>0.031</v>
+      </c>
+      <c r="H95">
+        <v>6.34</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K95">
+        <v>0.255</v>
+      </c>
+      <c r="L95">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M95">
+        <v>1.517499972</v>
+      </c>
+      <c r="N95">
+        <v>-1.135833305333334</v>
+      </c>
+      <c r="O95">
+        <v>-0.2271666610666667</v>
+      </c>
+      <c r="P95">
+        <v>-0.9086666442666669</v>
+      </c>
+      <c r="Q95">
+        <v>-0.6536666442666669</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.324916810614084</v>
+      </c>
+      <c r="T95">
+        <v>11.50015601587806</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05030203277877447</v>
+      </c>
+      <c r="W95">
+        <v>0.2267878745724287</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2515101638938723</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3056569000953445</v>
+      </c>
+      <c r="C96">
+        <v>-3.943766445006767</v>
+      </c>
+      <c r="D96">
+        <v>2.448253554993233</v>
+      </c>
+      <c r="E96">
+        <v>5.93002</v>
+      </c>
+      <c r="F96">
+        <v>6.42302</v>
+      </c>
+      <c r="G96">
+        <v>0.031</v>
+      </c>
+      <c r="H96">
+        <v>6.34</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K96">
+        <v>0.255</v>
+      </c>
+      <c r="L96">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M96">
+        <v>1.533817176</v>
+      </c>
+      <c r="N96">
+        <v>-1.152150509333334</v>
+      </c>
+      <c r="O96">
+        <v>-0.2304301018666667</v>
+      </c>
+      <c r="P96">
+        <v>-0.9217204074666668</v>
+      </c>
+      <c r="Q96">
+        <v>-0.6667204074666668</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.539269612383099</v>
+      </c>
+      <c r="T96">
+        <v>13.41684868519107</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04976690477048964</v>
+      </c>
+      <c r="W96">
+        <v>0.2269156631408071</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2488345238524481</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3076569000953445</v>
+      </c>
+      <c r="C97">
+        <v>-4.030308762073021</v>
+      </c>
+      <c r="D97">
+        <v>2.430041237926979</v>
+      </c>
+      <c r="E97">
+        <v>5.99835</v>
+      </c>
+      <c r="F97">
+        <v>6.491350000000001</v>
+      </c>
+      <c r="G97">
+        <v>0.031</v>
+      </c>
+      <c r="H97">
+        <v>6.34</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K97">
+        <v>0.255</v>
+      </c>
+      <c r="L97">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M97">
+        <v>1.55013438</v>
+      </c>
+      <c r="N97">
+        <v>-1.168467713333333</v>
+      </c>
+      <c r="O97">
+        <v>-0.2336935426666667</v>
+      </c>
+      <c r="P97">
+        <v>-0.9347741706666668</v>
+      </c>
+      <c r="Q97">
+        <v>-0.6797741706666668</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.839363534859719</v>
+      </c>
+      <c r="T97">
+        <v>16.10021842222929</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04924304261501079</v>
+      </c>
+      <c r="W97">
+        <v>0.2270407614235354</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.246215213075054</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3096569000953445</v>
+      </c>
+      <c r="C98">
+        <v>-4.116582120629303</v>
+      </c>
+      <c r="D98">
+        <v>2.412097879370696</v>
+      </c>
+      <c r="E98">
+        <v>6.06668</v>
+      </c>
+      <c r="F98">
+        <v>6.55968</v>
+      </c>
+      <c r="G98">
+        <v>0.031</v>
+      </c>
+      <c r="H98">
+        <v>6.34</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K98">
+        <v>0.255</v>
+      </c>
+      <c r="L98">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M98">
+        <v>1.566451584</v>
+      </c>
+      <c r="N98">
+        <v>-1.184784917333333</v>
+      </c>
+      <c r="O98">
+        <v>-0.2369569834666667</v>
+      </c>
+      <c r="P98">
+        <v>-0.9478279338666666</v>
+      </c>
+      <c r="Q98">
+        <v>-0.6928279338666666</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.289504418574644</v>
+      </c>
+      <c r="T98">
+        <v>20.12527302778657</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04873009425443776</v>
+      </c>
+      <c r="W98">
+        <v>0.2271632534920403</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2436504712721889</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3116569000953445</v>
+      </c>
+      <c r="C99">
+        <v>-4.202592434951776</v>
+      </c>
+      <c r="D99">
+        <v>2.394417565048224</v>
+      </c>
+      <c r="E99">
+        <v>6.135009999999999</v>
+      </c>
+      <c r="F99">
+        <v>6.62801</v>
+      </c>
+      <c r="G99">
+        <v>0.031</v>
+      </c>
+      <c r="H99">
+        <v>6.34</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K99">
+        <v>0.255</v>
+      </c>
+      <c r="L99">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M99">
+        <v>1.582768788</v>
+      </c>
+      <c r="N99">
+        <v>-1.201102121333333</v>
+      </c>
+      <c r="O99">
+        <v>-0.2402204242666667</v>
+      </c>
+      <c r="P99">
+        <v>-0.9608816970666666</v>
+      </c>
+      <c r="Q99">
+        <v>-0.7058816970666666</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.039739224766192</v>
+      </c>
+      <c r="T99">
+        <v>26.83369737038209</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04822772214872192</v>
+      </c>
+      <c r="W99">
+        <v>0.2272832199508852</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2411386107436096</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3136569000953445</v>
+      </c>
+      <c r="C100">
+        <v>-4.288345447175357</v>
+      </c>
+      <c r="D100">
+        <v>2.376994552824643</v>
+      </c>
+      <c r="E100">
+        <v>6.20334</v>
+      </c>
+      <c r="F100">
+        <v>6.69634</v>
+      </c>
+      <c r="G100">
+        <v>0.031</v>
+      </c>
+      <c r="H100">
+        <v>6.34</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K100">
+        <v>0.255</v>
+      </c>
+      <c r="L100">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M100">
+        <v>1.599085992</v>
+      </c>
+      <c r="N100">
+        <v>-1.217419325333334</v>
+      </c>
+      <c r="O100">
+        <v>-0.2434838650666667</v>
+      </c>
+      <c r="P100">
+        <v>-0.9739354602666669</v>
+      </c>
+      <c r="Q100">
+        <v>-0.7189354602666669</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.540208837149288</v>
+      </c>
+      <c r="T100">
+        <v>40.25054605557314</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04773560253495945</v>
+      </c>
+      <c r="W100">
+        <v>0.2274007381146517</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2386780126747972</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3156569000953445</v>
+      </c>
+      <c r="C101">
+        <v>-4.373846733511408</v>
+      </c>
+      <c r="D101">
+        <v>2.359823266488591</v>
+      </c>
+      <c r="E101">
+        <v>6.271669999999999</v>
+      </c>
+      <c r="F101">
+        <v>6.76467</v>
+      </c>
+      <c r="G101">
+        <v>0.031</v>
+      </c>
+      <c r="H101">
+        <v>6.34</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="K101">
+        <v>0.255</v>
+      </c>
+      <c r="L101">
+        <v>0.3816666666666667</v>
+      </c>
+      <c r="M101">
+        <v>1.615403196</v>
+      </c>
+      <c r="N101">
+        <v>-1.233736529333333</v>
+      </c>
+      <c r="O101">
+        <v>-0.2467473058666666</v>
+      </c>
+      <c r="P101">
+        <v>-0.9869892234666665</v>
+      </c>
+      <c r="Q101">
+        <v>-0.7319892234666665</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.041617674298577</v>
+      </c>
+      <c r="T101">
+        <v>80.50109211114628</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04725342473157602</v>
+      </c>
+      <c r="W101">
+        <v>0.2275158821740997</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2362671236578802</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jordan/jordan_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_restaurant_dining.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1229220662789319</v>
+        <v>0.122712222146374</v>
       </c>
       <c r="C2">
-        <v>8.629566572411873</v>
+        <v>8.567295597292278</v>
       </c>
       <c r="D2">
-        <v>8.561566572411873</v>
+        <v>8.584925597292278</v>
       </c>
       <c r="E2">
-        <v>-0.383</v>
+        <v>-0.29737</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.08562999999999998</v>
       </c>
       <c r="G2">
         <v>0.068</v>
@@ -1445,28 +1445,28 @@
         <v>0.651</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.004307188999999999</v>
       </c>
       <c r="N2">
-        <v>0.651</v>
+        <v>0.646692811</v>
       </c>
       <c r="O2">
-        <v>0.1302</v>
+        <v>0.1293385622</v>
       </c>
       <c r="P2">
-        <v>0.5208</v>
+        <v>0.5173542488</v>
       </c>
       <c r="Q2">
-        <v>0.6538</v>
+        <v>0.6503542488</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1229220662789319</v>
+        <v>0.1235452748953273</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326223</v>
+        <v>0.8513426260203607</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>151.1426594003653</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.122712222146374</v>
+        <v>0.1225023780138162</v>
       </c>
       <c r="C3">
-        <v>8.567295597292278</v>
+        <v>8.505152434489334</v>
       </c>
       <c r="D3">
-        <v>8.584925597292278</v>
+        <v>8.608412434489335</v>
       </c>
       <c r="E3">
-        <v>-0.29737</v>
+        <v>-0.21174</v>
       </c>
       <c r="F3">
-        <v>0.08562999999999998</v>
+        <v>0.17126</v>
       </c>
       <c r="G3">
         <v>0.068</v>
@@ -1527,28 +1527,28 @@
         <v>0.651</v>
       </c>
       <c r="M3">
-        <v>0.004307188999999999</v>
+        <v>0.008614377999999997</v>
       </c>
       <c r="N3">
-        <v>0.646692811</v>
+        <v>0.642385622</v>
       </c>
       <c r="O3">
-        <v>0.1293385622</v>
+        <v>0.1284771244</v>
       </c>
       <c r="P3">
-        <v>0.5173542488</v>
+        <v>0.5139084976</v>
       </c>
       <c r="Q3">
-        <v>0.6503542488</v>
+        <v>0.6469084976</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1235452748953273</v>
+        <v>0.1241812020549145</v>
       </c>
       <c r="T3">
-        <v>0.8513426260203607</v>
+        <v>0.8583062890690732</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>151.1426594003653</v>
+        <v>75.57132970018267</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1225023780138162</v>
+        <v>0.1222925338812583</v>
       </c>
       <c r="C4">
-        <v>8.505152434489334</v>
+        <v>8.443138135896477</v>
       </c>
       <c r="D4">
-        <v>8.608412434489335</v>
+        <v>8.632028135896478</v>
       </c>
       <c r="E4">
-        <v>-0.21174</v>
+        <v>-0.1261100000000001</v>
       </c>
       <c r="F4">
-        <v>0.17126</v>
+        <v>0.25689</v>
       </c>
       <c r="G4">
         <v>0.068</v>
@@ -1609,28 +1609,28 @@
         <v>0.651</v>
       </c>
       <c r="M4">
-        <v>0.008614377999999997</v>
+        <v>0.012921567</v>
       </c>
       <c r="N4">
-        <v>0.642385622</v>
+        <v>0.638078433</v>
       </c>
       <c r="O4">
-        <v>0.1284771244</v>
+        <v>0.1276156866</v>
       </c>
       <c r="P4">
-        <v>0.5139084976</v>
+        <v>0.5104627464</v>
       </c>
       <c r="Q4">
-        <v>0.6469084976</v>
+        <v>0.6434627464</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1241812020549145</v>
+        <v>0.1248302411146993</v>
       </c>
       <c r="T4">
-        <v>0.8583062890690732</v>
+        <v>0.8654135327992026</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.57132970018267</v>
+        <v>50.38088646678845</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1222925338812583</v>
+        <v>0.1220826897487005</v>
       </c>
       <c r="C5">
-        <v>8.443138135896477</v>
+        <v>8.381253764981654</v>
       </c>
       <c r="D5">
-        <v>8.632028135896478</v>
+        <v>8.655773764981655</v>
       </c>
       <c r="E5">
-        <v>-0.1261100000000001</v>
+        <v>-0.04048000000000007</v>
       </c>
       <c r="F5">
-        <v>0.25689</v>
+        <v>0.3425199999999999</v>
       </c>
       <c r="G5">
         <v>0.068</v>
@@ -1691,28 +1691,28 @@
         <v>0.651</v>
       </c>
       <c r="M5">
-        <v>0.012921567</v>
+        <v>0.01722875599999999</v>
       </c>
       <c r="N5">
-        <v>0.638078433</v>
+        <v>0.6337712440000001</v>
       </c>
       <c r="O5">
-        <v>0.1276156866</v>
+        <v>0.1267542488</v>
       </c>
       <c r="P5">
-        <v>0.5104627464</v>
+        <v>0.5070169952000001</v>
       </c>
       <c r="Q5">
-        <v>0.6434627464</v>
+        <v>0.6400169952000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1248302411146993</v>
+        <v>0.125492801821563</v>
       </c>
       <c r="T5">
-        <v>0.8654135327992026</v>
+        <v>0.8726688441070432</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.38088646678845</v>
+        <v>37.78566485009134</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1220826897487005</v>
+        <v>0.1218728456161426</v>
       </c>
       <c r="C6">
-        <v>8.381253764981654</v>
+        <v>8.319500396946955</v>
       </c>
       <c r="D6">
-        <v>8.655773764981655</v>
+        <v>8.679650396946956</v>
       </c>
       <c r="E6">
-        <v>-0.04048000000000007</v>
+        <v>0.04514999999999997</v>
       </c>
       <c r="F6">
-        <v>0.3425199999999999</v>
+        <v>0.42815</v>
       </c>
       <c r="G6">
         <v>0.068</v>
@@ -1773,28 +1773,28 @@
         <v>0.651</v>
       </c>
       <c r="M6">
-        <v>0.01722875599999999</v>
+        <v>0.021535945</v>
       </c>
       <c r="N6">
-        <v>0.6337712440000001</v>
+        <v>0.629464055</v>
       </c>
       <c r="O6">
-        <v>0.1267542488</v>
+        <v>0.125892811</v>
       </c>
       <c r="P6">
-        <v>0.5070169952000001</v>
+        <v>0.503571244</v>
       </c>
       <c r="Q6">
-        <v>0.6400169952000001</v>
+        <v>0.636571244</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.125492801821563</v>
+        <v>0.1261693111748869</v>
       </c>
       <c r="T6">
-        <v>0.8726688441070432</v>
+        <v>0.8800768988108379</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.78566485009134</v>
+        <v>30.22853188007306</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1218728456161426</v>
+        <v>0.1216630014835847</v>
       </c>
       <c r="C7">
-        <v>8.319500396946955</v>
+        <v>8.257879118890905</v>
       </c>
       <c r="D7">
-        <v>8.679650396946956</v>
+        <v>8.703659118890906</v>
       </c>
       <c r="E7">
-        <v>0.04514999999999997</v>
+        <v>0.13078</v>
       </c>
       <c r="F7">
-        <v>0.42815</v>
+        <v>0.51378</v>
       </c>
       <c r="G7">
         <v>0.068</v>
@@ -1855,28 +1855,28 @@
         <v>0.651</v>
       </c>
       <c r="M7">
-        <v>0.021535945</v>
+        <v>0.025843134</v>
       </c>
       <c r="N7">
-        <v>0.629464055</v>
+        <v>0.625156866</v>
       </c>
       <c r="O7">
-        <v>0.125892811</v>
+        <v>0.1250313732</v>
       </c>
       <c r="P7">
-        <v>0.503571244</v>
+        <v>0.5001254928</v>
       </c>
       <c r="Q7">
-        <v>0.636571244</v>
+        <v>0.6331254928</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1261693111748869</v>
+        <v>0.1268602143442391</v>
       </c>
       <c r="T7">
-        <v>0.8800768988108379</v>
+        <v>0.8876425716998202</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.22853188007306</v>
+        <v>25.19044323339422</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1216630014835847</v>
+        <v>0.1214531573510269</v>
       </c>
       <c r="C8">
-        <v>8.257879118890905</v>
+        <v>8.196391029973459</v>
       </c>
       <c r="D8">
-        <v>8.703659118890906</v>
+        <v>8.72780102997346</v>
       </c>
       <c r="E8">
-        <v>0.1307799999999999</v>
+        <v>0.2164099999999999</v>
       </c>
       <c r="F8">
-        <v>0.5137799999999999</v>
+        <v>0.5994099999999999</v>
       </c>
       <c r="G8">
         <v>0.068</v>
@@ -1937,28 +1937,28 @@
         <v>0.651</v>
       </c>
       <c r="M8">
-        <v>0.02584313399999999</v>
+        <v>0.03015032299999999</v>
       </c>
       <c r="N8">
-        <v>0.625156866</v>
+        <v>0.620849677</v>
       </c>
       <c r="O8">
-        <v>0.1250313732</v>
+        <v>0.1241699354</v>
       </c>
       <c r="P8">
-        <v>0.5001254928</v>
+        <v>0.4966797416000001</v>
       </c>
       <c r="Q8">
-        <v>0.6331254928</v>
+        <v>0.6296797416000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1268602143442391</v>
+        <v>0.1275659756462654</v>
       </c>
       <c r="T8">
-        <v>0.8876425716998202</v>
+        <v>0.8953709472315761</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.19044323339422</v>
+        <v>21.59180848576648</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1214531573510268</v>
+        <v>0.121243313218469</v>
       </c>
       <c r="C9">
-        <v>8.19639102997346</v>
+        <v>8.135037241583742</v>
       </c>
       <c r="D9">
-        <v>8.727801029973461</v>
+        <v>8.752077241583743</v>
       </c>
       <c r="E9">
-        <v>0.21641</v>
+        <v>0.3020399999999999</v>
       </c>
       <c r="F9">
-        <v>0.59941</v>
+        <v>0.6850399999999999</v>
       </c>
       <c r="G9">
         <v>0.068</v>
@@ -2019,28 +2019,28 @@
         <v>0.651</v>
       </c>
       <c r="M9">
-        <v>0.030150323</v>
+        <v>0.03445751199999999</v>
       </c>
       <c r="N9">
-        <v>0.620849677</v>
+        <v>0.616542488</v>
       </c>
       <c r="O9">
-        <v>0.1241699354</v>
+        <v>0.1233084976</v>
       </c>
       <c r="P9">
-        <v>0.4966797416000001</v>
+        <v>0.4932339904</v>
       </c>
       <c r="Q9">
-        <v>0.6296797416000001</v>
+        <v>0.6262339904000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1275659756462654</v>
+        <v>0.1282870795852924</v>
       </c>
       <c r="T9">
-        <v>0.8953709472315761</v>
+        <v>0.9032673309270657</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.59180848576647</v>
+        <v>18.89283242504567</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.121243313218469</v>
+        <v>0.1210334690859111</v>
       </c>
       <c r="C10">
-        <v>8.135037241583742</v>
+        <v>8.0738188775106</v>
       </c>
       <c r="D10">
-        <v>8.752077241583743</v>
+        <v>8.7764888775106</v>
       </c>
       <c r="E10">
-        <v>0.3020399999999999</v>
+        <v>0.3876699999999998</v>
       </c>
       <c r="F10">
-        <v>0.6850399999999999</v>
+        <v>0.7706699999999999</v>
       </c>
       <c r="G10">
         <v>0.068</v>
@@ -2101,28 +2101,28 @@
         <v>0.651</v>
       </c>
       <c r="M10">
-        <v>0.03445751199999999</v>
+        <v>0.03876470099999999</v>
       </c>
       <c r="N10">
-        <v>0.616542488</v>
+        <v>0.6122352990000001</v>
       </c>
       <c r="O10">
-        <v>0.1233084976</v>
+        <v>0.1224470598</v>
       </c>
       <c r="P10">
-        <v>0.4932339904</v>
+        <v>0.4897882392</v>
       </c>
       <c r="Q10">
-        <v>0.6262339904000001</v>
+        <v>0.6227882392</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1282870795852924</v>
+        <v>0.1290240319625397</v>
       </c>
       <c r="T10">
-        <v>0.9032673309270657</v>
+        <v>0.9113372615169616</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.89283242504567</v>
+        <v>16.79362882226282</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1210334690859111</v>
+        <v>0.1208236249533533</v>
       </c>
       <c r="C11">
-        <v>8.0738188775106</v>
+        <v>8.012737074116002</v>
       </c>
       <c r="D11">
-        <v>8.7764888775106</v>
+        <v>8.801037074116001</v>
       </c>
       <c r="E11">
-        <v>0.3876699999999998</v>
+        <v>0.4732999999999998</v>
       </c>
       <c r="F11">
-        <v>0.7706699999999999</v>
+        <v>0.8562999999999998</v>
       </c>
       <c r="G11">
         <v>0.068</v>
@@ -2183,28 +2183,28 @@
         <v>0.651</v>
       </c>
       <c r="M11">
-        <v>0.03876470099999999</v>
+        <v>0.04307188999999999</v>
       </c>
       <c r="N11">
-        <v>0.6122352990000001</v>
+        <v>0.60792811</v>
       </c>
       <c r="O11">
-        <v>0.1224470598</v>
+        <v>0.121585622</v>
       </c>
       <c r="P11">
-        <v>0.4897882392</v>
+        <v>0.486342488</v>
       </c>
       <c r="Q11">
-        <v>0.6227882392</v>
+        <v>0.619342488</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1290240319625397</v>
+        <v>0.1297773610592814</v>
       </c>
       <c r="T11">
-        <v>0.9113372615169616</v>
+        <v>0.9195865238977442</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.79362882226282</v>
+        <v>15.11426594003653</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1208236249533533</v>
+        <v>0.1206137808207954</v>
       </c>
       <c r="C12">
-        <v>8.012737074116002</v>
+        <v>7.951792980511393</v>
       </c>
       <c r="D12">
-        <v>8.801037074116001</v>
+        <v>8.825722980511394</v>
       </c>
       <c r="E12">
-        <v>0.4732999999999999</v>
+        <v>0.5589299999999998</v>
       </c>
       <c r="F12">
-        <v>0.8563</v>
+        <v>0.9419299999999998</v>
       </c>
       <c r="G12">
         <v>0.068</v>
@@ -2265,28 +2265,28 @@
         <v>0.651</v>
       </c>
       <c r="M12">
-        <v>0.04307188999999999</v>
+        <v>0.04737907899999999</v>
       </c>
       <c r="N12">
-        <v>0.60792811</v>
+        <v>0.6036209210000001</v>
       </c>
       <c r="O12">
-        <v>0.121585622</v>
+        <v>0.1207241842</v>
       </c>
       <c r="P12">
-        <v>0.486342488</v>
+        <v>0.4828967368000001</v>
       </c>
       <c r="Q12">
-        <v>0.619342488</v>
+        <v>0.6158967368000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1297773610592814</v>
+        <v>0.1305476188997701</v>
       </c>
       <c r="T12">
-        <v>0.9195865238977444</v>
+        <v>0.9280211629612412</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.11426594003653</v>
+        <v>13.74024176366958</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1206137808207954</v>
+        <v>0.1205479366882375</v>
       </c>
       <c r="C13">
-        <v>7.951792980511393</v>
+        <v>7.873937403453279</v>
       </c>
       <c r="D13">
-        <v>8.825722980511394</v>
+        <v>8.833497403453279</v>
       </c>
       <c r="E13">
-        <v>0.5589299999999998</v>
+        <v>0.6445599999999998</v>
       </c>
       <c r="F13">
-        <v>0.9419299999999998</v>
+        <v>1.02756</v>
       </c>
       <c r="G13">
         <v>0.068</v>
@@ -2347,45 +2347,45 @@
         <v>0.651</v>
       </c>
       <c r="M13">
-        <v>0.04737907899999999</v>
+        <v>0.05322760799999999</v>
       </c>
       <c r="N13">
-        <v>0.6036209210000001</v>
+        <v>0.597772392</v>
       </c>
       <c r="O13">
-        <v>0.1207241842</v>
+        <v>0.1195544784</v>
       </c>
       <c r="P13">
-        <v>0.4828967368000001</v>
+        <v>0.4782179136</v>
       </c>
       <c r="Q13">
-        <v>0.6158967368000001</v>
+        <v>0.6112179136</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1305476188997701</v>
+        <v>0.1313353826002699</v>
       </c>
       <c r="T13">
-        <v>0.9280211629612412</v>
+        <v>0.9366474983670903</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.74024176366958</v>
+        <v>12.23049512200511</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1205479366882375</v>
+        <v>0.1203500925556796</v>
       </c>
       <c r="C14">
-        <v>7.873937403453279</v>
+        <v>7.811750105820595</v>
       </c>
       <c r="D14">
-        <v>8.833497403453279</v>
+        <v>8.856940105820595</v>
       </c>
       <c r="E14">
-        <v>0.6445599999999998</v>
+        <v>0.7301899999999999</v>
       </c>
       <c r="F14">
-        <v>1.02756</v>
+        <v>1.11319</v>
       </c>
       <c r="G14">
         <v>0.068</v>
@@ -2429,28 +2429,28 @@
         <v>0.651</v>
       </c>
       <c r="M14">
-        <v>0.05322760799999999</v>
+        <v>0.057663242</v>
       </c>
       <c r="N14">
-        <v>0.597772392</v>
+        <v>0.5933367580000001</v>
       </c>
       <c r="O14">
-        <v>0.1195544784</v>
+        <v>0.1186673516</v>
       </c>
       <c r="P14">
-        <v>0.4782179136</v>
+        <v>0.4746694064</v>
       </c>
       <c r="Q14">
-        <v>0.6112179136</v>
+        <v>0.6076694064000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1313353826002699</v>
+        <v>0.132141255811126</v>
       </c>
       <c r="T14">
-        <v>0.9366474983670903</v>
+        <v>0.9454721403339933</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.23049512200511</v>
+        <v>11.28968780492779</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1203500925556796</v>
+        <v>0.1201522484231218</v>
       </c>
       <c r="C15">
-        <v>7.811750105820595</v>
+        <v>7.74968756570938</v>
       </c>
       <c r="D15">
-        <v>8.856940105820595</v>
+        <v>8.880507565709379</v>
       </c>
       <c r="E15">
-        <v>0.7301899999999999</v>
+        <v>0.81582</v>
       </c>
       <c r="F15">
-        <v>1.11319</v>
+        <v>1.19882</v>
       </c>
       <c r="G15">
         <v>0.068</v>
@@ -2511,28 +2511,28 @@
         <v>0.651</v>
       </c>
       <c r="M15">
-        <v>0.057663242</v>
+        <v>0.062098876</v>
       </c>
       <c r="N15">
-        <v>0.5933367580000001</v>
+        <v>0.5889011240000001</v>
       </c>
       <c r="O15">
-        <v>0.1186673516</v>
+        <v>0.1177802248</v>
       </c>
       <c r="P15">
-        <v>0.4746694064</v>
+        <v>0.4711208992000001</v>
       </c>
       <c r="Q15">
-        <v>0.6076694064000001</v>
+        <v>0.6041208992</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.132141255811126</v>
+        <v>0.132965870259444</v>
       </c>
       <c r="T15">
-        <v>0.9454721403339933</v>
+        <v>0.9545020065326848</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.28968780492779</v>
+        <v>10.48328153314724</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1201522484231218</v>
+        <v>0.1201584042905639</v>
       </c>
       <c r="C16">
-        <v>7.74968756570938</v>
+        <v>7.663322380118524</v>
       </c>
       <c r="D16">
-        <v>8.880507565709379</v>
+        <v>8.879772380118524</v>
       </c>
       <c r="E16">
-        <v>0.81582</v>
+        <v>0.9014500000000001</v>
       </c>
       <c r="F16">
-        <v>1.19882</v>
+        <v>1.28445</v>
       </c>
       <c r="G16">
         <v>0.068</v>
@@ -2593,45 +2593,45 @@
         <v>0.651</v>
       </c>
       <c r="M16">
-        <v>0.062098876</v>
+        <v>0.068718075</v>
       </c>
       <c r="N16">
-        <v>0.5889011240000001</v>
+        <v>0.582281925</v>
       </c>
       <c r="O16">
-        <v>0.1177802248</v>
+        <v>0.116456385</v>
       </c>
       <c r="P16">
-        <v>0.4711208992000001</v>
+        <v>0.46582554</v>
       </c>
       <c r="Q16">
-        <v>0.6041208992</v>
+        <v>0.59882554</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.132965870259444</v>
+        <v>0.1338098874006635</v>
       </c>
       <c r="T16">
-        <v>0.9545020065326848</v>
+        <v>0.9637443401713455</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.48328153314724</v>
+        <v>9.473490053381152</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1201584042905639</v>
+        <v>0.1199741601580061</v>
       </c>
       <c r="C17">
-        <v>7.663322380118524</v>
+        <v>7.599749198234173</v>
       </c>
       <c r="D17">
-        <v>8.879772380118524</v>
+        <v>8.901829198234173</v>
       </c>
       <c r="E17">
-        <v>0.9014499999999999</v>
+        <v>0.9870799999999997</v>
       </c>
       <c r="F17">
-        <v>1.28445</v>
+        <v>1.37008</v>
       </c>
       <c r="G17">
         <v>0.068</v>
@@ -2675,28 +2675,28 @@
         <v>0.651</v>
       </c>
       <c r="M17">
-        <v>0.06871807499999999</v>
+        <v>0.07329927999999998</v>
       </c>
       <c r="N17">
-        <v>0.582281925</v>
+        <v>0.5777007200000001</v>
       </c>
       <c r="O17">
-        <v>0.116456385</v>
+        <v>0.115540144</v>
       </c>
       <c r="P17">
-        <v>0.46582554</v>
+        <v>0.462160576</v>
       </c>
       <c r="Q17">
-        <v>0.59882554</v>
+        <v>0.5951605760000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1338098874006635</v>
+        <v>0.1346740001881025</v>
       </c>
       <c r="T17">
-        <v>0.9637443401713455</v>
+        <v>0.9732067293728314</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.473490053381154</v>
+        <v>8.881396925044832</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1199741601580061</v>
+        <v>0.1197899160254482</v>
       </c>
       <c r="C18">
-        <v>7.599749198234173</v>
+        <v>7.536285864814019</v>
       </c>
       <c r="D18">
-        <v>8.901829198234173</v>
+        <v>8.923995864814019</v>
       </c>
       <c r="E18">
-        <v>0.9870799999999997</v>
+        <v>1.07271</v>
       </c>
       <c r="F18">
-        <v>1.37008</v>
+        <v>1.45571</v>
       </c>
       <c r="G18">
         <v>0.068</v>
@@ -2757,28 +2757,28 @@
         <v>0.651</v>
       </c>
       <c r="M18">
-        <v>0.07329927999999998</v>
+        <v>0.07788048499999999</v>
       </c>
       <c r="N18">
-        <v>0.5777007200000001</v>
+        <v>0.573119515</v>
       </c>
       <c r="O18">
-        <v>0.115540144</v>
+        <v>0.114623903</v>
       </c>
       <c r="P18">
-        <v>0.462160576</v>
+        <v>0.458495612</v>
       </c>
       <c r="Q18">
-        <v>0.5951605760000001</v>
+        <v>0.591495612</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1346740001881025</v>
+        <v>0.1355589349704195</v>
       </c>
       <c r="T18">
-        <v>0.9732067293728314</v>
+        <v>0.9828971279526665</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.881396925044832</v>
+        <v>8.3589618118069</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1197899160254482</v>
+        <v>0.1196056718928903</v>
       </c>
       <c r="C19">
-        <v>7.536285864814019</v>
+        <v>7.472933202515772</v>
       </c>
       <c r="D19">
-        <v>8.923995864814019</v>
+        <v>8.946273202515773</v>
       </c>
       <c r="E19">
-        <v>1.07271</v>
+        <v>1.15834</v>
       </c>
       <c r="F19">
-        <v>1.45571</v>
+        <v>1.54134</v>
       </c>
       <c r="G19">
         <v>0.068</v>
@@ -2839,28 +2839,28 @@
         <v>0.651</v>
       </c>
       <c r="M19">
-        <v>0.07788048499999999</v>
+        <v>0.08246168999999999</v>
       </c>
       <c r="N19">
-        <v>0.573119515</v>
+        <v>0.56853831</v>
       </c>
       <c r="O19">
-        <v>0.114623903</v>
+        <v>0.113707662</v>
       </c>
       <c r="P19">
-        <v>0.458495612</v>
+        <v>0.454830648</v>
       </c>
       <c r="Q19">
-        <v>0.591495612</v>
+        <v>0.587830648</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1355589349704195</v>
+        <v>0.1364654535279151</v>
       </c>
       <c r="T19">
-        <v>0.9828971279526665</v>
+        <v>0.9928238777173757</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.3589618118069</v>
+        <v>7.894575044484294</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1196056718928904</v>
+        <v>0.1195430277603325</v>
       </c>
       <c r="C20">
-        <v>7.472933202515771</v>
+        <v>7.394902992508372</v>
       </c>
       <c r="D20">
-        <v>8.946273202515771</v>
+        <v>8.953872992508373</v>
       </c>
       <c r="E20">
-        <v>1.15834</v>
+        <v>1.24397</v>
       </c>
       <c r="F20">
-        <v>1.54134</v>
+        <v>1.62697</v>
       </c>
       <c r="G20">
         <v>0.068</v>
@@ -2921,45 +2921,45 @@
         <v>0.651</v>
       </c>
       <c r="M20">
-        <v>0.08246168999999998</v>
+        <v>0.08834447099999999</v>
       </c>
       <c r="N20">
-        <v>0.5685383100000001</v>
+        <v>0.562655529</v>
       </c>
       <c r="O20">
-        <v>0.113707662</v>
+        <v>0.1125311058</v>
       </c>
       <c r="P20">
-        <v>0.4548306480000001</v>
+        <v>0.4501244232</v>
       </c>
       <c r="Q20">
-        <v>0.5878306480000001</v>
+        <v>0.5831244232</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1364654535279151</v>
+        <v>0.1373943552596698</v>
       </c>
       <c r="T20">
-        <v>0.9928238777173755</v>
+        <v>1.002995732414547</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.894575044484297</v>
+        <v>7.368882202033901</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1195430277603325</v>
+        <v>0.1193651836277746</v>
       </c>
       <c r="C21">
-        <v>7.394902992508372</v>
+        <v>7.330919017120276</v>
       </c>
       <c r="D21">
-        <v>8.953872992508373</v>
+        <v>8.975519017120277</v>
       </c>
       <c r="E21">
-        <v>1.24397</v>
+        <v>1.3296</v>
       </c>
       <c r="F21">
-        <v>1.62697</v>
+        <v>1.7126</v>
       </c>
       <c r="G21">
         <v>0.068</v>
@@ -3003,28 +3003,28 @@
         <v>0.651</v>
       </c>
       <c r="M21">
-        <v>0.08834447099999999</v>
+        <v>0.09299418</v>
       </c>
       <c r="N21">
-        <v>0.562655529</v>
+        <v>0.55800582</v>
       </c>
       <c r="O21">
-        <v>0.1125311058</v>
+        <v>0.111601164</v>
       </c>
       <c r="P21">
-        <v>0.4501244232</v>
+        <v>0.446404656</v>
       </c>
       <c r="Q21">
-        <v>0.5831244232</v>
+        <v>0.579404656</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1373943552596698</v>
+        <v>0.1383464795347183</v>
       </c>
       <c r="T21">
-        <v>1.002995732414547</v>
+        <v>1.013421883479147</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.368882202033901</v>
+        <v>7.000438091932205</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1193651836277746</v>
+        <v>0.1191873394952168</v>
       </c>
       <c r="C22">
-        <v>7.330919017120276</v>
+        <v>7.267039954064384</v>
       </c>
       <c r="D22">
-        <v>8.975519017120277</v>
+        <v>8.997269954064384</v>
       </c>
       <c r="E22">
-        <v>1.3296</v>
+        <v>1.41523</v>
       </c>
       <c r="F22">
-        <v>1.7126</v>
+        <v>1.79823</v>
       </c>
       <c r="G22">
         <v>0.068</v>
@@ -3085,28 +3085,28 @@
         <v>0.651</v>
       </c>
       <c r="M22">
-        <v>0.09299418</v>
+        <v>0.097643889</v>
       </c>
       <c r="N22">
-        <v>0.55800582</v>
+        <v>0.553356111</v>
       </c>
       <c r="O22">
-        <v>0.111601164</v>
+        <v>0.1106712222</v>
       </c>
       <c r="P22">
-        <v>0.446404656</v>
+        <v>0.4426848888</v>
       </c>
       <c r="Q22">
-        <v>0.579404656</v>
+        <v>0.5756848888</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1383464795347183</v>
+        <v>0.1393227082217934</v>
       </c>
       <c r="T22">
-        <v>1.013421883479147</v>
+        <v>1.024111987735256</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.000438091932205</v>
+        <v>6.667083897078291</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1191873394952168</v>
+        <v>0.1190094953626589</v>
       </c>
       <c r="C23">
-        <v>7.267039954064384</v>
+        <v>7.203266567915404</v>
       </c>
       <c r="D23">
-        <v>8.997269954064384</v>
+        <v>9.019126567915404</v>
       </c>
       <c r="E23">
-        <v>1.41523</v>
+        <v>1.50086</v>
       </c>
       <c r="F23">
-        <v>1.79823</v>
+        <v>1.88386</v>
       </c>
       <c r="G23">
         <v>0.068</v>
@@ -3167,28 +3167,28 @@
         <v>0.651</v>
       </c>
       <c r="M23">
-        <v>0.09764388899999998</v>
+        <v>0.102293598</v>
       </c>
       <c r="N23">
-        <v>0.553356111</v>
+        <v>0.5487064020000001</v>
       </c>
       <c r="O23">
-        <v>0.1106712222</v>
+        <v>0.1097412804</v>
       </c>
       <c r="P23">
-        <v>0.4426848888</v>
+        <v>0.4389651216000001</v>
       </c>
       <c r="Q23">
-        <v>0.5756848888</v>
+        <v>0.5719651216000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1393227082217934</v>
+        <v>0.1403239684136652</v>
       </c>
       <c r="T23">
-        <v>1.024111987735256</v>
+        <v>1.035076197228701</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.667083897078292</v>
+        <v>6.364034629029279</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1190094953626589</v>
+        <v>0.119015651230101</v>
       </c>
       <c r="C24">
-        <v>7.203266567915404</v>
+        <v>7.116878252628124</v>
       </c>
       <c r="D24">
-        <v>9.019126567915404</v>
+        <v>9.018368252628123</v>
       </c>
       <c r="E24">
-        <v>1.50086</v>
+        <v>1.58649</v>
       </c>
       <c r="F24">
-        <v>1.88386</v>
+        <v>1.96949</v>
       </c>
       <c r="G24">
         <v>0.068</v>
@@ -3249,45 +3249,45 @@
         <v>0.651</v>
       </c>
       <c r="M24">
-        <v>0.102293598</v>
+        <v>0.108912797</v>
       </c>
       <c r="N24">
-        <v>0.5487064020000001</v>
+        <v>0.542087203</v>
       </c>
       <c r="O24">
-        <v>0.1097412804</v>
+        <v>0.1084174406</v>
       </c>
       <c r="P24">
-        <v>0.4389651216000001</v>
+        <v>0.4336697624</v>
       </c>
       <c r="Q24">
-        <v>0.5719651216000001</v>
+        <v>0.5666697624</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1403239684136652</v>
+        <v>0.1413512353637676</v>
       </c>
       <c r="T24">
-        <v>1.035076197228701</v>
+        <v>1.046325191384314</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.364034629029279</v>
+        <v>5.977259035960669</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.119015651230101</v>
+        <v>0.1188458070975432</v>
       </c>
       <c r="C25">
-        <v>7.116878252628124</v>
+        <v>7.052217518268646</v>
       </c>
       <c r="D25">
-        <v>9.018368252628123</v>
+        <v>9.039337518268647</v>
       </c>
       <c r="E25">
-        <v>1.58649</v>
+        <v>1.67212</v>
       </c>
       <c r="F25">
-        <v>1.96949</v>
+        <v>2.05512</v>
       </c>
       <c r="G25">
         <v>0.068</v>
@@ -3331,28 +3331,28 @@
         <v>0.651</v>
       </c>
       <c r="M25">
-        <v>0.108912797</v>
+        <v>0.113648136</v>
       </c>
       <c r="N25">
-        <v>0.542087203</v>
+        <v>0.537351864</v>
       </c>
       <c r="O25">
-        <v>0.1084174406</v>
+        <v>0.1074703728</v>
       </c>
       <c r="P25">
-        <v>0.4336697624</v>
+        <v>0.4298814912</v>
       </c>
       <c r="Q25">
-        <v>0.5666697624</v>
+        <v>0.5628814912</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1413512353637676</v>
+        <v>0.1424055356546621</v>
       </c>
       <c r="T25">
-        <v>1.046325191384314</v>
+        <v>1.057870211701917</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.977259035960669</v>
+        <v>5.728206576128974</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1188458070975432</v>
+        <v>0.1186759629649853</v>
       </c>
       <c r="C26">
-        <v>7.052217518268649</v>
+        <v>6.987654525512531</v>
       </c>
       <c r="D26">
-        <v>9.039337518268649</v>
+        <v>9.060404525512531</v>
       </c>
       <c r="E26">
-        <v>1.67212</v>
+        <v>1.75775</v>
       </c>
       <c r="F26">
-        <v>2.05512</v>
+        <v>2.14075</v>
       </c>
       <c r="G26">
         <v>0.068</v>
@@ -3413,28 +3413,28 @@
         <v>0.651</v>
       </c>
       <c r="M26">
-        <v>0.113648136</v>
+        <v>0.118383475</v>
       </c>
       <c r="N26">
-        <v>0.537351864</v>
+        <v>0.532616525</v>
       </c>
       <c r="O26">
-        <v>0.1074703728</v>
+        <v>0.106523305</v>
       </c>
       <c r="P26">
-        <v>0.4298814912</v>
+        <v>0.42609322</v>
       </c>
       <c r="Q26">
-        <v>0.5628814912</v>
+        <v>0.5590932200000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.142405535654662</v>
+        <v>0.1434879506199804</v>
       </c>
       <c r="T26">
-        <v>1.057870211701916</v>
+        <v>1.069723099227988</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.728206576128975</v>
+        <v>5.499078313083816</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1186759629649853</v>
+        <v>0.1185061188324274</v>
       </c>
       <c r="C27">
-        <v>6.987654525512531</v>
+        <v>6.923189959343564</v>
       </c>
       <c r="D27">
-        <v>9.060404525512531</v>
+        <v>9.081569959343565</v>
       </c>
       <c r="E27">
-        <v>1.75775</v>
+        <v>1.84338</v>
       </c>
       <c r="F27">
-        <v>2.14075</v>
+        <v>2.22638</v>
       </c>
       <c r="G27">
         <v>0.068</v>
@@ -3495,28 +3495,28 @@
         <v>0.651</v>
       </c>
       <c r="M27">
-        <v>0.118383475</v>
+        <v>0.123118814</v>
       </c>
       <c r="N27">
-        <v>0.532616525</v>
+        <v>0.527881186</v>
       </c>
       <c r="O27">
-        <v>0.106523305</v>
+        <v>0.1055762372</v>
       </c>
       <c r="P27">
-        <v>0.42609322</v>
+        <v>0.4223049488</v>
       </c>
       <c r="Q27">
-        <v>0.5590932200000001</v>
+        <v>0.5553049488</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1434879506199804</v>
+        <v>0.1445996200438209</v>
       </c>
       <c r="T27">
-        <v>1.069723099227988</v>
+        <v>1.081896335065576</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.499078313083816</v>
+        <v>5.28757530104213</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1185061188324274</v>
+        <v>0.1183362746998696</v>
       </c>
       <c r="C28">
-        <v>6.923189959343564</v>
+        <v>6.858824511161123</v>
       </c>
       <c r="D28">
-        <v>9.081569959343565</v>
+        <v>9.102834511161124</v>
       </c>
       <c r="E28">
-        <v>1.84338</v>
+        <v>1.92901</v>
       </c>
       <c r="F28">
-        <v>2.22638</v>
+        <v>2.31201</v>
       </c>
       <c r="G28">
         <v>0.068</v>
@@ -3577,28 +3577,28 @@
         <v>0.651</v>
       </c>
       <c r="M28">
-        <v>0.123118814</v>
+        <v>0.127854153</v>
       </c>
       <c r="N28">
-        <v>0.527881186</v>
+        <v>0.523145847</v>
       </c>
       <c r="O28">
-        <v>0.1055762372</v>
+        <v>0.1046291694</v>
       </c>
       <c r="P28">
-        <v>0.4223049488</v>
+        <v>0.4185166776</v>
       </c>
       <c r="Q28">
-        <v>0.5553049488</v>
+        <v>0.5515166776</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1445996200438209</v>
+        <v>0.1457417461642049</v>
       </c>
       <c r="T28">
-        <v>1.081896335065576</v>
+        <v>1.094403084213782</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.28757530104213</v>
+        <v>5.09173917878131</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1183362746998696</v>
+        <v>0.1181664305673117</v>
       </c>
       <c r="C29">
-        <v>6.858824511161123</v>
+        <v>6.794558878855452</v>
       </c>
       <c r="D29">
-        <v>9.102834511161124</v>
+        <v>9.124198878855452</v>
       </c>
       <c r="E29">
-        <v>1.92901</v>
+        <v>2.01464</v>
       </c>
       <c r="F29">
-        <v>2.31201</v>
+        <v>2.39764</v>
       </c>
       <c r="G29">
         <v>0.068</v>
@@ -3659,28 +3659,28 @@
         <v>0.651</v>
       </c>
       <c r="M29">
-        <v>0.127854153</v>
+        <v>0.132589492</v>
       </c>
       <c r="N29">
-        <v>0.523145847</v>
+        <v>0.518410508</v>
       </c>
       <c r="O29">
-        <v>0.1046291694</v>
+        <v>0.1036821016</v>
       </c>
       <c r="P29">
-        <v>0.4185166776</v>
+        <v>0.4147284064</v>
       </c>
       <c r="Q29">
-        <v>0.5515166776</v>
+        <v>0.5477284064</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1457417461642049</v>
+        <v>0.1469155980101552</v>
       </c>
       <c r="T29">
-        <v>1.094403084213782</v>
+        <v>1.107257243060549</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.09173917878131</v>
+        <v>4.909891350967692</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1181664305673117</v>
+        <v>0.1179965864347538</v>
       </c>
       <c r="C30">
-        <v>6.794558878855452</v>
+        <v>6.730393766883991</v>
       </c>
       <c r="D30">
-        <v>9.124198878855452</v>
+        <v>9.145663766883992</v>
       </c>
       <c r="E30">
-        <v>2.01464</v>
+        <v>2.10027</v>
       </c>
       <c r="F30">
-        <v>2.39764</v>
+        <v>2.48327</v>
       </c>
       <c r="G30">
         <v>0.068</v>
@@ -3741,28 +3741,28 @@
         <v>0.651</v>
       </c>
       <c r="M30">
-        <v>0.132589492</v>
+        <v>0.137324831</v>
       </c>
       <c r="N30">
-        <v>0.518410508</v>
+        <v>0.513675169</v>
       </c>
       <c r="O30">
-        <v>0.1036821016</v>
+        <v>0.1027350338</v>
       </c>
       <c r="P30">
-        <v>0.4147284064</v>
+        <v>0.4109401352</v>
       </c>
       <c r="Q30">
-        <v>0.5477284064</v>
+        <v>0.5439401352</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1469155980101552</v>
+        <v>0.1481225161052871</v>
       </c>
       <c r="T30">
-        <v>1.107257243060549</v>
+        <v>1.120473490888916</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.909891350967692</v>
+        <v>4.740584752658461</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1179965864347538</v>
+        <v>0.117826742302196</v>
       </c>
       <c r="C31">
-        <v>6.730393766883992</v>
+        <v>6.666329886348828</v>
       </c>
       <c r="D31">
-        <v>9.145663766883992</v>
+        <v>9.167229886348828</v>
       </c>
       <c r="E31">
-        <v>2.10027</v>
+        <v>2.1859</v>
       </c>
       <c r="F31">
-        <v>2.48327</v>
+        <v>2.5689</v>
       </c>
       <c r="G31">
         <v>0.068</v>
@@ -3823,28 +3823,28 @@
         <v>0.651</v>
       </c>
       <c r="M31">
-        <v>0.137324831</v>
+        <v>0.14206017</v>
       </c>
       <c r="N31">
-        <v>0.5136751690000001</v>
+        <v>0.5089398300000001</v>
       </c>
       <c r="O31">
-        <v>0.1027350338</v>
+        <v>0.101787966</v>
       </c>
       <c r="P31">
-        <v>0.4109401352000001</v>
+        <v>0.4071518640000001</v>
       </c>
       <c r="Q31">
-        <v>0.5439401352000001</v>
+        <v>0.540151864</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1481225161052871</v>
+        <v>0.1493639175745657</v>
       </c>
       <c r="T31">
-        <v>1.120473490888916</v>
+        <v>1.134067345798093</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.740584752658462</v>
+        <v>4.582565260903181</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.117826742302196</v>
+        <v>0.1182768981696381</v>
       </c>
       <c r="C32">
-        <v>6.666329886348828</v>
+        <v>6.523761987159599</v>
       </c>
       <c r="D32">
-        <v>9.167229886348828</v>
+        <v>9.110291987159599</v>
       </c>
       <c r="E32">
-        <v>2.1859</v>
+        <v>2.27153</v>
       </c>
       <c r="F32">
-        <v>2.5689</v>
+        <v>2.65453</v>
       </c>
       <c r="G32">
         <v>0.068</v>
@@ -3905,45 +3905,45 @@
         <v>0.651</v>
       </c>
       <c r="M32">
-        <v>0.14206017</v>
+        <v>0.153431834</v>
       </c>
       <c r="N32">
-        <v>0.5089398300000001</v>
+        <v>0.497568166</v>
       </c>
       <c r="O32">
-        <v>0.101787966</v>
+        <v>0.09951363320000001</v>
       </c>
       <c r="P32">
-        <v>0.4071518640000001</v>
+        <v>0.3980545328</v>
       </c>
       <c r="Q32">
-        <v>0.540151864</v>
+        <v>0.5310545328</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1493639175745657</v>
+        <v>0.1506413016951277</v>
       </c>
       <c r="T32">
-        <v>1.134067345798093</v>
+        <v>1.148055225487246</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.582565260903181</v>
+        <v>4.242926536353597</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1182768981696381</v>
+        <v>0.1181270540370802</v>
       </c>
       <c r="C33">
-        <v>6.523761987159599</v>
+        <v>6.457006304914406</v>
       </c>
       <c r="D33">
-        <v>9.110291987159599</v>
+        <v>9.129166304914406</v>
       </c>
       <c r="E33">
-        <v>2.27153</v>
+        <v>2.357159999999999</v>
       </c>
       <c r="F33">
-        <v>2.65453</v>
+        <v>2.740159999999999</v>
       </c>
       <c r="G33">
         <v>0.068</v>
@@ -3987,28 +3987,28 @@
         <v>0.651</v>
       </c>
       <c r="M33">
-        <v>0.153431834</v>
+        <v>0.158381248</v>
       </c>
       <c r="N33">
-        <v>0.497568166</v>
+        <v>0.492618752</v>
       </c>
       <c r="O33">
-        <v>0.09951363320000001</v>
+        <v>0.09852375040000001</v>
       </c>
       <c r="P33">
-        <v>0.3980545328</v>
+        <v>0.3940950016</v>
       </c>
       <c r="Q33">
-        <v>0.5310545328</v>
+        <v>0.5270950016</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1506413016951277</v>
+        <v>0.1519562559368827</v>
       </c>
       <c r="T33">
-        <v>1.148055225487246</v>
+        <v>1.162454513402551</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.242926536353597</v>
+        <v>4.110335082092547</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1181270540370802</v>
+        <v>0.1189012099045224</v>
       </c>
       <c r="C34">
-        <v>6.457006304914406</v>
+        <v>6.274696678557532</v>
       </c>
       <c r="D34">
-        <v>9.129166304914406</v>
+        <v>9.032486678557532</v>
       </c>
       <c r="E34">
-        <v>2.357159999999999</v>
+        <v>2.44279</v>
       </c>
       <c r="F34">
-        <v>2.740159999999999</v>
+        <v>2.82579</v>
       </c>
       <c r="G34">
         <v>0.068</v>
@@ -4069,45 +4069,45 @@
         <v>0.651</v>
       </c>
       <c r="M34">
-        <v>0.158381248</v>
+        <v>0.173220927</v>
       </c>
       <c r="N34">
-        <v>0.492618752</v>
+        <v>0.4777790730000001</v>
       </c>
       <c r="O34">
-        <v>0.09852375040000001</v>
+        <v>0.09555581460000001</v>
       </c>
       <c r="P34">
-        <v>0.3940950016</v>
+        <v>0.3822232584</v>
       </c>
       <c r="Q34">
-        <v>0.5270950016</v>
+        <v>0.5152232584000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1519562559368827</v>
+        <v>0.1533104625440633</v>
       </c>
       <c r="T34">
-        <v>1.162454513402551</v>
+        <v>1.177283630807865</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.110335082092547</v>
+        <v>3.758206420405545</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1189012099045224</v>
+        <v>0.1187793657719645</v>
       </c>
       <c r="C35">
-        <v>6.274696678557532</v>
+        <v>6.204147043980662</v>
       </c>
       <c r="D35">
-        <v>9.032486678557532</v>
+        <v>9.047567043980662</v>
       </c>
       <c r="E35">
-        <v>2.44279</v>
+        <v>2.52842</v>
       </c>
       <c r="F35">
-        <v>2.82579</v>
+        <v>2.91142</v>
       </c>
       <c r="G35">
         <v>0.068</v>
@@ -4151,28 +4151,28 @@
         <v>0.651</v>
       </c>
       <c r="M35">
-        <v>0.173220927</v>
+        <v>0.178470046</v>
       </c>
       <c r="N35">
-        <v>0.4777790730000001</v>
+        <v>0.472529954</v>
       </c>
       <c r="O35">
-        <v>0.09555581460000001</v>
+        <v>0.09450599080000001</v>
       </c>
       <c r="P35">
-        <v>0.3822232584</v>
+        <v>0.3780239632</v>
       </c>
       <c r="Q35">
-        <v>0.5152232584000001</v>
+        <v>0.5110239632</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1533104625440633</v>
+        <v>0.1547057057150978</v>
       </c>
       <c r="T35">
-        <v>1.177283630807865</v>
+        <v>1.192562115407279</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.758206420405545</v>
+        <v>3.64767093745244</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1187793657719645</v>
+        <v>0.1186575216394067</v>
       </c>
       <c r="C36">
-        <v>6.204147043980662</v>
+        <v>6.133647849056477</v>
       </c>
       <c r="D36">
-        <v>9.047567043980662</v>
+        <v>9.062697849056477</v>
       </c>
       <c r="E36">
-        <v>2.52842</v>
+        <v>2.61405</v>
       </c>
       <c r="F36">
-        <v>2.91142</v>
+        <v>2.99705</v>
       </c>
       <c r="G36">
         <v>0.068</v>
@@ -4233,28 +4233,28 @@
         <v>0.651</v>
       </c>
       <c r="M36">
-        <v>0.178470046</v>
+        <v>0.183719165</v>
       </c>
       <c r="N36">
-        <v>0.472529954</v>
+        <v>0.4672808350000001</v>
       </c>
       <c r="O36">
-        <v>0.09450599080000001</v>
+        <v>0.09345616700000002</v>
       </c>
       <c r="P36">
-        <v>0.3780239632</v>
+        <v>0.373824668</v>
       </c>
       <c r="Q36">
-        <v>0.5110239632</v>
+        <v>0.506824668</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1547057057150978</v>
+        <v>0.156143879445241</v>
       </c>
       <c r="T36">
-        <v>1.192562115407279</v>
+        <v>1.208310707225137</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.64767093745244</v>
+        <v>3.543451767810942</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1186575216394067</v>
+        <v>0.1193420775068488</v>
       </c>
       <c r="C37">
-        <v>6.133647849056477</v>
+        <v>5.963659027579764</v>
       </c>
       <c r="D37">
-        <v>9.062697849056477</v>
+        <v>8.978339027579764</v>
       </c>
       <c r="E37">
-        <v>2.61405</v>
+        <v>2.69968</v>
       </c>
       <c r="F37">
-        <v>2.99705</v>
+        <v>3.08268</v>
       </c>
       <c r="G37">
         <v>0.068</v>
@@ -4315,45 +4315,45 @@
         <v>0.651</v>
       </c>
       <c r="M37">
-        <v>0.183719165</v>
+        <v>0.197599788</v>
       </c>
       <c r="N37">
-        <v>0.4672808350000001</v>
+        <v>0.453400212</v>
       </c>
       <c r="O37">
-        <v>0.09345616700000002</v>
+        <v>0.09068004240000001</v>
       </c>
       <c r="P37">
-        <v>0.373824668</v>
+        <v>0.3627201696</v>
       </c>
       <c r="Q37">
-        <v>0.506824668</v>
+        <v>0.4957201696</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.156143879445241</v>
+        <v>0.1576269961044512</v>
       </c>
       <c r="T37">
-        <v>1.208310707225137</v>
+        <v>1.224551442537303</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.543451767810942</v>
+        <v>3.294537947581199</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1193420775068488</v>
+        <v>0.119242633374291</v>
       </c>
       <c r="C38">
-        <v>5.963659027579761</v>
+        <v>5.890186041774195</v>
       </c>
       <c r="D38">
-        <v>8.978339027579761</v>
+        <v>8.990496041774195</v>
       </c>
       <c r="E38">
-        <v>2.699679999999999</v>
+        <v>2.78531</v>
       </c>
       <c r="F38">
-        <v>3.082679999999999</v>
+        <v>3.16831</v>
       </c>
       <c r="G38">
         <v>0.068</v>
@@ -4397,28 +4397,28 @@
         <v>0.651</v>
       </c>
       <c r="M38">
-        <v>0.197599788</v>
+        <v>0.203088671</v>
       </c>
       <c r="N38">
-        <v>0.453400212</v>
+        <v>0.4479113290000001</v>
       </c>
       <c r="O38">
-        <v>0.09068004240000001</v>
+        <v>0.08958226580000002</v>
       </c>
       <c r="P38">
-        <v>0.3627201696</v>
+        <v>0.3583290632000001</v>
       </c>
       <c r="Q38">
-        <v>0.4957201696</v>
+        <v>0.4913290632000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1576269961044512</v>
+        <v>0.1591571958322079</v>
       </c>
       <c r="T38">
-        <v>1.224551442537302</v>
+        <v>1.241307756748267</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.294537947581199</v>
+        <v>3.205496381430356</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.119242633374291</v>
+        <v>0.1191431892417331</v>
       </c>
       <c r="C39">
-        <v>5.890186041774195</v>
+        <v>5.816746022730612</v>
       </c>
       <c r="D39">
-        <v>8.990496041774195</v>
+        <v>9.002686022730613</v>
       </c>
       <c r="E39">
-        <v>2.78531</v>
+        <v>2.87094</v>
       </c>
       <c r="F39">
-        <v>3.16831</v>
+        <v>3.25394</v>
       </c>
       <c r="G39">
         <v>0.068</v>
@@ -4479,28 +4479,28 @@
         <v>0.651</v>
       </c>
       <c r="M39">
-        <v>0.203088671</v>
+        <v>0.208577554</v>
       </c>
       <c r="N39">
-        <v>0.4479113290000001</v>
+        <v>0.442422446</v>
       </c>
       <c r="O39">
-        <v>0.08958226580000002</v>
+        <v>0.08848448920000002</v>
       </c>
       <c r="P39">
-        <v>0.3583290632000001</v>
+        <v>0.3539379568</v>
       </c>
       <c r="Q39">
-        <v>0.4913290632000001</v>
+        <v>0.4869379568</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1591571958322079</v>
+        <v>0.1607367568415049</v>
       </c>
       <c r="T39">
-        <v>1.241307756748267</v>
+        <v>1.258604597224102</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.205496381430356</v>
+        <v>3.121141213497978</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1191431892417331</v>
+        <v>0.1190437451091752</v>
       </c>
       <c r="C40">
-        <v>5.816746022730612</v>
+        <v>5.743339104727394</v>
       </c>
       <c r="D40">
-        <v>9.002686022730613</v>
+        <v>9.014909104727394</v>
       </c>
       <c r="E40">
-        <v>2.87094</v>
+        <v>2.95657</v>
       </c>
       <c r="F40">
-        <v>3.25394</v>
+        <v>3.33957</v>
       </c>
       <c r="G40">
         <v>0.068</v>
@@ -4561,28 +4561,28 @@
         <v>0.651</v>
       </c>
       <c r="M40">
-        <v>0.208577554</v>
+        <v>0.214066437</v>
       </c>
       <c r="N40">
-        <v>0.442422446</v>
+        <v>0.436933563</v>
       </c>
       <c r="O40">
-        <v>0.08848448920000002</v>
+        <v>0.08738671260000001</v>
       </c>
       <c r="P40">
-        <v>0.3539379568</v>
+        <v>0.3495468504</v>
       </c>
       <c r="Q40">
-        <v>0.4869379568</v>
+        <v>0.4825468504</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1607367568415049</v>
+        <v>0.1623681067363528</v>
       </c>
       <c r="T40">
-        <v>1.258604597224102</v>
+        <v>1.276468547223734</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.121141213497978</v>
+        <v>3.041111951613415</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1190437451091752</v>
+        <v>0.1214403009766173</v>
       </c>
       <c r="C41">
-        <v>5.743339104727394</v>
+        <v>5.372084470366532</v>
       </c>
       <c r="D41">
-        <v>9.014909104727394</v>
+        <v>8.729284470366533</v>
       </c>
       <c r="E41">
-        <v>2.95657</v>
+        <v>3.0422</v>
       </c>
       <c r="F41">
-        <v>3.33957</v>
+        <v>3.4252</v>
       </c>
       <c r="G41">
         <v>0.068</v>
@@ -4643,45 +4643,45 @@
         <v>0.651</v>
       </c>
       <c r="M41">
-        <v>0.214066437</v>
+        <v>0.24627188</v>
       </c>
       <c r="N41">
-        <v>0.436933563</v>
+        <v>0.40472812</v>
       </c>
       <c r="O41">
-        <v>0.08738671260000001</v>
+        <v>0.08094562400000001</v>
       </c>
       <c r="P41">
-        <v>0.3495468504</v>
+        <v>0.323782496</v>
       </c>
       <c r="Q41">
-        <v>0.4825468504</v>
+        <v>0.456782496</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1623681067363528</v>
+        <v>0.1640538349610289</v>
       </c>
       <c r="T41">
-        <v>1.276468547223734</v>
+        <v>1.294927962223354</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.041111951613415</v>
+        <v>2.64341994709262</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1214403009766173</v>
+        <v>0.1214032568440595</v>
       </c>
       <c r="C42">
-        <v>5.372084470366532</v>
+        <v>5.290731650802325</v>
       </c>
       <c r="D42">
-        <v>8.729284470366533</v>
+        <v>8.733561650802326</v>
       </c>
       <c r="E42">
-        <v>3.0422</v>
+        <v>3.12783</v>
       </c>
       <c r="F42">
-        <v>3.4252</v>
+        <v>3.51083</v>
       </c>
       <c r="G42">
         <v>0.068</v>
@@ -4725,28 +4725,28 @@
         <v>0.651</v>
       </c>
       <c r="M42">
-        <v>0.24627188</v>
+        <v>0.252428677</v>
       </c>
       <c r="N42">
-        <v>0.40472812</v>
+        <v>0.398571323</v>
       </c>
       <c r="O42">
-        <v>0.08094562400000001</v>
+        <v>0.07971426460000001</v>
       </c>
       <c r="P42">
-        <v>0.323782496</v>
+        <v>0.3188570584</v>
       </c>
       <c r="Q42">
-        <v>0.456782496</v>
+        <v>0.4518570584</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1640538349610289</v>
+        <v>0.1657967065153551</v>
       </c>
       <c r="T42">
-        <v>1.294927962223354</v>
+        <v>1.314013120104317</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.64341994709262</v>
+        <v>2.578946289846459</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1214032568440595</v>
+        <v>0.1213662127115016</v>
       </c>
       <c r="C43">
-        <v>5.290731650802325</v>
+        <v>5.209383024764119</v>
       </c>
       <c r="D43">
-        <v>8.733561650802326</v>
+        <v>8.737843024764119</v>
       </c>
       <c r="E43">
-        <v>3.12783</v>
+        <v>3.21346</v>
       </c>
       <c r="F43">
-        <v>3.51083</v>
+        <v>3.59646</v>
       </c>
       <c r="G43">
         <v>0.068</v>
@@ -4807,28 +4807,28 @@
         <v>0.651</v>
       </c>
       <c r="M43">
-        <v>0.252428677</v>
+        <v>0.258585474</v>
       </c>
       <c r="N43">
-        <v>0.398571323</v>
+        <v>0.392414526</v>
       </c>
       <c r="O43">
-        <v>0.07971426460000001</v>
+        <v>0.07848290520000001</v>
       </c>
       <c r="P43">
-        <v>0.3188570584</v>
+        <v>0.3139316208</v>
       </c>
       <c r="Q43">
-        <v>0.4518570584</v>
+        <v>0.4469316208</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1657967065153551</v>
+        <v>0.1675996770887959</v>
       </c>
       <c r="T43">
-        <v>1.314013120104317</v>
+        <v>1.333756386877728</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.578946289846459</v>
+        <v>2.517542806754876</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1213662127115016</v>
+        <v>0.1226707685789438</v>
       </c>
       <c r="C44">
-        <v>5.20938302476412</v>
+        <v>4.975465130711934</v>
       </c>
       <c r="D44">
-        <v>8.737843024764119</v>
+        <v>8.589555130711934</v>
       </c>
       <c r="E44">
-        <v>3.21346</v>
+        <v>3.29909</v>
       </c>
       <c r="F44">
-        <v>3.59646</v>
+        <v>3.68209</v>
       </c>
       <c r="G44">
         <v>0.068</v>
@@ -4889,45 +4889,45 @@
         <v>0.651</v>
       </c>
       <c r="M44">
-        <v>0.258585474</v>
+        <v>0.279102422</v>
       </c>
       <c r="N44">
-        <v>0.392414526</v>
+        <v>0.371897578</v>
       </c>
       <c r="O44">
-        <v>0.07848290520000001</v>
+        <v>0.0743795156</v>
       </c>
       <c r="P44">
-        <v>0.3139316208</v>
+        <v>0.2975180624</v>
       </c>
       <c r="Q44">
-        <v>0.4469316208</v>
+        <v>0.4305180624</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1675996770887959</v>
+        <v>0.1694659097876206</v>
       </c>
       <c r="T44">
-        <v>1.333756386877728</v>
+        <v>1.354192399853714</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.517542806754876</v>
+        <v>2.332477071804128</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1226707685789438</v>
+        <v>0.1226649244463859</v>
       </c>
       <c r="C45">
-        <v>4.975465130711934</v>
+        <v>4.890488204908765</v>
       </c>
       <c r="D45">
-        <v>8.589555130711934</v>
+        <v>8.590208204908764</v>
       </c>
       <c r="E45">
-        <v>3.29909</v>
+        <v>3.384719999999999</v>
       </c>
       <c r="F45">
-        <v>3.68209</v>
+        <v>3.767719999999999</v>
       </c>
       <c r="G45">
         <v>0.068</v>
@@ -4971,28 +4971,28 @@
         <v>0.651</v>
       </c>
       <c r="M45">
-        <v>0.279102422</v>
+        <v>0.2855931759999999</v>
       </c>
       <c r="N45">
-        <v>0.371897578</v>
+        <v>0.3654068240000001</v>
       </c>
       <c r="O45">
-        <v>0.0743795156</v>
+        <v>0.07308136480000002</v>
       </c>
       <c r="P45">
-        <v>0.2975180624</v>
+        <v>0.2923254592000001</v>
       </c>
       <c r="Q45">
-        <v>0.4305180624</v>
+        <v>0.4253254592000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1694659097876206</v>
+        <v>0.1713987936542605</v>
       </c>
       <c r="T45">
-        <v>1.354192399853714</v>
+        <v>1.375358270435985</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.332477071804128</v>
+        <v>2.279466229263125</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1226649244463859</v>
+        <v>0.122659080313828</v>
       </c>
       <c r="C46">
-        <v>4.890488204908765</v>
+        <v>4.805511378421173</v>
       </c>
       <c r="D46">
-        <v>8.590208204908764</v>
+        <v>8.590861378421172</v>
       </c>
       <c r="E46">
-        <v>3.384719999999999</v>
+        <v>3.470349999999999</v>
       </c>
       <c r="F46">
-        <v>3.767719999999999</v>
+        <v>3.853349999999999</v>
       </c>
       <c r="G46">
         <v>0.068</v>
@@ -5053,28 +5053,28 @@
         <v>0.651</v>
       </c>
       <c r="M46">
-        <v>0.2855931759999999</v>
+        <v>0.29208393</v>
       </c>
       <c r="N46">
-        <v>0.3654068240000001</v>
+        <v>0.35891607</v>
       </c>
       <c r="O46">
-        <v>0.07308136480000002</v>
+        <v>0.07178321400000001</v>
       </c>
       <c r="P46">
-        <v>0.2923254592000001</v>
+        <v>0.287132856</v>
       </c>
       <c r="Q46">
-        <v>0.4253254592000001</v>
+        <v>0.4201328560000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1713987936542605</v>
+        <v>0.1734019642069601</v>
       </c>
       <c r="T46">
-        <v>1.375358270435985</v>
+        <v>1.39729380903943</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.279466229263125</v>
+        <v>2.228811424168389</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.122659080313828</v>
+        <v>0.1226532361812702</v>
       </c>
       <c r="C47">
-        <v>4.805511378421173</v>
+        <v>4.720534651271821</v>
       </c>
       <c r="D47">
-        <v>8.590861378421172</v>
+        <v>8.591514651271821</v>
       </c>
       <c r="E47">
-        <v>3.470349999999999</v>
+        <v>3.555979999999999</v>
       </c>
       <c r="F47">
-        <v>3.853349999999999</v>
+        <v>3.938979999999999</v>
       </c>
       <c r="G47">
         <v>0.068</v>
@@ -5135,28 +5135,28 @@
         <v>0.651</v>
       </c>
       <c r="M47">
-        <v>0.29208393</v>
+        <v>0.298574684</v>
       </c>
       <c r="N47">
-        <v>0.35891607</v>
+        <v>0.352425316</v>
       </c>
       <c r="O47">
-        <v>0.07178321400000001</v>
+        <v>0.07048506320000002</v>
       </c>
       <c r="P47">
-        <v>0.287132856</v>
+        <v>0.2819402528</v>
       </c>
       <c r="Q47">
-        <v>0.4201328560000001</v>
+        <v>0.4149402528</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1734019642069601</v>
+        <v>0.1754793262616114</v>
       </c>
       <c r="T47">
-        <v>1.39729380903943</v>
+        <v>1.420041774998558</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.228811424168389</v>
+        <v>2.180359001903859</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1226532361812702</v>
+        <v>0.1226473920487123</v>
       </c>
       <c r="C48">
-        <v>4.720534651271821</v>
+        <v>4.635558023483372</v>
       </c>
       <c r="D48">
-        <v>8.591514651271821</v>
+        <v>8.592168023483373</v>
       </c>
       <c r="E48">
-        <v>3.555979999999999</v>
+        <v>3.64161</v>
       </c>
       <c r="F48">
-        <v>3.938979999999999</v>
+        <v>4.02461</v>
       </c>
       <c r="G48">
         <v>0.068</v>
@@ -5217,28 +5217,28 @@
         <v>0.651</v>
       </c>
       <c r="M48">
-        <v>0.298574684</v>
+        <v>0.305065438</v>
       </c>
       <c r="N48">
-        <v>0.352425316</v>
+        <v>0.345934562</v>
       </c>
       <c r="O48">
-        <v>0.07048506320000002</v>
+        <v>0.06918691240000001</v>
       </c>
       <c r="P48">
-        <v>0.2819402528</v>
+        <v>0.2767476496</v>
       </c>
       <c r="Q48">
-        <v>0.4149402528</v>
+        <v>0.4097476496</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1754793262616114</v>
+        <v>0.177635079337193</v>
       </c>
       <c r="T48">
-        <v>1.420041774998558</v>
+        <v>1.443648154767464</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.180359001903859</v>
+        <v>2.133968384842074</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1226473920487123</v>
+        <v>0.1226415479161544</v>
       </c>
       <c r="C49">
-        <v>4.635558023483372</v>
+        <v>4.550581495078498</v>
       </c>
       <c r="D49">
-        <v>8.592168023483373</v>
+        <v>8.592821495078498</v>
       </c>
       <c r="E49">
-        <v>3.64161</v>
+        <v>3.72724</v>
       </c>
       <c r="F49">
-        <v>4.02461</v>
+        <v>4.11024</v>
       </c>
       <c r="G49">
         <v>0.068</v>
@@ -5299,28 +5299,28 @@
         <v>0.651</v>
       </c>
       <c r="M49">
-        <v>0.305065438</v>
+        <v>0.311556192</v>
       </c>
       <c r="N49">
-        <v>0.345934562</v>
+        <v>0.339443808</v>
       </c>
       <c r="O49">
-        <v>0.06918691240000001</v>
+        <v>0.0678887616</v>
       </c>
       <c r="P49">
-        <v>0.2767476496</v>
+        <v>0.2715550464</v>
       </c>
       <c r="Q49">
-        <v>0.4097476496</v>
+        <v>0.4045550464</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.177635079337193</v>
+        <v>0.1798737459926047</v>
       </c>
       <c r="T49">
-        <v>1.443648154767464</v>
+        <v>1.46816247221979</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.133968384842074</v>
+        <v>2.089510710157865</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1226415479161544</v>
+        <v>0.1226357037835966</v>
       </c>
       <c r="C50">
-        <v>4.550581495078498</v>
+        <v>4.465605066079878</v>
       </c>
       <c r="D50">
-        <v>8.592821495078498</v>
+        <v>8.593475066079877</v>
       </c>
       <c r="E50">
-        <v>3.727239999999999</v>
+        <v>3.812869999999999</v>
       </c>
       <c r="F50">
-        <v>4.110239999999999</v>
+        <v>4.195869999999999</v>
       </c>
       <c r="G50">
         <v>0.068</v>
@@ -5381,28 +5381,28 @@
         <v>0.651</v>
       </c>
       <c r="M50">
-        <v>0.311556192</v>
+        <v>0.318046946</v>
       </c>
       <c r="N50">
-        <v>0.3394438080000001</v>
+        <v>0.332953054</v>
       </c>
       <c r="O50">
-        <v>0.06788876160000001</v>
+        <v>0.06659061080000001</v>
       </c>
       <c r="P50">
-        <v>0.2715550464000001</v>
+        <v>0.2663624432</v>
       </c>
       <c r="Q50">
-        <v>0.4045550464000001</v>
+        <v>0.3993624432</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1798737459926047</v>
+        <v>0.1822002034972482</v>
       </c>
       <c r="T50">
-        <v>1.46816247221979</v>
+        <v>1.493638135454559</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.089510710157865</v>
+        <v>2.046867634440357</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1226357037835966</v>
+        <v>0.1226298596510387</v>
       </c>
       <c r="C51">
-        <v>4.465605066079878</v>
+        <v>4.380628736510188</v>
       </c>
       <c r="D51">
-        <v>8.593475066079877</v>
+        <v>8.594128736510187</v>
       </c>
       <c r="E51">
-        <v>3.812869999999999</v>
+        <v>3.898499999999999</v>
       </c>
       <c r="F51">
-        <v>4.195869999999999</v>
+        <v>4.281499999999999</v>
       </c>
       <c r="G51">
         <v>0.068</v>
@@ -5463,28 +5463,28 @@
         <v>0.651</v>
       </c>
       <c r="M51">
-        <v>0.318046946</v>
+        <v>0.3245377</v>
       </c>
       <c r="N51">
-        <v>0.332953054</v>
+        <v>0.3264623</v>
       </c>
       <c r="O51">
-        <v>0.06659061080000001</v>
+        <v>0.06529246000000001</v>
       </c>
       <c r="P51">
-        <v>0.2663624432</v>
+        <v>0.26116984</v>
       </c>
       <c r="Q51">
-        <v>0.3993624432</v>
+        <v>0.39416984</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1822002034972482</v>
+        <v>0.1846197193020774</v>
       </c>
       <c r="T51">
-        <v>1.493638135454559</v>
+        <v>1.52013282521872</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.046867634440357</v>
+        <v>2.00593028175155</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1226298596510387</v>
+        <v>0.1284176155184809</v>
       </c>
       <c r="C52">
-        <v>4.380628736510188</v>
+        <v>3.692939251881715</v>
       </c>
       <c r="D52">
-        <v>8.594128736510187</v>
+        <v>7.992069251881714</v>
       </c>
       <c r="E52">
-        <v>3.898499999999999</v>
+        <v>3.98413</v>
       </c>
       <c r="F52">
-        <v>4.281499999999999</v>
+        <v>4.36713</v>
       </c>
       <c r="G52">
         <v>0.068</v>
@@ -5545,45 +5545,45 @@
         <v>0.651</v>
       </c>
       <c r="M52">
-        <v>0.3245377</v>
+        <v>0.3930416999999999</v>
       </c>
       <c r="N52">
-        <v>0.3264623</v>
+        <v>0.2579583000000001</v>
       </c>
       <c r="O52">
-        <v>0.06529246000000001</v>
+        <v>0.05159166000000002</v>
       </c>
       <c r="P52">
-        <v>0.26116984</v>
+        <v>0.2063666400000001</v>
       </c>
       <c r="Q52">
-        <v>0.39416984</v>
+        <v>0.3393666400000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1846197193020774</v>
+        <v>0.1871379908540426</v>
       </c>
       <c r="T52">
-        <v>1.52013282521872</v>
+        <v>1.547708930891622</v>
       </c>
       <c r="U52">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.00593028175155</v>
+        <v>1.656312803450627</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1284176155184809</v>
+        <v>0.128525371385923</v>
       </c>
       <c r="C53">
-        <v>3.692939251881715</v>
+        <v>3.596898995143473</v>
       </c>
       <c r="D53">
-        <v>7.992069251881714</v>
+        <v>7.981658995143472</v>
       </c>
       <c r="E53">
-        <v>3.98413</v>
+        <v>4.06976</v>
       </c>
       <c r="F53">
-        <v>4.36713</v>
+        <v>4.45276</v>
       </c>
       <c r="G53">
         <v>0.068</v>
@@ -5627,28 +5627,28 @@
         <v>0.651</v>
       </c>
       <c r="M53">
-        <v>0.3930416999999999</v>
+        <v>0.4007483999999999</v>
       </c>
       <c r="N53">
-        <v>0.2579583000000001</v>
+        <v>0.2502516000000001</v>
       </c>
       <c r="O53">
-        <v>0.05159166000000002</v>
+        <v>0.05005032000000002</v>
       </c>
       <c r="P53">
-        <v>0.2063666400000001</v>
+        <v>0.2002012800000001</v>
       </c>
       <c r="Q53">
-        <v>0.3393666400000001</v>
+        <v>0.33320128</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1871379908540426</v>
+        <v>0.1897611903873395</v>
       </c>
       <c r="T53">
-        <v>1.547708930891622</v>
+        <v>1.576434040967562</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.656312803450627</v>
+        <v>1.624460634153499</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.128525371385923</v>
+        <v>0.1286331272533651</v>
       </c>
       <c r="C54">
-        <v>3.596898995143473</v>
+        <v>3.500885823371888</v>
       </c>
       <c r="D54">
-        <v>7.981658995143472</v>
+        <v>7.971275823371887</v>
       </c>
       <c r="E54">
-        <v>4.06976</v>
+        <v>4.15539</v>
       </c>
       <c r="F54">
-        <v>4.45276</v>
+        <v>4.53839</v>
       </c>
       <c r="G54">
         <v>0.068</v>
@@ -5709,28 +5709,28 @@
         <v>0.651</v>
       </c>
       <c r="M54">
-        <v>0.4007483999999999</v>
+        <v>0.4084551</v>
       </c>
       <c r="N54">
-        <v>0.2502516000000001</v>
+        <v>0.2425449000000001</v>
       </c>
       <c r="O54">
-        <v>0.05005032000000002</v>
+        <v>0.04850898000000001</v>
       </c>
       <c r="P54">
-        <v>0.2002012800000001</v>
+        <v>0.1940359200000001</v>
       </c>
       <c r="Q54">
-        <v>0.33320128</v>
+        <v>0.32703592</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1897611903873395</v>
+        <v>0.1924960154326917</v>
       </c>
       <c r="T54">
-        <v>1.576434040967562</v>
+        <v>1.606381496153116</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.624460634153499</v>
+        <v>1.593810433509093</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1286331272533651</v>
+        <v>0.1287408831208073</v>
       </c>
       <c r="C55">
-        <v>3.500885823371888</v>
+        <v>3.404899631001511</v>
       </c>
       <c r="D55">
-        <v>7.971275823371887</v>
+        <v>7.960919631001511</v>
       </c>
       <c r="E55">
-        <v>4.15539</v>
+        <v>4.24102</v>
       </c>
       <c r="F55">
-        <v>4.53839</v>
+        <v>4.62402</v>
       </c>
       <c r="G55">
         <v>0.068</v>
@@ -5791,28 +5791,28 @@
         <v>0.651</v>
       </c>
       <c r="M55">
-        <v>0.4084551</v>
+        <v>0.4161618</v>
       </c>
       <c r="N55">
-        <v>0.2425449000000001</v>
+        <v>0.2348382000000001</v>
       </c>
       <c r="O55">
-        <v>0.04850898000000001</v>
+        <v>0.04696764000000001</v>
       </c>
       <c r="P55">
-        <v>0.1940359200000001</v>
+        <v>0.18787056</v>
       </c>
       <c r="Q55">
-        <v>0.32703592</v>
+        <v>0.32087056</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1924960154326917</v>
+        <v>0.1953497459147984</v>
       </c>
       <c r="T55">
-        <v>1.606381496153116</v>
+        <v>1.637631014607607</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.593810433509093</v>
+        <v>1.564295425481147</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1287408831208073</v>
+        <v>0.1288486389882494</v>
       </c>
       <c r="C56">
-        <v>3.404899631001511</v>
+        <v>3.308940313014771</v>
       </c>
       <c r="D56">
-        <v>7.960919631001511</v>
+        <v>7.950590313014771</v>
       </c>
       <c r="E56">
-        <v>4.24102</v>
+        <v>4.32665</v>
       </c>
       <c r="F56">
-        <v>4.62402</v>
+        <v>4.70965</v>
       </c>
       <c r="G56">
         <v>0.068</v>
@@ -5873,28 +5873,28 @@
         <v>0.651</v>
       </c>
       <c r="M56">
-        <v>0.4161618</v>
+        <v>0.4238685</v>
       </c>
       <c r="N56">
-        <v>0.2348382000000001</v>
+        <v>0.2271315</v>
       </c>
       <c r="O56">
-        <v>0.04696764000000001</v>
+        <v>0.04542630000000001</v>
       </c>
       <c r="P56">
-        <v>0.18787056</v>
+        <v>0.1817052</v>
       </c>
       <c r="Q56">
-        <v>0.32087056</v>
+        <v>0.3147052</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1953497459147984</v>
+        <v>0.1983303088627764</v>
       </c>
       <c r="T56">
-        <v>1.637631014607607</v>
+        <v>1.670269400548964</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.564295425481147</v>
+        <v>1.535853690472399</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1288486389882494</v>
+        <v>0.1289563948556915</v>
       </c>
       <c r="C57">
-        <v>3.308940313014771</v>
+        <v>3.21300776493843</v>
       </c>
       <c r="D57">
-        <v>7.950590313014771</v>
+        <v>7.94028776493843</v>
       </c>
       <c r="E57">
-        <v>4.32665</v>
+        <v>4.41228</v>
       </c>
       <c r="F57">
-        <v>4.70965</v>
+        <v>4.79528</v>
       </c>
       <c r="G57">
         <v>0.068</v>
@@ -5955,28 +5955,28 @@
         <v>0.651</v>
       </c>
       <c r="M57">
-        <v>0.4238685</v>
+        <v>0.4315752</v>
       </c>
       <c r="N57">
-        <v>0.2271315</v>
+        <v>0.2194248</v>
       </c>
       <c r="O57">
-        <v>0.04542630000000001</v>
+        <v>0.04388496000000001</v>
       </c>
       <c r="P57">
-        <v>0.1817052</v>
+        <v>0.17553984</v>
       </c>
       <c r="Q57">
-        <v>0.3147052</v>
+        <v>0.30853984</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1983303088627764</v>
+        <v>0.2014463519447535</v>
       </c>
       <c r="T57">
-        <v>1.670269400548964</v>
+        <v>1.704391349487656</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.535853690472399</v>
+        <v>1.508427731713963</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1289563948556915</v>
+        <v>0.1572991223719853</v>
       </c>
       <c r="C58">
-        <v>3.21300776493843</v>
+        <v>1.108981496564246</v>
       </c>
       <c r="D58">
-        <v>7.94028776493843</v>
+        <v>5.921891496564246</v>
       </c>
       <c r="E58">
-        <v>4.41228</v>
+        <v>4.49791</v>
       </c>
       <c r="F58">
-        <v>4.79528</v>
+        <v>4.88091</v>
       </c>
       <c r="G58">
         <v>0.068</v>
@@ -6037,45 +6037,45 @@
         <v>0.651</v>
       </c>
       <c r="M58">
-        <v>0.4315752</v>
+        <v>0.7165175880000001</v>
       </c>
       <c r="N58">
-        <v>0.2194248</v>
+        <v>-0.06551758800000007</v>
       </c>
       <c r="O58">
-        <v>0.04388496000000001</v>
+        <v>-0.01310351760000002</v>
       </c>
       <c r="P58">
-        <v>0.17553984</v>
+        <v>-0.05241407040000005</v>
       </c>
       <c r="Q58">
-        <v>0.30853984</v>
+        <v>0.08058592959999995</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2014463519447535</v>
+        <v>0.2065769160643304</v>
       </c>
       <c r="T58">
-        <v>1.704391349487656</v>
+        <v>1.760573129491742</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2</v>
+        <v>0.1817122177885744</v>
       </c>
       <c r="W58">
-        <v>0.07199999999999999</v>
+        <v>0.1201246464286373</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.508427731713963</v>
+        <v>0.9085610889428718</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1572991223719853</v>
+        <v>0.1583091223719854</v>
       </c>
       <c r="C59">
-        <v>1.108981496564246</v>
+        <v>0.9701903813992478</v>
       </c>
       <c r="D59">
-        <v>5.921891496564246</v>
+        <v>5.868730381399248</v>
       </c>
       <c r="E59">
-        <v>4.49791</v>
+        <v>4.58354</v>
       </c>
       <c r="F59">
-        <v>4.88091</v>
+        <v>4.96654</v>
       </c>
       <c r="G59">
         <v>0.068</v>
@@ -6119,37 +6119,37 @@
         <v>0.651</v>
       </c>
       <c r="M59">
-        <v>0.7165175880000001</v>
+        <v>0.7290880720000001</v>
       </c>
       <c r="N59">
-        <v>-0.06551758800000007</v>
+        <v>-0.07808807200000012</v>
       </c>
       <c r="O59">
-        <v>-0.01310351760000002</v>
+        <v>-0.01561761440000002</v>
       </c>
       <c r="P59">
-        <v>-0.05241407040000005</v>
+        <v>-0.0624704576000001</v>
       </c>
       <c r="Q59">
-        <v>0.08058592959999995</v>
+        <v>0.07052954239999991</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2065769160643304</v>
+        <v>0.2104049378753859</v>
       </c>
       <c r="T59">
-        <v>1.760573129491742</v>
+        <v>1.802491537336784</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1817122177885744</v>
+        <v>0.1785792485163575</v>
       </c>
       <c r="W59">
-        <v>0.1201246464286373</v>
+        <v>0.1205845663177987</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9085610889428718</v>
+        <v>0.8928962425817877</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1583091223719853</v>
+        <v>0.1593191223719853</v>
       </c>
       <c r="C60">
-        <v>0.9701903813992514</v>
+        <v>0.8323452341944471</v>
       </c>
       <c r="D60">
-        <v>5.868730381399251</v>
+        <v>5.816515234194447</v>
       </c>
       <c r="E60">
-        <v>4.583539999999999</v>
+        <v>4.669169999999999</v>
       </c>
       <c r="F60">
-        <v>4.966539999999999</v>
+        <v>5.052169999999999</v>
       </c>
       <c r="G60">
         <v>0.068</v>
@@ -6201,37 +6201,37 @@
         <v>0.651</v>
       </c>
       <c r="M60">
-        <v>0.7290880719999999</v>
+        <v>0.741658556</v>
       </c>
       <c r="N60">
-        <v>-0.0780880719999999</v>
+        <v>-0.09065855599999995</v>
       </c>
       <c r="O60">
-        <v>-0.01561761439999998</v>
+        <v>-0.01813171119999999</v>
       </c>
       <c r="P60">
-        <v>-0.06247045759999992</v>
+        <v>-0.07252684479999996</v>
       </c>
       <c r="Q60">
-        <v>0.07052954240000009</v>
+        <v>0.06047315520000004</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2104049378753859</v>
+        <v>0.2144196924577124</v>
       </c>
       <c r="T60">
-        <v>1.802491537336783</v>
+        <v>1.84645474556451</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1785792485163576</v>
+        <v>0.1755524815923515</v>
       </c>
       <c r="W60">
-        <v>0.1205845663177987</v>
+        <v>0.1210288957022428</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.892896242581788</v>
+        <v>0.8777624079617576</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1593191223719853</v>
+        <v>0.1603291223719853</v>
       </c>
       <c r="C61">
-        <v>0.8323452341944471</v>
+        <v>0.6954210282766224</v>
       </c>
       <c r="D61">
-        <v>5.816515234194447</v>
+        <v>5.765221028276622</v>
       </c>
       <c r="E61">
-        <v>4.669169999999999</v>
+        <v>4.754799999999999</v>
       </c>
       <c r="F61">
-        <v>5.052169999999999</v>
+        <v>5.137799999999999</v>
       </c>
       <c r="G61">
         <v>0.068</v>
@@ -6283,37 +6283,37 @@
         <v>0.651</v>
       </c>
       <c r="M61">
-        <v>0.741658556</v>
+        <v>0.75422904</v>
       </c>
       <c r="N61">
-        <v>-0.09065855599999995</v>
+        <v>-0.10322904</v>
       </c>
       <c r="O61">
-        <v>-0.01813171119999999</v>
+        <v>-0.020645808</v>
       </c>
       <c r="P61">
-        <v>-0.07252684479999996</v>
+        <v>-0.08258323199999999</v>
       </c>
       <c r="Q61">
-        <v>0.06047315520000004</v>
+        <v>0.05041676800000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2144196924577124</v>
+        <v>0.2186351847691552</v>
       </c>
       <c r="T61">
-        <v>1.84645474556451</v>
+        <v>1.892616114203622</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1755524815923515</v>
+        <v>0.1726266068991457</v>
       </c>
       <c r="W61">
-        <v>0.1210288957022428</v>
+        <v>0.1214584141072054</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8777624079617576</v>
+        <v>0.8631330344957282</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1603291223719853</v>
+        <v>0.1613391223719853</v>
       </c>
       <c r="C62">
-        <v>0.6954210282766224</v>
+        <v>0.5593936120680043</v>
       </c>
       <c r="D62">
-        <v>5.765221028276622</v>
+        <v>5.714823612068004</v>
       </c>
       <c r="E62">
-        <v>4.754799999999999</v>
+        <v>4.84043</v>
       </c>
       <c r="F62">
-        <v>5.137799999999999</v>
+        <v>5.22343</v>
       </c>
       <c r="G62">
         <v>0.068</v>
@@ -6365,37 +6365,37 @@
         <v>0.651</v>
       </c>
       <c r="M62">
-        <v>0.75422904</v>
+        <v>0.766799524</v>
       </c>
       <c r="N62">
-        <v>-0.10322904</v>
+        <v>-0.1157995239999999</v>
       </c>
       <c r="O62">
-        <v>-0.020645808</v>
+        <v>-0.02315990479999999</v>
       </c>
       <c r="P62">
-        <v>-0.08258323199999999</v>
+        <v>-0.09263961919999994</v>
       </c>
       <c r="Q62">
-        <v>0.05041676800000001</v>
+        <v>0.04036038080000007</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2186351847691552</v>
+        <v>0.2230668561734925</v>
       </c>
       <c r="T62">
-        <v>1.892616114203622</v>
+        <v>1.941144732516537</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1726266068991457</v>
+        <v>0.1697966625237498</v>
       </c>
       <c r="W62">
-        <v>0.1214584141072054</v>
+        <v>0.1218738499415135</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8631330344957282</v>
+        <v>0.8489833126187492</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1613391223719853</v>
+        <v>0.1623491223719853</v>
       </c>
       <c r="C63">
-        <v>0.5593936120680043</v>
+        <v>0.4242396711689338</v>
       </c>
       <c r="D63">
-        <v>5.714823612068004</v>
+        <v>5.665299671168934</v>
       </c>
       <c r="E63">
-        <v>4.84043</v>
+        <v>4.92606</v>
       </c>
       <c r="F63">
-        <v>5.22343</v>
+        <v>5.30906</v>
       </c>
       <c r="G63">
         <v>0.068</v>
@@ -6447,37 +6447,37 @@
         <v>0.651</v>
       </c>
       <c r="M63">
-        <v>0.766799524</v>
+        <v>0.779370008</v>
       </c>
       <c r="N63">
-        <v>-0.1157995239999999</v>
+        <v>-0.128370008</v>
       </c>
       <c r="O63">
-        <v>-0.02315990479999999</v>
+        <v>-0.0256740016</v>
       </c>
       <c r="P63">
-        <v>-0.09263961919999994</v>
+        <v>-0.1026960064</v>
       </c>
       <c r="Q63">
-        <v>0.04036038080000007</v>
+        <v>0.03030399360000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2230668561734925</v>
+        <v>0.227731773441216</v>
       </c>
       <c r="T63">
-        <v>1.941144732516537</v>
+        <v>1.992227488635392</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1697966625237498</v>
+        <v>0.1670580066765926</v>
       </c>
       <c r="W63">
-        <v>0.1218738499415135</v>
+        <v>0.1222758846198762</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8489833126187492</v>
+        <v>0.8352900333829628</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1623491223719853</v>
+        <v>0.1633591223719853</v>
       </c>
       <c r="C64">
-        <v>0.4242396711689338</v>
+        <v>0.2899366923951145</v>
       </c>
       <c r="D64">
-        <v>5.665299671168934</v>
+        <v>5.616626692395114</v>
       </c>
       <c r="E64">
-        <v>4.92606</v>
+        <v>5.011689999999999</v>
       </c>
       <c r="F64">
-        <v>5.30906</v>
+        <v>5.394689999999999</v>
       </c>
       <c r="G64">
         <v>0.068</v>
@@ -6529,37 +6529,37 @@
         <v>0.651</v>
       </c>
       <c r="M64">
-        <v>0.779370008</v>
+        <v>0.7919404919999999</v>
       </c>
       <c r="N64">
-        <v>-0.128370008</v>
+        <v>-0.1409404919999999</v>
       </c>
       <c r="O64">
-        <v>-0.0256740016</v>
+        <v>-0.02818809839999999</v>
       </c>
       <c r="P64">
-        <v>-0.1026960064</v>
+        <v>-0.1127523935999999</v>
       </c>
       <c r="Q64">
-        <v>0.03030399360000002</v>
+        <v>0.02024760640000008</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.227731773441216</v>
+        <v>0.2326488483990867</v>
       </c>
       <c r="T64">
-        <v>1.992227488635392</v>
+        <v>2.046071474814727</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1670580066765926</v>
+        <v>0.1644062922849007</v>
       </c>
       <c r="W64">
-        <v>0.1222758846198762</v>
+        <v>0.1226651562925766</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8352900333829628</v>
+        <v>0.8220314614245032</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1633591223719853</v>
+        <v>0.1643691223719853</v>
       </c>
       <c r="C65">
-        <v>0.2899366923951145</v>
+        <v>0.1564629296528901</v>
       </c>
       <c r="D65">
-        <v>5.616626692395114</v>
+        <v>5.568782929652889</v>
       </c>
       <c r="E65">
-        <v>5.011689999999999</v>
+        <v>5.097319999999999</v>
       </c>
       <c r="F65">
-        <v>5.394689999999999</v>
+        <v>5.480319999999999</v>
       </c>
       <c r="G65">
         <v>0.068</v>
@@ -6611,37 +6611,37 @@
         <v>0.651</v>
       </c>
       <c r="M65">
-        <v>0.7919404919999999</v>
+        <v>0.8045109759999999</v>
       </c>
       <c r="N65">
-        <v>-0.1409404919999999</v>
+        <v>-0.1535109759999999</v>
       </c>
       <c r="O65">
-        <v>-0.02818809839999999</v>
+        <v>-0.03070219519999997</v>
       </c>
       <c r="P65">
-        <v>-0.1127523935999999</v>
+        <v>-0.1228087807999999</v>
       </c>
       <c r="Q65">
-        <v>0.02024760640000008</v>
+        <v>0.01019121920000013</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2326488483990867</v>
+        <v>0.2378390941879502</v>
       </c>
       <c r="T65">
-        <v>2.046071474814727</v>
+        <v>2.102906793559581</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1644062922849007</v>
+        <v>0.1618374439679491</v>
       </c>
       <c r="W65">
-        <v>0.1226651562925766</v>
+        <v>0.1230422632255051</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8220314614245032</v>
+        <v>0.8091872198397454</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1643691223719853</v>
+        <v>0.2026272876511117</v>
       </c>
       <c r="C66">
-        <v>0.1564629296528901</v>
+        <v>-1.287676937585303</v>
       </c>
       <c r="D66">
-        <v>5.568782929652889</v>
+        <v>4.210273062414696</v>
       </c>
       <c r="E66">
-        <v>5.097319999999999</v>
+        <v>5.182949999999999</v>
       </c>
       <c r="F66">
-        <v>5.480319999999999</v>
+        <v>5.565949999999999</v>
       </c>
       <c r="G66">
         <v>0.068</v>
@@ -6693,45 +6693,45 @@
         <v>0.651</v>
       </c>
       <c r="M66">
-        <v>0.8045109759999999</v>
+        <v>1.11764276</v>
       </c>
       <c r="N66">
-        <v>-0.1535109759999999</v>
+        <v>-0.4666427599999998</v>
       </c>
       <c r="O66">
-        <v>-0.03070219519999997</v>
+        <v>-0.09332855199999997</v>
       </c>
       <c r="P66">
-        <v>-0.1228087807999999</v>
+        <v>-0.3733142079999999</v>
       </c>
       <c r="Q66">
-        <v>0.01019121920000013</v>
+        <v>-0.2403142079999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2378390941879502</v>
+        <v>0.2494635405336812</v>
       </c>
       <c r="T66">
-        <v>2.102906793559581</v>
+        <v>2.230199245626043</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1618374439679491</v>
+        <v>0.1164951849193744</v>
       </c>
       <c r="W66">
-        <v>0.1230422632255051</v>
+        <v>0.1774077668681896</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8091872198397454</v>
+        <v>0.5824759245968723</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2026272876511117</v>
+        <v>0.2041772876511117</v>
       </c>
       <c r="C67">
-        <v>-1.287676937585303</v>
+        <v>-1.414511856191555</v>
       </c>
       <c r="D67">
-        <v>4.210273062414696</v>
+        <v>4.169068143808444</v>
       </c>
       <c r="E67">
-        <v>5.182949999999999</v>
+        <v>5.268579999999999</v>
       </c>
       <c r="F67">
-        <v>5.565949999999999</v>
+        <v>5.651579999999999</v>
       </c>
       <c r="G67">
         <v>0.068</v>
@@ -6775,37 +6775,37 @@
         <v>0.651</v>
       </c>
       <c r="M67">
-        <v>1.11764276</v>
+        <v>1.134837264</v>
       </c>
       <c r="N67">
-        <v>-0.4666427599999998</v>
+        <v>-0.4838372639999999</v>
       </c>
       <c r="O67">
-        <v>-0.09332855199999997</v>
+        <v>-0.09676745279999999</v>
       </c>
       <c r="P67">
-        <v>-0.3733142079999999</v>
+        <v>-0.3870698111999999</v>
       </c>
       <c r="Q67">
-        <v>-0.2403142079999999</v>
+        <v>-0.2540698111999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2494635405336812</v>
+        <v>0.2554536446670248</v>
       </c>
       <c r="T67">
-        <v>2.230199245626043</v>
+        <v>2.295793341085633</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1164951849193744</v>
+        <v>0.11473010635999</v>
       </c>
       <c r="W67">
-        <v>0.1774077668681896</v>
+        <v>0.177762194642914</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5824759245968723</v>
+        <v>0.5736505317999498</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2041772876511117</v>
+        <v>0.2057272876511117</v>
       </c>
       <c r="C68">
-        <v>-1.414511856191555</v>
+        <v>-1.540548066525093</v>
       </c>
       <c r="D68">
-        <v>4.169068143808444</v>
+        <v>4.128661933474906</v>
       </c>
       <c r="E68">
-        <v>5.268579999999999</v>
+        <v>5.354209999999999</v>
       </c>
       <c r="F68">
-        <v>5.651579999999999</v>
+        <v>5.737209999999999</v>
       </c>
       <c r="G68">
         <v>0.068</v>
@@ -6857,37 +6857,37 @@
         <v>0.651</v>
       </c>
       <c r="M68">
-        <v>1.134837264</v>
+        <v>1.152031768</v>
       </c>
       <c r="N68">
-        <v>-0.4838372639999999</v>
+        <v>-0.5010317679999998</v>
       </c>
       <c r="O68">
-        <v>-0.09676745279999999</v>
+        <v>-0.1002063536</v>
       </c>
       <c r="P68">
-        <v>-0.3870698111999999</v>
+        <v>-0.4008254143999999</v>
       </c>
       <c r="Q68">
-        <v>-0.2540698111999999</v>
+        <v>-0.2678254143999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2554536446670248</v>
+        <v>0.2618067854145104</v>
       </c>
       <c r="T68">
-        <v>2.295793341085633</v>
+        <v>2.365362836270047</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.11473010635999</v>
+        <v>0.113017716712826</v>
       </c>
       <c r="W68">
-        <v>0.177762194642914</v>
+        <v>0.1781060424840646</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5736505317999498</v>
+        <v>0.5650885835641297</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2057272876511117</v>
+        <v>0.2072772876511117</v>
       </c>
       <c r="C69">
-        <v>-1.540548066525093</v>
+        <v>-1.665808568684088</v>
       </c>
       <c r="D69">
-        <v>4.128661933474906</v>
+        <v>4.089031431315911</v>
       </c>
       <c r="E69">
-        <v>5.354209999999999</v>
+        <v>5.439839999999999</v>
       </c>
       <c r="F69">
-        <v>5.737209999999999</v>
+        <v>5.822839999999999</v>
       </c>
       <c r="G69">
         <v>0.068</v>
@@ -6939,37 +6939,37 @@
         <v>0.651</v>
       </c>
       <c r="M69">
-        <v>1.152031768</v>
+        <v>1.169226272</v>
       </c>
       <c r="N69">
-        <v>-0.5010317679999998</v>
+        <v>-0.5182262719999999</v>
       </c>
       <c r="O69">
-        <v>-0.1002063536</v>
+        <v>-0.1036452544</v>
       </c>
       <c r="P69">
-        <v>-0.4008254143999999</v>
+        <v>-0.4145810175999999</v>
       </c>
       <c r="Q69">
-        <v>-0.2678254143999999</v>
+        <v>-0.2815810175999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2618067854145104</v>
+        <v>0.2685569974587139</v>
       </c>
       <c r="T69">
-        <v>2.365362836270047</v>
+        <v>2.439280424903485</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.113017716712826</v>
+        <v>0.1113556914670491</v>
       </c>
       <c r="W69">
-        <v>0.1781060424840646</v>
+        <v>0.1784397771534166</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5650885835641297</v>
+        <v>0.5567784573352454</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2072772876511117</v>
+        <v>0.2088272876511116</v>
       </c>
       <c r="C70">
-        <v>-1.665808568684088</v>
+        <v>-1.790315488062783</v>
       </c>
       <c r="D70">
-        <v>4.089031431315911</v>
+        <v>4.050154511937217</v>
       </c>
       <c r="E70">
-        <v>5.439839999999999</v>
+        <v>5.525469999999999</v>
       </c>
       <c r="F70">
-        <v>5.822839999999999</v>
+        <v>5.908469999999999</v>
       </c>
       <c r="G70">
         <v>0.068</v>
@@ -7021,37 +7021,37 @@
         <v>0.651</v>
       </c>
       <c r="M70">
-        <v>1.169226272</v>
+        <v>1.186420776</v>
       </c>
       <c r="N70">
-        <v>-0.5182262719999999</v>
+        <v>-0.5354207759999998</v>
       </c>
       <c r="O70">
-        <v>-0.1036452544</v>
+        <v>-0.1070841552</v>
       </c>
       <c r="P70">
-        <v>-0.4145810175999999</v>
+        <v>-0.4283366207999998</v>
       </c>
       <c r="Q70">
-        <v>-0.2815810175999999</v>
+        <v>-0.2953366207999998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2685569974587139</v>
+        <v>0.2757427070541562</v>
       </c>
       <c r="T70">
-        <v>2.439280424903485</v>
+        <v>2.517966890222953</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1113556914670491</v>
+        <v>0.1097418408660774</v>
       </c>
       <c r="W70">
-        <v>0.1784397771534166</v>
+        <v>0.1787638383540917</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5567784573352454</v>
+        <v>0.5487092043303868</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2088272876511116</v>
+        <v>0.2103772876511117</v>
       </c>
       <c r="C71">
-        <v>-1.790315488062783</v>
+        <v>-1.914090116541599</v>
       </c>
       <c r="D71">
-        <v>4.050154511937217</v>
+        <v>4.012009883458401</v>
       </c>
       <c r="E71">
-        <v>5.525469999999999</v>
+        <v>5.6111</v>
       </c>
       <c r="F71">
-        <v>5.908469999999999</v>
+        <v>5.9941</v>
       </c>
       <c r="G71">
         <v>0.068</v>
@@ -7103,37 +7103,37 @@
         <v>0.651</v>
       </c>
       <c r="M71">
-        <v>1.186420776</v>
+        <v>1.20361528</v>
       </c>
       <c r="N71">
-        <v>-0.5354207759999998</v>
+        <v>-0.5526152799999999</v>
       </c>
       <c r="O71">
-        <v>-0.1070841552</v>
+        <v>-0.110523056</v>
       </c>
       <c r="P71">
-        <v>-0.4283366207999998</v>
+        <v>-0.4420922239999999</v>
       </c>
       <c r="Q71">
-        <v>-0.2953366207999998</v>
+        <v>-0.3090922239999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2757427070541562</v>
+        <v>0.2834074639559614</v>
       </c>
       <c r="T71">
-        <v>2.517966890222953</v>
+        <v>2.601899119897051</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1097418408660774</v>
+        <v>0.1081741002822763</v>
       </c>
       <c r="W71">
-        <v>0.1787638383540917</v>
+        <v>0.1790786406633189</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5487092043303868</v>
+        <v>0.5408705014113813</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2103772876511117</v>
+        <v>0.2119272876511117</v>
       </c>
       <c r="C72">
-        <v>-1.914090116541599</v>
+        <v>-2.037152951371361</v>
       </c>
       <c r="D72">
-        <v>4.012009883458401</v>
+        <v>3.974577048628639</v>
       </c>
       <c r="E72">
-        <v>5.6111</v>
+        <v>5.69673</v>
       </c>
       <c r="F72">
-        <v>5.9941</v>
+        <v>6.07973</v>
       </c>
       <c r="G72">
         <v>0.068</v>
@@ -7185,37 +7185,37 @@
         <v>0.651</v>
       </c>
       <c r="M72">
-        <v>1.20361528</v>
+        <v>1.220809784</v>
       </c>
       <c r="N72">
-        <v>-0.5526152799999999</v>
+        <v>-0.569809784</v>
       </c>
       <c r="O72">
-        <v>-0.110523056</v>
+        <v>-0.1139619568</v>
       </c>
       <c r="P72">
-        <v>-0.4420922239999999</v>
+        <v>-0.4558478272000001</v>
       </c>
       <c r="Q72">
-        <v>-0.3090922239999999</v>
+        <v>-0.3228478272</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2834074639559614</v>
+        <v>0.2916008247820291</v>
       </c>
       <c r="T72">
-        <v>2.601899119897051</v>
+        <v>2.691619779203847</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1081741002822763</v>
+        <v>0.1066505214050611</v>
       </c>
       <c r="W72">
-        <v>0.1790786406633189</v>
+        <v>0.1793845753018637</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5408705014113813</v>
+        <v>0.5332526070253054</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2119272876511117</v>
+        <v>0.2134772876511117</v>
       </c>
       <c r="C73">
-        <v>-2.03715295137136</v>
+        <v>-2.159523731900878</v>
       </c>
       <c r="D73">
-        <v>3.974577048628639</v>
+        <v>3.937836268099121</v>
       </c>
       <c r="E73">
-        <v>5.696729999999999</v>
+        <v>5.782359999999999</v>
       </c>
       <c r="F73">
-        <v>6.079729999999999</v>
+        <v>6.165359999999999</v>
       </c>
       <c r="G73">
         <v>0.068</v>
@@ -7267,37 +7267,37 @@
         <v>0.651</v>
       </c>
       <c r="M73">
-        <v>1.220809784</v>
+        <v>1.238004288</v>
       </c>
       <c r="N73">
-        <v>-0.5698097839999998</v>
+        <v>-0.5870042879999997</v>
       </c>
       <c r="O73">
-        <v>-0.1139619568</v>
+        <v>-0.1174008575999999</v>
       </c>
       <c r="P73">
-        <v>-0.4558478271999998</v>
+        <v>-0.4696034303999997</v>
       </c>
       <c r="Q73">
-        <v>-0.3228478271999998</v>
+        <v>-0.3366034303999997</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.291600824782029</v>
+        <v>0.3003794256671015</v>
       </c>
       <c r="T73">
-        <v>2.691619779203846</v>
+        <v>2.787749057032554</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1066505214050611</v>
+        <v>0.1051692641633242</v>
       </c>
       <c r="W73">
-        <v>0.1793845753018637</v>
+        <v>0.1796820117560045</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5332526070253055</v>
+        <v>0.5258463208166207</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2134772876511117</v>
+        <v>0.2150272876511117</v>
       </c>
       <c r="C74">
-        <v>-2.159523731900878</v>
+        <v>-2.281221474286121</v>
       </c>
       <c r="D74">
-        <v>3.937836268099121</v>
+        <v>3.901768525713878</v>
       </c>
       <c r="E74">
-        <v>5.782359999999999</v>
+        <v>5.867989999999999</v>
       </c>
       <c r="F74">
-        <v>6.165359999999999</v>
+        <v>6.250989999999999</v>
       </c>
       <c r="G74">
         <v>0.068</v>
@@ -7349,37 +7349,37 @@
         <v>0.651</v>
       </c>
       <c r="M74">
-        <v>1.238004288</v>
+        <v>1.255198792</v>
       </c>
       <c r="N74">
-        <v>-0.5870042879999997</v>
+        <v>-0.6041987919999998</v>
       </c>
       <c r="O74">
-        <v>-0.1174008575999999</v>
+        <v>-0.1208397584</v>
       </c>
       <c r="P74">
-        <v>-0.4696034303999997</v>
+        <v>-0.4833590335999999</v>
       </c>
       <c r="Q74">
-        <v>-0.3366034303999997</v>
+        <v>-0.3503590335999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3003794256671015</v>
+        <v>0.3098082932844015</v>
       </c>
       <c r="T74">
-        <v>2.787749057032554</v>
+        <v>2.890999022107834</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1051692641633242</v>
+        <v>0.1037285893117718</v>
       </c>
       <c r="W74">
-        <v>0.1796820117560045</v>
+        <v>0.1799712992661962</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5258463208166207</v>
+        <v>0.5186429465588588</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2150272876511117</v>
+        <v>0.2165772876511117</v>
       </c>
       <c r="C75">
-        <v>-2.281221474286121</v>
+        <v>-2.402264504309245</v>
       </c>
       <c r="D75">
-        <v>3.901768525713878</v>
+        <v>3.866355495690754</v>
       </c>
       <c r="E75">
-        <v>5.867989999999999</v>
+        <v>5.953619999999999</v>
       </c>
       <c r="F75">
-        <v>6.250989999999999</v>
+        <v>6.336619999999999</v>
       </c>
       <c r="G75">
         <v>0.068</v>
@@ -7431,37 +7431,37 @@
         <v>0.651</v>
       </c>
       <c r="M75">
-        <v>1.255198792</v>
+        <v>1.272393296</v>
       </c>
       <c r="N75">
-        <v>-0.6041987919999998</v>
+        <v>-0.6213932959999999</v>
       </c>
       <c r="O75">
-        <v>-0.1208397584</v>
+        <v>-0.1242786592</v>
       </c>
       <c r="P75">
-        <v>-0.4833590335999999</v>
+        <v>-0.4971146368</v>
       </c>
       <c r="Q75">
-        <v>-0.3503590335999999</v>
+        <v>-0.3641146367999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3098082932844015</v>
+        <v>0.3199624584107247</v>
       </c>
       <c r="T75">
-        <v>2.890999022107834</v>
+        <v>3.002191292188904</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1037285893117718</v>
+        <v>0.1023268516183694</v>
       </c>
       <c r="W75">
-        <v>0.1799712992661962</v>
+        <v>0.1802527681950314</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5186429465588588</v>
+        <v>0.5116342580918471</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2165772876511117</v>
+        <v>0.2181272876511117</v>
       </c>
       <c r="C76">
-        <v>-2.402264504309245</v>
+        <v>-2.522670488426477</v>
       </c>
       <c r="D76">
-        <v>3.866355495690754</v>
+        <v>3.831579511573522</v>
       </c>
       <c r="E76">
-        <v>5.953619999999999</v>
+        <v>6.039249999999999</v>
       </c>
       <c r="F76">
-        <v>6.336619999999999</v>
+        <v>6.422249999999999</v>
       </c>
       <c r="G76">
         <v>0.068</v>
@@ -7513,37 +7513,37 @@
         <v>0.651</v>
       </c>
       <c r="M76">
-        <v>1.272393296</v>
+        <v>1.2895878</v>
       </c>
       <c r="N76">
-        <v>-0.6213932959999999</v>
+        <v>-0.6385877999999998</v>
       </c>
       <c r="O76">
-        <v>-0.1242786592</v>
+        <v>-0.12771756</v>
       </c>
       <c r="P76">
-        <v>-0.4971146368</v>
+        <v>-0.5108702399999998</v>
       </c>
       <c r="Q76">
-        <v>-0.3641146367999999</v>
+        <v>-0.3778702399999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3199624584107247</v>
+        <v>0.3309289567471537</v>
       </c>
       <c r="T76">
-        <v>3.002191292188904</v>
+        <v>3.122278943876461</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1023268516183694</v>
+        <v>0.1009624935967912</v>
       </c>
       <c r="W76">
-        <v>0.1802527681950314</v>
+        <v>0.1805267312857643</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5116342580918471</v>
+        <v>0.5048124679839558</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2181272876511117</v>
+        <v>0.2471440982881983</v>
       </c>
       <c r="C77">
-        <v>-2.522670488426477</v>
+        <v>-3.160490585248334</v>
       </c>
       <c r="D77">
-        <v>3.831579511573522</v>
+        <v>3.279389414751665</v>
       </c>
       <c r="E77">
-        <v>6.039249999999999</v>
+        <v>6.124879999999999</v>
       </c>
       <c r="F77">
-        <v>6.422249999999999</v>
+        <v>6.507879999999999</v>
       </c>
       <c r="G77">
         <v>0.068</v>
@@ -7595,45 +7595,45 @@
         <v>0.651</v>
       </c>
       <c r="M77">
-        <v>1.2895878</v>
+        <v>1.534558104</v>
       </c>
       <c r="N77">
-        <v>-0.6385877999999998</v>
+        <v>-0.8835581039999998</v>
       </c>
       <c r="O77">
-        <v>-0.12771756</v>
+        <v>-0.1767116208</v>
       </c>
       <c r="P77">
-        <v>-0.5108702399999998</v>
+        <v>-0.7068464831999999</v>
       </c>
       <c r="Q77">
-        <v>-0.3778702399999998</v>
+        <v>-0.5738464831999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3309289567471537</v>
+        <v>0.3464210409328126</v>
       </c>
       <c r="T77">
-        <v>3.122278943876461</v>
+        <v>3.291923615541775</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1009624935967912</v>
+        <v>0.08484527217354555</v>
       </c>
       <c r="W77">
-        <v>0.1805267312857643</v>
+        <v>0.215793484821478</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5048124679839558</v>
+        <v>0.4242263608677278</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2471440982881983</v>
+        <v>0.2490440982881983</v>
       </c>
       <c r="C78">
-        <v>-3.160490585248334</v>
+        <v>-3.276777514234252</v>
       </c>
       <c r="D78">
-        <v>3.279389414751665</v>
+        <v>3.248732485765748</v>
       </c>
       <c r="E78">
-        <v>6.124879999999999</v>
+        <v>6.210509999999999</v>
       </c>
       <c r="F78">
-        <v>6.507879999999999</v>
+        <v>6.593509999999999</v>
       </c>
       <c r="G78">
         <v>0.068</v>
@@ -7677,37 +7677,37 @@
         <v>0.651</v>
       </c>
       <c r="M78">
-        <v>1.534558104</v>
+        <v>1.554749658</v>
       </c>
       <c r="N78">
-        <v>-0.8835581039999998</v>
+        <v>-0.903749658</v>
       </c>
       <c r="O78">
-        <v>-0.1767116208</v>
+        <v>-0.1807499316</v>
       </c>
       <c r="P78">
-        <v>-0.7068464831999999</v>
+        <v>-0.7229997264</v>
       </c>
       <c r="Q78">
-        <v>-0.5738464831999999</v>
+        <v>-0.5899997264</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3464210409328126</v>
+        <v>0.3594915209733697</v>
       </c>
       <c r="T78">
-        <v>3.291923615541775</v>
+        <v>3.435050729260983</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08484527217354555</v>
+        <v>0.08374338552194105</v>
       </c>
       <c r="W78">
-        <v>0.215793484821478</v>
+        <v>0.2160533096939263</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4242263608677278</v>
+        <v>0.4187169276097052</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2490440982881983</v>
+        <v>0.2509440982881983</v>
       </c>
       <c r="C79">
-        <v>-3.276777514234252</v>
+        <v>-3.392496567609228</v>
       </c>
       <c r="D79">
-        <v>3.248732485765748</v>
+        <v>3.218643432390772</v>
       </c>
       <c r="E79">
-        <v>6.210509999999999</v>
+        <v>6.296139999999999</v>
       </c>
       <c r="F79">
-        <v>6.593509999999999</v>
+        <v>6.679139999999999</v>
       </c>
       <c r="G79">
         <v>0.068</v>
@@ -7759,37 +7759,37 @@
         <v>0.651</v>
       </c>
       <c r="M79">
-        <v>1.554749658</v>
+        <v>1.574941212</v>
       </c>
       <c r="N79">
-        <v>-0.903749658</v>
+        <v>-0.9239412119999999</v>
       </c>
       <c r="O79">
-        <v>-0.1807499316</v>
+        <v>-0.1847882424</v>
       </c>
       <c r="P79">
-        <v>-0.7229997264</v>
+        <v>-0.7391529695999999</v>
       </c>
       <c r="Q79">
-        <v>-0.5899997264</v>
+        <v>-0.6061529695999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3594915209733697</v>
+        <v>0.3737502264721592</v>
       </c>
       <c r="T79">
-        <v>3.435050729260983</v>
+        <v>3.591189398772845</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08374338552194105</v>
+        <v>0.08266975237422386</v>
       </c>
       <c r="W79">
-        <v>0.2160533096939263</v>
+        <v>0.216306472390158</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4187169276097052</v>
+        <v>0.4133487618711194</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2509440982881983</v>
+        <v>0.2528440982881983</v>
       </c>
       <c r="C80">
-        <v>-3.392496567609228</v>
+        <v>-3.507663379197212</v>
       </c>
       <c r="D80">
-        <v>3.218643432390772</v>
+        <v>3.189106620802788</v>
       </c>
       <c r="E80">
-        <v>6.296139999999999</v>
+        <v>6.381769999999999</v>
       </c>
       <c r="F80">
-        <v>6.679139999999999</v>
+        <v>6.76477</v>
       </c>
       <c r="G80">
         <v>0.068</v>
@@ -7841,37 +7841,37 @@
         <v>0.651</v>
       </c>
       <c r="M80">
-        <v>1.574941212</v>
+        <v>1.595132766</v>
       </c>
       <c r="N80">
-        <v>-0.9239412119999999</v>
+        <v>-0.9441327659999998</v>
       </c>
       <c r="O80">
-        <v>-0.1847882424</v>
+        <v>-0.1888265532</v>
       </c>
       <c r="P80">
-        <v>-0.7391529695999999</v>
+        <v>-0.7553062127999999</v>
       </c>
       <c r="Q80">
-        <v>-0.6061529695999999</v>
+        <v>-0.6223062127999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3737502264721592</v>
+        <v>0.3893669039232145</v>
       </c>
       <c r="T80">
-        <v>3.591189398772845</v>
+        <v>3.762198417762029</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08266975237422386</v>
+        <v>0.08162329981252484</v>
       </c>
       <c r="W80">
-        <v>0.216306472390158</v>
+        <v>0.2165532259042067</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4133487618711194</v>
+        <v>0.4081164990626241</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2528440982881983</v>
+        <v>0.2547440982881983</v>
       </c>
       <c r="C81">
-        <v>-3.507663379197212</v>
+        <v>-3.622293014167364</v>
       </c>
       <c r="D81">
-        <v>3.189106620802788</v>
+        <v>3.160106985832636</v>
       </c>
       <c r="E81">
-        <v>6.381769999999999</v>
+        <v>6.4674</v>
       </c>
       <c r="F81">
-        <v>6.76477</v>
+        <v>6.8504</v>
       </c>
       <c r="G81">
         <v>0.068</v>
@@ -7923,37 +7923,37 @@
         <v>0.651</v>
       </c>
       <c r="M81">
-        <v>1.595132766</v>
+        <v>1.61532432</v>
       </c>
       <c r="N81">
-        <v>-0.9441327659999998</v>
+        <v>-0.96432432</v>
       </c>
       <c r="O81">
-        <v>-0.1888265532</v>
+        <v>-0.192864864</v>
       </c>
       <c r="P81">
-        <v>-0.7553062127999999</v>
+        <v>-0.771459456</v>
       </c>
       <c r="Q81">
-        <v>-0.6223062127999999</v>
+        <v>-0.638459456</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3893669039232145</v>
+        <v>0.4065452491193752</v>
       </c>
       <c r="T81">
-        <v>3.762198417762029</v>
+        <v>3.950308338650131</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08162329981252484</v>
+        <v>0.08060300856486827</v>
       </c>
       <c r="W81">
-        <v>0.2165532259042067</v>
+        <v>0.2167938105804041</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4081164990626241</v>
+        <v>0.4030150428243413</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2547440982881983</v>
+        <v>0.2566440982881983</v>
       </c>
       <c r="C82">
-        <v>-3.622293014167364</v>
+        <v>-3.736399994655928</v>
       </c>
       <c r="D82">
-        <v>3.160106985832636</v>
+        <v>3.131630005344071</v>
       </c>
       <c r="E82">
-        <v>6.4674</v>
+        <v>6.55303</v>
       </c>
       <c r="F82">
-        <v>6.8504</v>
+        <v>6.93603</v>
       </c>
       <c r="G82">
         <v>0.068</v>
@@ -8005,37 +8005,37 @@
         <v>0.651</v>
       </c>
       <c r="M82">
-        <v>1.61532432</v>
+        <v>1.635515874</v>
       </c>
       <c r="N82">
-        <v>-0.96432432</v>
+        <v>-0.984515874</v>
       </c>
       <c r="O82">
-        <v>-0.192864864</v>
+        <v>-0.1969031748</v>
       </c>
       <c r="P82">
-        <v>-0.771459456</v>
+        <v>-0.7876126992</v>
       </c>
       <c r="Q82">
-        <v>-0.638459456</v>
+        <v>-0.6546126992</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4065452491193752</v>
+        <v>0.4255318411782897</v>
       </c>
       <c r="T82">
-        <v>3.950308338650131</v>
+        <v>4.158219303842243</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08060300856486827</v>
+        <v>0.07960790969369706</v>
       </c>
       <c r="W82">
-        <v>0.2167938105804041</v>
+        <v>0.2170284548942263</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4030150428243413</v>
+        <v>0.3980395484684852</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2566440982881983</v>
+        <v>0.2585440982881982</v>
       </c>
       <c r="C83">
-        <v>-3.736399994655928</v>
+        <v>-3.849998324015143</v>
       </c>
       <c r="D83">
-        <v>3.131630005344071</v>
+        <v>3.103661675984856</v>
       </c>
       <c r="E83">
-        <v>6.55303</v>
+        <v>6.63866</v>
       </c>
       <c r="F83">
-        <v>6.93603</v>
+        <v>7.02166</v>
       </c>
       <c r="G83">
         <v>0.068</v>
@@ -8087,37 +8087,37 @@
         <v>0.651</v>
       </c>
       <c r="M83">
-        <v>1.635515874</v>
+        <v>1.655707428</v>
       </c>
       <c r="N83">
-        <v>-0.984515874</v>
+        <v>-1.004707428</v>
       </c>
       <c r="O83">
-        <v>-0.1969031748</v>
+        <v>-0.2009414856</v>
       </c>
       <c r="P83">
-        <v>-0.7876126992</v>
+        <v>-0.8037659423999999</v>
       </c>
       <c r="Q83">
-        <v>-0.6546126992</v>
+        <v>-0.6707659423999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4255318411782897</v>
+        <v>0.4466280545770836</v>
       </c>
       <c r="T83">
-        <v>4.158219303842243</v>
+        <v>4.389231487389035</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07960790969369706</v>
+        <v>0.07863708152670075</v>
       </c>
       <c r="W83">
-        <v>0.2170284548942263</v>
+        <v>0.217257376176004</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3980395484684852</v>
+        <v>0.3931854076335037</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2585440982881982</v>
+        <v>0.2604440982881983</v>
       </c>
       <c r="C84">
-        <v>-3.849998324015143</v>
+        <v>-3.963101509774267</v>
       </c>
       <c r="D84">
-        <v>3.103661675984856</v>
+        <v>3.076188490225733</v>
       </c>
       <c r="E84">
-        <v>6.63866</v>
+        <v>6.72429</v>
       </c>
       <c r="F84">
-        <v>7.02166</v>
+        <v>7.10729</v>
       </c>
       <c r="G84">
         <v>0.068</v>
@@ -8169,37 +8169,37 @@
         <v>0.651</v>
       </c>
       <c r="M84">
-        <v>1.655707428</v>
+        <v>1.675898982</v>
       </c>
       <c r="N84">
-        <v>-1.004707428</v>
+        <v>-1.024898982</v>
       </c>
       <c r="O84">
-        <v>-0.2009414856</v>
+        <v>-0.2049797964</v>
       </c>
       <c r="P84">
-        <v>-0.8037659423999999</v>
+        <v>-0.8199191856000001</v>
       </c>
       <c r="Q84">
-        <v>-0.6707659423999999</v>
+        <v>-0.6869191856000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4466280545770836</v>
+        <v>0.4702061754345591</v>
       </c>
       <c r="T84">
-        <v>4.389231487389035</v>
+        <v>4.647421574882507</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07863708152670075</v>
+        <v>0.07768964680951158</v>
       </c>
       <c r="W84">
-        <v>0.217257376176004</v>
+        <v>0.2174807812823172</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3931854076335037</v>
+        <v>0.3884482340475579</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2604440982881983</v>
+        <v>0.2623440982881983</v>
       </c>
       <c r="C85">
-        <v>-3.963101509774267</v>
+        <v>-4.075722585391809</v>
       </c>
       <c r="D85">
-        <v>3.076188490225733</v>
+        <v>3.049197414608191</v>
       </c>
       <c r="E85">
-        <v>6.72429</v>
+        <v>6.80992</v>
       </c>
       <c r="F85">
-        <v>7.10729</v>
+        <v>7.19292</v>
       </c>
       <c r="G85">
         <v>0.068</v>
@@ -8251,37 +8251,37 @@
         <v>0.651</v>
       </c>
       <c r="M85">
-        <v>1.675898982</v>
+        <v>1.696090536</v>
       </c>
       <c r="N85">
-        <v>-1.024898982</v>
+        <v>-1.045090536</v>
       </c>
       <c r="O85">
-        <v>-0.2049797964</v>
+        <v>-0.2090181072</v>
       </c>
       <c r="P85">
-        <v>-0.8199191856000001</v>
+        <v>-0.8360724288</v>
       </c>
       <c r="Q85">
-        <v>-0.6869191856000001</v>
+        <v>-0.7030724288</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4702061754345591</v>
+        <v>0.4967315613992192</v>
       </c>
       <c r="T85">
-        <v>4.647421574882507</v>
+        <v>4.937885423312665</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07768964680951158</v>
+        <v>0.0767647700617793</v>
       </c>
       <c r="W85">
-        <v>0.2174807812823172</v>
+        <v>0.2176988672194325</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3884482340475579</v>
+        <v>0.3838238503088965</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2623440982881983</v>
+        <v>0.2642440982881983</v>
       </c>
       <c r="C86">
-        <v>-4.075722585391808</v>
+        <v>-4.187874130872574</v>
       </c>
       <c r="D86">
-        <v>3.049197414608191</v>
+        <v>3.022675869127425</v>
       </c>
       <c r="E86">
-        <v>6.809919999999999</v>
+        <v>6.895549999999999</v>
       </c>
       <c r="F86">
-        <v>7.192919999999999</v>
+        <v>7.278549999999999</v>
       </c>
       <c r="G86">
         <v>0.068</v>
@@ -8333,37 +8333,37 @@
         <v>0.651</v>
       </c>
       <c r="M86">
-        <v>1.696090536</v>
+        <v>1.71628209</v>
       </c>
       <c r="N86">
-        <v>-1.045090536</v>
+        <v>-1.06528209</v>
       </c>
       <c r="O86">
-        <v>-0.2090181072</v>
+        <v>-0.213056418</v>
       </c>
       <c r="P86">
-        <v>-0.8360724287999999</v>
+        <v>-0.852225672</v>
       </c>
       <c r="Q86">
-        <v>-0.7030724287999999</v>
+        <v>-0.719225672</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4967315613992188</v>
+        <v>0.5267936654925001</v>
       </c>
       <c r="T86">
-        <v>4.937885423312661</v>
+        <v>5.267077784866839</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07676477006177931</v>
+        <v>0.07586165511987603</v>
       </c>
       <c r="W86">
-        <v>0.2176988672194325</v>
+        <v>0.2179118217227332</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3838238503088965</v>
+        <v>0.3793082755993801</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2642440982881983</v>
+        <v>0.2661440982881983</v>
       </c>
       <c r="C87">
-        <v>-4.187874130872574</v>
+        <v>-4.299568292318053</v>
       </c>
       <c r="D87">
-        <v>3.022675869127425</v>
+        <v>2.996611707681946</v>
       </c>
       <c r="E87">
-        <v>6.895549999999999</v>
+        <v>6.981179999999999</v>
       </c>
       <c r="F87">
-        <v>7.278549999999999</v>
+        <v>7.364179999999999</v>
       </c>
       <c r="G87">
         <v>0.068</v>
@@ -8415,37 +8415,37 @@
         <v>0.651</v>
       </c>
       <c r="M87">
-        <v>1.71628209</v>
+        <v>1.736473644</v>
       </c>
       <c r="N87">
-        <v>-1.06528209</v>
+        <v>-1.085473644</v>
       </c>
       <c r="O87">
-        <v>-0.213056418</v>
+        <v>-0.2170947288</v>
       </c>
       <c r="P87">
-        <v>-0.852225672</v>
+        <v>-0.8683789151999999</v>
       </c>
       <c r="Q87">
-        <v>-0.719225672</v>
+        <v>-0.7353789151999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5267936654925001</v>
+        <v>0.5611503558848215</v>
       </c>
       <c r="T87">
-        <v>5.267077784866839</v>
+        <v>5.643297626643042</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07586165511987603</v>
+        <v>0.07497954285104025</v>
       </c>
       <c r="W87">
-        <v>0.2179118217227332</v>
+        <v>0.2181198237957247</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3793082755993801</v>
+        <v>0.3748977142552012</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2661440982881983</v>
+        <v>0.2680440982881983</v>
       </c>
       <c r="C88">
-        <v>-4.299568292318053</v>
+        <v>-4.410816800473949</v>
       </c>
       <c r="D88">
-        <v>2.996611707681946</v>
+        <v>2.97099319952605</v>
       </c>
       <c r="E88">
-        <v>6.981179999999999</v>
+        <v>7.066809999999999</v>
       </c>
       <c r="F88">
-        <v>7.364179999999999</v>
+        <v>7.449809999999999</v>
       </c>
       <c r="G88">
         <v>0.068</v>
@@ -8497,37 +8497,37 @@
         <v>0.651</v>
       </c>
       <c r="M88">
-        <v>1.736473644</v>
+        <v>1.756665198</v>
       </c>
       <c r="N88">
-        <v>-1.085473644</v>
+        <v>-1.105665198</v>
       </c>
       <c r="O88">
-        <v>-0.2170947288</v>
+        <v>-0.2211330396</v>
       </c>
       <c r="P88">
-        <v>-0.8683789151999999</v>
+        <v>-0.8845321583999999</v>
       </c>
       <c r="Q88">
-        <v>-0.7353789151999999</v>
+        <v>-0.7515321583999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5611503558848215</v>
+        <v>0.6007926909528847</v>
       </c>
       <c r="T88">
-        <v>5.643297626643042</v>
+        <v>6.077397444077122</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07497954285104025</v>
+        <v>0.07411770902516622</v>
       </c>
       <c r="W88">
-        <v>0.2181198237957247</v>
+        <v>0.2183230442118658</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3748977142552012</v>
+        <v>0.3705885451258312</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2680440982881983</v>
+        <v>0.2699440982881983</v>
       </c>
       <c r="C89">
-        <v>-4.410816800473949</v>
+        <v>-4.521630988334389</v>
       </c>
       <c r="D89">
-        <v>2.97099319952605</v>
+        <v>2.945809011665609</v>
       </c>
       <c r="E89">
-        <v>7.066809999999999</v>
+        <v>7.152439999999999</v>
       </c>
       <c r="F89">
-        <v>7.449809999999999</v>
+        <v>7.535439999999999</v>
       </c>
       <c r="G89">
         <v>0.068</v>
@@ -8579,37 +8579,37 @@
         <v>0.651</v>
       </c>
       <c r="M89">
-        <v>1.756665198</v>
+        <v>1.776856752</v>
       </c>
       <c r="N89">
-        <v>-1.105665198</v>
+        <v>-1.125856752</v>
       </c>
       <c r="O89">
-        <v>-0.2211330396</v>
+        <v>-0.2251713504</v>
       </c>
       <c r="P89">
-        <v>-0.8845321583999999</v>
+        <v>-0.9006854015999999</v>
       </c>
       <c r="Q89">
-        <v>-0.7515321583999999</v>
+        <v>-0.7676854015999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6007926909528847</v>
+        <v>0.6470420818656252</v>
       </c>
       <c r="T89">
-        <v>6.077397444077122</v>
+        <v>6.583847231083549</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07411770902516622</v>
+        <v>0.07327546233169843</v>
       </c>
       <c r="W89">
-        <v>0.2183230442118658</v>
+        <v>0.2185216459821855</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3705885451258312</v>
+        <v>0.3663773116584922</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2699440982881983</v>
+        <v>0.2718440982881983</v>
       </c>
       <c r="C90">
-        <v>-4.521630988334389</v>
+        <v>-4.632021807858325</v>
       </c>
       <c r="D90">
-        <v>2.945809011665609</v>
+        <v>2.921048192141674</v>
       </c>
       <c r="E90">
-        <v>7.152439999999999</v>
+        <v>7.238069999999999</v>
       </c>
       <c r="F90">
-        <v>7.535439999999999</v>
+        <v>7.621069999999999</v>
       </c>
       <c r="G90">
         <v>0.068</v>
@@ -8661,37 +8661,37 @@
         <v>0.651</v>
       </c>
       <c r="M90">
-        <v>1.776856752</v>
+        <v>1.797048306</v>
       </c>
       <c r="N90">
-        <v>-1.125856752</v>
+        <v>-1.146048306</v>
       </c>
       <c r="O90">
-        <v>-0.2251713504</v>
+        <v>-0.2292096612</v>
       </c>
       <c r="P90">
-        <v>-0.9006854015999999</v>
+        <v>-0.9168386447999998</v>
       </c>
       <c r="Q90">
-        <v>-0.7676854015999999</v>
+        <v>-0.7838386447999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6470420818656252</v>
+        <v>0.7017004529443184</v>
       </c>
       <c r="T90">
-        <v>6.583847231083549</v>
+        <v>7.182378797545691</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07327546233169843</v>
+        <v>0.07245214253021869</v>
       </c>
       <c r="W90">
-        <v>0.2185216459821855</v>
+        <v>0.2187157847913744</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3663773116584922</v>
+        <v>0.3622607126510934</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2718440982881983</v>
+        <v>0.2737440982881982</v>
       </c>
       <c r="C91">
-        <v>-4.632021807858325</v>
+        <v>-4.741999845849868</v>
       </c>
       <c r="D91">
-        <v>2.921048192141674</v>
+        <v>2.896700154150131</v>
       </c>
       <c r="E91">
-        <v>7.238069999999999</v>
+        <v>7.323699999999999</v>
       </c>
       <c r="F91">
-        <v>7.621069999999999</v>
+        <v>7.706699999999999</v>
       </c>
       <c r="G91">
         <v>0.068</v>
@@ -8743,37 +8743,37 @@
         <v>0.651</v>
       </c>
       <c r="M91">
-        <v>1.797048306</v>
+        <v>1.81723986</v>
       </c>
       <c r="N91">
-        <v>-1.146048306</v>
+        <v>-1.16623986</v>
       </c>
       <c r="O91">
-        <v>-0.2292096612</v>
+        <v>-0.2332479719999999</v>
       </c>
       <c r="P91">
-        <v>-0.9168386447999998</v>
+        <v>-0.9329918879999998</v>
       </c>
       <c r="Q91">
-        <v>-0.7838386447999998</v>
+        <v>-0.7999918879999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7017004529443184</v>
+        <v>0.7672904982387503</v>
       </c>
       <c r="T91">
-        <v>7.182378797545691</v>
+        <v>7.900616677300261</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07245214253021869</v>
+        <v>0.07164711872432736</v>
       </c>
       <c r="W91">
-        <v>0.2187157847913744</v>
+        <v>0.2189056094048036</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3622607126510934</v>
+        <v>0.3582355936216368</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2737440982881982</v>
+        <v>0.2756440982881983</v>
       </c>
       <c r="C92">
-        <v>-4.741999845849868</v>
+        <v>-4.851575339051022</v>
       </c>
       <c r="D92">
-        <v>2.896700154150131</v>
+        <v>2.872754660948976</v>
       </c>
       <c r="E92">
-        <v>7.323699999999999</v>
+        <v>7.409329999999999</v>
       </c>
       <c r="F92">
-        <v>7.706699999999999</v>
+        <v>7.792329999999999</v>
       </c>
       <c r="G92">
         <v>0.068</v>
@@ -8825,37 +8825,37 @@
         <v>0.651</v>
       </c>
       <c r="M92">
-        <v>1.81723986</v>
+        <v>1.837431414</v>
       </c>
       <c r="N92">
-        <v>-1.16623986</v>
+        <v>-1.186431414</v>
       </c>
       <c r="O92">
-        <v>-0.2332479719999999</v>
+        <v>-0.2372862828</v>
       </c>
       <c r="P92">
-        <v>-0.9329918879999998</v>
+        <v>-0.9491451311999999</v>
       </c>
       <c r="Q92">
-        <v>-0.7999918879999998</v>
+        <v>-0.8161451311999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7672904982387503</v>
+        <v>0.8474561091541671</v>
       </c>
       <c r="T92">
-        <v>7.900616677300261</v>
+        <v>8.778462974778069</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07164711872432736</v>
+        <v>0.07085978774933475</v>
       </c>
       <c r="W92">
-        <v>0.2189056094048036</v>
+        <v>0.2190912620487069</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3582355936216368</v>
+        <v>0.3542989387466737</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2756440982881983</v>
+        <v>0.2775440982881983</v>
       </c>
       <c r="C93">
-        <v>-4.851575339051022</v>
+        <v>-4.960758188491941</v>
       </c>
       <c r="D93">
-        <v>2.872754660948976</v>
+        <v>2.849201811508059</v>
       </c>
       <c r="E93">
-        <v>7.409329999999999</v>
+        <v>7.494959999999999</v>
       </c>
       <c r="F93">
-        <v>7.792329999999999</v>
+        <v>7.877959999999999</v>
       </c>
       <c r="G93">
         <v>0.068</v>
@@ -8907,37 +8907,37 @@
         <v>0.651</v>
       </c>
       <c r="M93">
-        <v>1.837431414</v>
+        <v>1.857622968</v>
       </c>
       <c r="N93">
-        <v>-1.186431414</v>
+        <v>-1.206622968</v>
       </c>
       <c r="O93">
-        <v>-0.2372862828</v>
+        <v>-0.2413245936</v>
       </c>
       <c r="P93">
-        <v>-0.9491451311999999</v>
+        <v>-0.9652983743999999</v>
       </c>
       <c r="Q93">
-        <v>-0.8161451311999999</v>
+        <v>-0.8322983743999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8474561091541671</v>
+        <v>0.9476631227984383</v>
       </c>
       <c r="T93">
-        <v>8.778462974778069</v>
+        <v>9.875770846625331</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07085978774933475</v>
+        <v>0.07008957266510285</v>
       </c>
       <c r="W93">
-        <v>0.2190912620487069</v>
+        <v>0.2192728787655688</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3542989387466737</v>
+        <v>0.3504478633255143</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2775440982881983</v>
+        <v>0.2794440982881983</v>
       </c>
       <c r="C94">
-        <v>-4.960758188491941</v>
+        <v>-5.069557973141016</v>
       </c>
       <c r="D94">
-        <v>2.849201811508059</v>
+        <v>2.826032026858983</v>
       </c>
       <c r="E94">
-        <v>7.494959999999999</v>
+        <v>7.580589999999999</v>
       </c>
       <c r="F94">
-        <v>7.877959999999999</v>
+        <v>7.963589999999999</v>
       </c>
       <c r="G94">
         <v>0.068</v>
@@ -8989,37 +8989,37 @@
         <v>0.651</v>
       </c>
       <c r="M94">
-        <v>1.857622968</v>
+        <v>1.877814522</v>
       </c>
       <c r="N94">
-        <v>-1.206622968</v>
+        <v>-1.226814522</v>
       </c>
       <c r="O94">
-        <v>-0.2413245936</v>
+        <v>-0.2453629044</v>
       </c>
       <c r="P94">
-        <v>-0.9652983743999999</v>
+        <v>-0.9814516175999998</v>
       </c>
       <c r="Q94">
-        <v>-0.8322983743999999</v>
+        <v>-0.8484516175999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9476631227984383</v>
+        <v>1.076500711769644</v>
       </c>
       <c r="T94">
-        <v>9.875770846625331</v>
+        <v>11.28659525328609</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07008957266510285</v>
+        <v>0.06933592134612325</v>
       </c>
       <c r="W94">
-        <v>0.2192728787655688</v>
+        <v>0.2194505897465842</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3504478633255143</v>
+        <v>0.3466796067306163</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2794440982881983</v>
+        <v>0.2813440982881983</v>
       </c>
       <c r="C95">
-        <v>-5.069557973141016</v>
+        <v>-5.177983962894334</v>
       </c>
       <c r="D95">
-        <v>2.826032026858983</v>
+        <v>2.803236037105665</v>
       </c>
       <c r="E95">
-        <v>7.580589999999999</v>
+        <v>7.66622</v>
       </c>
       <c r="F95">
-        <v>7.963589999999999</v>
+        <v>8.04922</v>
       </c>
       <c r="G95">
         <v>0.068</v>
@@ -9071,37 +9071,37 @@
         <v>0.651</v>
       </c>
       <c r="M95">
-        <v>1.877814522</v>
+        <v>1.898006076</v>
       </c>
       <c r="N95">
-        <v>-1.226814522</v>
+        <v>-1.247006076</v>
       </c>
       <c r="O95">
-        <v>-0.2453629044</v>
+        <v>-0.2494012152</v>
       </c>
       <c r="P95">
-        <v>-0.9814516175999998</v>
+        <v>-0.9976048608000001</v>
       </c>
       <c r="Q95">
-        <v>-0.8484516175999998</v>
+        <v>-0.8646048608000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.076500711769644</v>
+        <v>1.248284163731252</v>
       </c>
       <c r="T95">
-        <v>11.28659525328609</v>
+        <v>13.16769446216711</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06933592134612325</v>
+        <v>0.06859830516159002</v>
       </c>
       <c r="W95">
-        <v>0.2194505897465842</v>
+        <v>0.2196245196428971</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3466796067306163</v>
+        <v>0.34299152580795</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2813440982881983</v>
+        <v>0.2832440982881983</v>
       </c>
       <c r="C96">
-        <v>-5.177983962894334</v>
+        <v>-5.28604513094146</v>
       </c>
       <c r="D96">
-        <v>2.803236037105665</v>
+        <v>2.78080486905854</v>
       </c>
       <c r="E96">
-        <v>7.66622</v>
+        <v>7.75185</v>
       </c>
       <c r="F96">
-        <v>8.04922</v>
+        <v>8.13485</v>
       </c>
       <c r="G96">
         <v>0.068</v>
@@ -9153,37 +9153,37 @@
         <v>0.651</v>
       </c>
       <c r="M96">
-        <v>1.898006076</v>
+        <v>1.91819763</v>
       </c>
       <c r="N96">
-        <v>-1.247006076</v>
+        <v>-1.26719763</v>
       </c>
       <c r="O96">
-        <v>-0.2494012152</v>
+        <v>-0.253439526</v>
       </c>
       <c r="P96">
-        <v>-0.9976048608000001</v>
+        <v>-1.013758104</v>
       </c>
       <c r="Q96">
-        <v>-0.8646048608000001</v>
+        <v>-0.8807581040000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.248284163731252</v>
+        <v>1.488780996477503</v>
       </c>
       <c r="T96">
-        <v>13.16769446216711</v>
+        <v>15.80123335460054</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06859830516159002</v>
+        <v>0.06787621773883644</v>
       </c>
       <c r="W96">
-        <v>0.2196245196428971</v>
+        <v>0.2197947878571824</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.34299152580795</v>
+        <v>0.3393810886941822</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2832440982881983</v>
+        <v>0.2851440982881983</v>
       </c>
       <c r="C97">
-        <v>-5.28604513094146</v>
+        <v>-5.393750165542269</v>
       </c>
       <c r="D97">
-        <v>2.78080486905854</v>
+        <v>2.758729834457731</v>
       </c>
       <c r="E97">
-        <v>7.75185</v>
+        <v>7.83748</v>
       </c>
       <c r="F97">
-        <v>8.13485</v>
+        <v>8.22048</v>
       </c>
       <c r="G97">
         <v>0.068</v>
@@ -9235,37 +9235,37 @@
         <v>0.651</v>
       </c>
       <c r="M97">
-        <v>1.91819763</v>
+        <v>1.938389184</v>
       </c>
       <c r="N97">
-        <v>-1.26719763</v>
+        <v>-1.287389184</v>
       </c>
       <c r="O97">
-        <v>-0.253439526</v>
+        <v>-0.2574778368</v>
       </c>
       <c r="P97">
-        <v>-1.013758104</v>
+        <v>-1.0299113472</v>
       </c>
       <c r="Q97">
-        <v>-0.8807581040000001</v>
+        <v>-0.8969113472000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.488780996477503</v>
+        <v>1.849526245596879</v>
       </c>
       <c r="T97">
-        <v>15.80123335460054</v>
+        <v>19.75154169325068</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06787621773883644</v>
+        <v>0.06716917380405689</v>
       </c>
       <c r="W97">
-        <v>0.2197947878571824</v>
+        <v>0.2199615088170034</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3393810886941822</v>
+        <v>0.3358458690202845</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2851440982881983</v>
+        <v>0.2870440982881983</v>
       </c>
       <c r="C98">
-        <v>-5.393750165542267</v>
+        <v>-5.501107481247242</v>
       </c>
       <c r="D98">
-        <v>2.758729834457731</v>
+        <v>2.737002518752757</v>
       </c>
       <c r="E98">
-        <v>7.837479999999998</v>
+        <v>7.923109999999999</v>
       </c>
       <c r="F98">
-        <v>8.220479999999998</v>
+        <v>8.306109999999999</v>
       </c>
       <c r="G98">
         <v>0.068</v>
@@ -9317,37 +9317,37 @@
         <v>0.651</v>
       </c>
       <c r="M98">
-        <v>1.938389184</v>
+        <v>1.958580738</v>
       </c>
       <c r="N98">
-        <v>-1.287389184</v>
+        <v>-1.307580738</v>
       </c>
       <c r="O98">
-        <v>-0.2574778368</v>
+        <v>-0.2615161476</v>
       </c>
       <c r="P98">
-        <v>-1.0299113472</v>
+        <v>-1.0460645904</v>
       </c>
       <c r="Q98">
-        <v>-0.8969113471999999</v>
+        <v>-0.9130645903999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.849526245596874</v>
+        <v>2.450768327462499</v>
       </c>
       <c r="T98">
-        <v>19.75154169325063</v>
+        <v>26.33538892433418</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06716917380405689</v>
+        <v>0.06647670809473673</v>
       </c>
       <c r="W98">
-        <v>0.2199615088170034</v>
+        <v>0.2201247922312611</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3358458690202845</v>
+        <v>0.3323835404736836</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2870440982881983</v>
+        <v>0.2889440982881983</v>
       </c>
       <c r="C99">
-        <v>-5.501107481247242</v>
+        <v>-5.608125229591709</v>
       </c>
       <c r="D99">
-        <v>2.737002518752757</v>
+        <v>2.71561477040829</v>
       </c>
       <c r="E99">
-        <v>7.923109999999999</v>
+        <v>8.00874</v>
       </c>
       <c r="F99">
-        <v>8.306109999999999</v>
+        <v>8.391739999999999</v>
       </c>
       <c r="G99">
         <v>0.068</v>
@@ -9399,37 +9399,37 @@
         <v>0.651</v>
       </c>
       <c r="M99">
-        <v>1.958580738</v>
+        <v>1.978772292</v>
       </c>
       <c r="N99">
-        <v>-1.307580738</v>
+        <v>-1.327772292</v>
       </c>
       <c r="O99">
-        <v>-0.2615161476</v>
+        <v>-0.2655544584</v>
       </c>
       <c r="P99">
-        <v>-1.0460645904</v>
+        <v>-1.0622178336</v>
       </c>
       <c r="Q99">
-        <v>-0.9130645903999999</v>
+        <v>-0.9292178335999997</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.450768327462499</v>
+        <v>3.653252491193748</v>
       </c>
       <c r="T99">
-        <v>26.33538892433418</v>
+        <v>39.50308338650126</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06647670809473673</v>
+        <v>0.06579837433866798</v>
       </c>
       <c r="W99">
-        <v>0.2201247922312611</v>
+        <v>0.2202847433309421</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3323835404736836</v>
+        <v>0.3289918716933399</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2889440982881983</v>
+        <v>0.2908440982881983</v>
       </c>
       <c r="C100">
-        <v>-5.608125229591709</v>
+        <v>-5.714811309292545</v>
       </c>
       <c r="D100">
-        <v>2.71561477040829</v>
+        <v>2.694558690707454</v>
       </c>
       <c r="E100">
-        <v>8.00874</v>
+        <v>8.094369999999998</v>
       </c>
       <c r="F100">
-        <v>8.391739999999999</v>
+        <v>8.477369999999999</v>
       </c>
       <c r="G100">
         <v>0.068</v>
@@ -9481,37 +9481,37 @@
         <v>0.651</v>
       </c>
       <c r="M100">
-        <v>1.978772292</v>
+        <v>1.998963846</v>
       </c>
       <c r="N100">
-        <v>-1.327772292</v>
+        <v>-1.347963846</v>
       </c>
       <c r="O100">
-        <v>-0.2655544584</v>
+        <v>-0.2695927692</v>
       </c>
       <c r="P100">
-        <v>-1.0622178336</v>
+        <v>-1.0783710768</v>
       </c>
       <c r="Q100">
-        <v>-0.9292178335999997</v>
+        <v>-0.9453710767999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.653252491193748</v>
+        <v>7.260704982387495</v>
       </c>
       <c r="T100">
-        <v>39.50308338650126</v>
+        <v>79.00616677300252</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06579837433866798</v>
+        <v>0.06513374429484305</v>
       </c>
       <c r="W100">
-        <v>0.2202847433309421</v>
+        <v>0.220441463095276</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3289918716933399</v>
+        <v>0.3256687214742152</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2908440982881983</v>
-      </c>
-      <c r="C101">
-        <v>-5.714811309292545</v>
-      </c>
-      <c r="D101">
-        <v>2.694558690707454</v>
-      </c>
-      <c r="E101">
-        <v>8.094369999999998</v>
-      </c>
-      <c r="F101">
-        <v>8.477369999999999</v>
-      </c>
-      <c r="G101">
-        <v>0.068</v>
-      </c>
-      <c r="H101">
-        <v>8.18</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.784</v>
-      </c>
-      <c r="K101">
-        <v>0.133</v>
-      </c>
-      <c r="L101">
-        <v>0.651</v>
-      </c>
-      <c r="M101">
-        <v>1.998963846</v>
-      </c>
-      <c r="N101">
-        <v>-1.347963846</v>
-      </c>
-      <c r="O101">
-        <v>-0.2695927692</v>
-      </c>
-      <c r="P101">
-        <v>-1.0783710768</v>
-      </c>
-      <c r="Q101">
-        <v>-0.9453710767999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.260704982387495</v>
-      </c>
-      <c r="T101">
-        <v>79.00616677300252</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06513374429484305</v>
-      </c>
-      <c r="W101">
-        <v>0.220441463095276</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3256687214742152</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
